--- a/public/docs/forms/Форма-40.1.xlsx
+++ b/public/docs/forms/Форма-40.1.xlsx
@@ -1,11 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B37DDB2-4D90-497C-A3DC-86333F1F85E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="AKD5sYPD0YKOfvymdFThY2UHBHxOnq8q3W7fBHV57QdqeG0Xv6SYMF/MDeWimc8Y8KM3eUnIZVntncj0eqRtEw==" workbookSaltValue="oLd5J4tMj2SHaGVOzGvEZA==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19410" windowHeight="10980"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Форма № 40 с приложением" sheetId="1" r:id="rId1"/>
@@ -13,12 +14,26 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Форма № 40 с приложением'!$A$1:$AI$124</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="196">
   <si>
     <t>1.</t>
   </si>
@@ -754,11 +769,17 @@
   <si>
     <t>2024</t>
   </si>
+  <si>
+    <t>2025</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1385,7 +1406,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="233">
+  <cellXfs count="238">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1575,6 +1596,521 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -1587,91 +2123,8 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1689,437 +2142,16 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2155,7 +2187,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Овал 1"/>
+        <xdr:cNvPr id="2" name="Овал 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2217,7 +2255,13 @@
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="3" name="Прямая соединительная линия 2"/>
+        <xdr:cNvPr id="3" name="Прямая соединительная линия 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
@@ -2268,7 +2312,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Овал 3"/>
+        <xdr:cNvPr id="4" name="Овал 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -2394,6 +2444,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -2429,6 +2496,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -2604,7 +2688,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2635,267 +2719,267 @@
     <col min="104" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="223" t="s">
+    <row r="1" spans="1:46" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="111" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="224"/>
-      <c r="C1" s="224"/>
-      <c r="D1" s="224"/>
-      <c r="E1" s="224"/>
-      <c r="F1" s="224"/>
-      <c r="G1" s="224"/>
-      <c r="H1" s="224"/>
-      <c r="I1" s="224"/>
-      <c r="J1" s="224"/>
-      <c r="K1" s="224"/>
-      <c r="L1" s="224"/>
-      <c r="M1" s="224"/>
-      <c r="N1" s="224"/>
-      <c r="O1" s="224"/>
-      <c r="P1" s="224"/>
-      <c r="Q1" s="224"/>
-      <c r="R1" s="224"/>
-      <c r="S1" s="224"/>
-      <c r="T1" s="224"/>
-      <c r="U1" s="224"/>
-      <c r="V1" s="224"/>
-      <c r="W1" s="224"/>
-      <c r="X1" s="224"/>
-      <c r="Y1" s="224"/>
-      <c r="Z1" s="224"/>
-      <c r="AA1" s="224"/>
-      <c r="AB1" s="224"/>
-      <c r="AC1" s="224"/>
-      <c r="AD1" s="224"/>
-      <c r="AE1" s="224"/>
-      <c r="AF1" s="224"/>
-      <c r="AG1" s="224"/>
-      <c r="AH1" s="224"/>
-      <c r="AI1" s="224"/>
-    </row>
-    <row r="2" spans="1:42" ht="1.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="206" t="s">
+      <c r="B1" s="112"/>
+      <c r="C1" s="112"/>
+      <c r="D1" s="112"/>
+      <c r="E1" s="112"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="112"/>
+      <c r="L1" s="112"/>
+      <c r="M1" s="112"/>
+      <c r="N1" s="112"/>
+      <c r="O1" s="112"/>
+      <c r="P1" s="112"/>
+      <c r="Q1" s="112"/>
+      <c r="R1" s="112"/>
+      <c r="S1" s="112"/>
+      <c r="T1" s="112"/>
+      <c r="U1" s="112"/>
+      <c r="V1" s="112"/>
+      <c r="W1" s="112"/>
+      <c r="X1" s="112"/>
+      <c r="Y1" s="112"/>
+      <c r="Z1" s="112"/>
+      <c r="AA1" s="112"/>
+      <c r="AB1" s="112"/>
+      <c r="AC1" s="112"/>
+      <c r="AD1" s="112"/>
+      <c r="AE1" s="112"/>
+      <c r="AF1" s="112"/>
+      <c r="AG1" s="112"/>
+      <c r="AH1" s="112"/>
+      <c r="AI1" s="112"/>
+    </row>
+    <row r="2" spans="1:46" ht="1.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="149" t="s">
         <v>187</v>
       </c>
-      <c r="B2" s="207"/>
-      <c r="C2" s="207"/>
-      <c r="D2" s="207"/>
-      <c r="E2" s="207"/>
-      <c r="F2" s="207"/>
-      <c r="G2" s="207"/>
-      <c r="H2" s="207"/>
-      <c r="I2" s="207"/>
-      <c r="J2" s="207"/>
-      <c r="K2" s="207"/>
-      <c r="L2" s="207"/>
-      <c r="M2" s="207"/>
-      <c r="N2" s="207"/>
-      <c r="O2" s="207"/>
-      <c r="P2" s="207"/>
-      <c r="Q2" s="207"/>
-      <c r="R2" s="207"/>
-      <c r="S2" s="207"/>
-      <c r="T2" s="207"/>
-      <c r="U2" s="207"/>
-      <c r="V2" s="207"/>
-      <c r="W2" s="207"/>
-      <c r="X2" s="207"/>
-      <c r="Y2" s="207"/>
-      <c r="Z2" s="207"/>
-      <c r="AA2" s="207"/>
-      <c r="AB2" s="207"/>
-      <c r="AC2" s="207"/>
-      <c r="AD2" s="207"/>
-      <c r="AE2" s="207"/>
-      <c r="AF2" s="207"/>
-      <c r="AG2" s="207"/>
-      <c r="AH2" s="207"/>
-      <c r="AI2" s="207"/>
-    </row>
-    <row r="3" spans="1:42" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="207"/>
-      <c r="B3" s="207"/>
-      <c r="C3" s="207"/>
-      <c r="D3" s="207"/>
-      <c r="E3" s="207"/>
-      <c r="F3" s="207"/>
-      <c r="G3" s="207"/>
-      <c r="H3" s="207"/>
-      <c r="I3" s="207"/>
-      <c r="J3" s="207"/>
-      <c r="K3" s="207"/>
-      <c r="L3" s="207"/>
-      <c r="M3" s="207"/>
-      <c r="N3" s="207"/>
-      <c r="O3" s="207"/>
-      <c r="P3" s="207"/>
-      <c r="Q3" s="207"/>
-      <c r="R3" s="207"/>
-      <c r="S3" s="207"/>
-      <c r="T3" s="207"/>
-      <c r="U3" s="207"/>
-      <c r="V3" s="207"/>
-      <c r="W3" s="207"/>
-      <c r="X3" s="207"/>
-      <c r="Y3" s="207"/>
-      <c r="Z3" s="207"/>
-      <c r="AA3" s="207"/>
-      <c r="AB3" s="207"/>
-      <c r="AC3" s="207"/>
-      <c r="AD3" s="207"/>
-      <c r="AE3" s="207"/>
-      <c r="AF3" s="207"/>
-      <c r="AG3" s="207"/>
-      <c r="AH3" s="207"/>
-      <c r="AI3" s="207"/>
-    </row>
-    <row r="4" spans="1:42" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="208"/>
-      <c r="B4" s="208"/>
-      <c r="C4" s="208"/>
-      <c r="D4" s="208"/>
-      <c r="E4" s="208"/>
-      <c r="F4" s="208"/>
-      <c r="G4" s="208"/>
-      <c r="H4" s="208"/>
-      <c r="I4" s="208"/>
-      <c r="J4" s="208"/>
-      <c r="K4" s="208"/>
-      <c r="L4" s="208"/>
-      <c r="M4" s="208"/>
-      <c r="N4" s="208"/>
-      <c r="O4" s="208"/>
-      <c r="P4" s="208"/>
-      <c r="Q4" s="208"/>
-      <c r="R4" s="208"/>
-      <c r="S4" s="208"/>
-      <c r="T4" s="208"/>
-      <c r="U4" s="208"/>
-      <c r="V4" s="208"/>
-      <c r="W4" s="208"/>
-      <c r="X4" s="208"/>
-      <c r="Y4" s="208"/>
-      <c r="Z4" s="208"/>
-      <c r="AA4" s="208"/>
-      <c r="AB4" s="208"/>
-      <c r="AC4" s="208"/>
-      <c r="AD4" s="208"/>
-      <c r="AE4" s="208"/>
-      <c r="AF4" s="208"/>
-      <c r="AG4" s="208"/>
-      <c r="AH4" s="208"/>
-      <c r="AI4" s="208"/>
-    </row>
-    <row r="5" spans="1:42" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="209" t="s">
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="150"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="150"/>
+      <c r="I2" s="150"/>
+      <c r="J2" s="150"/>
+      <c r="K2" s="150"/>
+      <c r="L2" s="150"/>
+      <c r="M2" s="150"/>
+      <c r="N2" s="150"/>
+      <c r="O2" s="150"/>
+      <c r="P2" s="150"/>
+      <c r="Q2" s="150"/>
+      <c r="R2" s="150"/>
+      <c r="S2" s="150"/>
+      <c r="T2" s="150"/>
+      <c r="U2" s="150"/>
+      <c r="V2" s="150"/>
+      <c r="W2" s="150"/>
+      <c r="X2" s="150"/>
+      <c r="Y2" s="150"/>
+      <c r="Z2" s="150"/>
+      <c r="AA2" s="150"/>
+      <c r="AB2" s="150"/>
+      <c r="AC2" s="150"/>
+      <c r="AD2" s="150"/>
+      <c r="AE2" s="150"/>
+      <c r="AF2" s="150"/>
+      <c r="AG2" s="150"/>
+      <c r="AH2" s="150"/>
+      <c r="AI2" s="150"/>
+    </row>
+    <row r="3" spans="1:46" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="150"/>
+      <c r="B3" s="150"/>
+      <c r="C3" s="150"/>
+      <c r="D3" s="150"/>
+      <c r="E3" s="150"/>
+      <c r="F3" s="150"/>
+      <c r="G3" s="150"/>
+      <c r="H3" s="150"/>
+      <c r="I3" s="150"/>
+      <c r="J3" s="150"/>
+      <c r="K3" s="150"/>
+      <c r="L3" s="150"/>
+      <c r="M3" s="150"/>
+      <c r="N3" s="150"/>
+      <c r="O3" s="150"/>
+      <c r="P3" s="150"/>
+      <c r="Q3" s="150"/>
+      <c r="R3" s="150"/>
+      <c r="S3" s="150"/>
+      <c r="T3" s="150"/>
+      <c r="U3" s="150"/>
+      <c r="V3" s="150"/>
+      <c r="W3" s="150"/>
+      <c r="X3" s="150"/>
+      <c r="Y3" s="150"/>
+      <c r="Z3" s="150"/>
+      <c r="AA3" s="150"/>
+      <c r="AB3" s="150"/>
+      <c r="AC3" s="150"/>
+      <c r="AD3" s="150"/>
+      <c r="AE3" s="150"/>
+      <c r="AF3" s="150"/>
+      <c r="AG3" s="150"/>
+      <c r="AH3" s="150"/>
+      <c r="AI3" s="150"/>
+    </row>
+    <row r="4" spans="1:46" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="151"/>
+      <c r="B4" s="151"/>
+      <c r="C4" s="151"/>
+      <c r="D4" s="151"/>
+      <c r="E4" s="151"/>
+      <c r="F4" s="151"/>
+      <c r="G4" s="151"/>
+      <c r="H4" s="151"/>
+      <c r="I4" s="151"/>
+      <c r="J4" s="151"/>
+      <c r="K4" s="151"/>
+      <c r="L4" s="151"/>
+      <c r="M4" s="151"/>
+      <c r="N4" s="151"/>
+      <c r="O4" s="151"/>
+      <c r="P4" s="151"/>
+      <c r="Q4" s="151"/>
+      <c r="R4" s="151"/>
+      <c r="S4" s="151"/>
+      <c r="T4" s="151"/>
+      <c r="U4" s="151"/>
+      <c r="V4" s="151"/>
+      <c r="W4" s="151"/>
+      <c r="X4" s="151"/>
+      <c r="Y4" s="151"/>
+      <c r="Z4" s="151"/>
+      <c r="AA4" s="151"/>
+      <c r="AB4" s="151"/>
+      <c r="AC4" s="151"/>
+      <c r="AD4" s="151"/>
+      <c r="AE4" s="151"/>
+      <c r="AF4" s="151"/>
+      <c r="AG4" s="151"/>
+      <c r="AH4" s="151"/>
+      <c r="AI4" s="151"/>
+    </row>
+    <row r="5" spans="1:46" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="152" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="209"/>
-      <c r="C5" s="209"/>
-      <c r="D5" s="209"/>
-      <c r="E5" s="209"/>
-      <c r="F5" s="209"/>
-      <c r="G5" s="209"/>
-      <c r="H5" s="209"/>
-      <c r="I5" s="209"/>
-      <c r="J5" s="209"/>
-      <c r="K5" s="209"/>
-      <c r="L5" s="209"/>
-      <c r="M5" s="209"/>
-      <c r="N5" s="209"/>
-      <c r="O5" s="209"/>
-      <c r="P5" s="209"/>
-      <c r="Q5" s="209"/>
-      <c r="R5" s="209"/>
-      <c r="S5" s="209"/>
-      <c r="T5" s="209"/>
-      <c r="U5" s="209"/>
-      <c r="V5" s="209"/>
-      <c r="W5" s="209"/>
-      <c r="X5" s="209"/>
-      <c r="Y5" s="209"/>
-      <c r="Z5" s="209"/>
-      <c r="AA5" s="209"/>
-      <c r="AB5" s="209"/>
-      <c r="AC5" s="209"/>
-      <c r="AD5" s="209"/>
-      <c r="AE5" s="209"/>
-      <c r="AF5" s="209"/>
-      <c r="AG5" s="209"/>
-      <c r="AH5" s="209"/>
-      <c r="AI5" s="209"/>
-    </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="A6" s="210"/>
-      <c r="B6" s="210"/>
-      <c r="C6" s="210"/>
-      <c r="D6" s="210"/>
-      <c r="E6" s="210"/>
-      <c r="F6" s="210"/>
-      <c r="G6" s="210"/>
-      <c r="H6" s="210"/>
-      <c r="I6" s="210"/>
-      <c r="J6" s="210"/>
-      <c r="K6" s="210"/>
-      <c r="L6" s="210"/>
-      <c r="M6" s="210"/>
-      <c r="N6" s="210"/>
-      <c r="O6" s="210"/>
-      <c r="P6" s="210"/>
-      <c r="Q6" s="210"/>
-      <c r="R6" s="210"/>
-      <c r="S6" s="210"/>
-      <c r="T6" s="210"/>
-      <c r="U6" s="210"/>
-      <c r="V6" s="210"/>
-      <c r="W6" s="210"/>
-      <c r="X6" s="210"/>
-      <c r="Y6" s="210"/>
-      <c r="Z6" s="210"/>
-      <c r="AA6" s="210"/>
-      <c r="AB6" s="210"/>
-      <c r="AC6" s="210"/>
-      <c r="AD6" s="210"/>
-      <c r="AE6" s="210"/>
-      <c r="AF6" s="210"/>
-      <c r="AG6" s="210"/>
-      <c r="AH6" s="210"/>
-      <c r="AI6" s="210"/>
+      <c r="B5" s="152"/>
+      <c r="C5" s="152"/>
+      <c r="D5" s="152"/>
+      <c r="E5" s="152"/>
+      <c r="F5" s="152"/>
+      <c r="G5" s="152"/>
+      <c r="H5" s="152"/>
+      <c r="I5" s="152"/>
+      <c r="J5" s="152"/>
+      <c r="K5" s="152"/>
+      <c r="L5" s="152"/>
+      <c r="M5" s="152"/>
+      <c r="N5" s="152"/>
+      <c r="O5" s="152"/>
+      <c r="P5" s="152"/>
+      <c r="Q5" s="152"/>
+      <c r="R5" s="152"/>
+      <c r="S5" s="152"/>
+      <c r="T5" s="152"/>
+      <c r="U5" s="152"/>
+      <c r="V5" s="152"/>
+      <c r="W5" s="152"/>
+      <c r="X5" s="152"/>
+      <c r="Y5" s="152"/>
+      <c r="Z5" s="152"/>
+      <c r="AA5" s="152"/>
+      <c r="AB5" s="152"/>
+      <c r="AC5" s="152"/>
+      <c r="AD5" s="152"/>
+      <c r="AE5" s="152"/>
+      <c r="AF5" s="152"/>
+      <c r="AG5" s="152"/>
+      <c r="AH5" s="152"/>
+      <c r="AI5" s="152"/>
+    </row>
+    <row r="6" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A6" s="153"/>
+      <c r="B6" s="153"/>
+      <c r="C6" s="153"/>
+      <c r="D6" s="153"/>
+      <c r="E6" s="153"/>
+      <c r="F6" s="153"/>
+      <c r="G6" s="153"/>
+      <c r="H6" s="153"/>
+      <c r="I6" s="153"/>
+      <c r="J6" s="153"/>
+      <c r="K6" s="153"/>
+      <c r="L6" s="153"/>
+      <c r="M6" s="153"/>
+      <c r="N6" s="153"/>
+      <c r="O6" s="153"/>
+      <c r="P6" s="153"/>
+      <c r="Q6" s="153"/>
+      <c r="R6" s="153"/>
+      <c r="S6" s="153"/>
+      <c r="T6" s="153"/>
+      <c r="U6" s="153"/>
+      <c r="V6" s="153"/>
+      <c r="W6" s="153"/>
+      <c r="X6" s="153"/>
+      <c r="Y6" s="153"/>
+      <c r="Z6" s="153"/>
+      <c r="AA6" s="153"/>
+      <c r="AB6" s="153"/>
+      <c r="AC6" s="153"/>
+      <c r="AD6" s="153"/>
+      <c r="AE6" s="153"/>
+      <c r="AF6" s="153"/>
+      <c r="AG6" s="153"/>
+      <c r="AH6" s="153"/>
+      <c r="AI6" s="153"/>
       <c r="AJ6" s="65"/>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="160" t="s">
+      <c r="B7" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="160"/>
-      <c r="D7" s="160"/>
-      <c r="E7" s="160"/>
-      <c r="F7" s="160"/>
-      <c r="G7" s="160"/>
-      <c r="H7" s="160"/>
-      <c r="I7" s="160"/>
-      <c r="J7" s="160"/>
-      <c r="K7" s="160"/>
-      <c r="L7" s="160"/>
-      <c r="M7" s="160"/>
-      <c r="N7" s="160"/>
-      <c r="O7" s="72"/>
-      <c r="P7" s="73"/>
-      <c r="Q7" s="73"/>
-      <c r="R7" s="73"/>
-      <c r="S7" s="73"/>
-      <c r="T7" s="73"/>
-      <c r="U7" s="73"/>
-      <c r="V7" s="73"/>
-      <c r="W7" s="74"/>
-      <c r="X7" s="75" t="s">
+      <c r="C7" s="103"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="103"/>
+      <c r="F7" s="103"/>
+      <c r="G7" s="103"/>
+      <c r="H7" s="103"/>
+      <c r="I7" s="103"/>
+      <c r="J7" s="103"/>
+      <c r="K7" s="103"/>
+      <c r="L7" s="103"/>
+      <c r="M7" s="103"/>
+      <c r="N7" s="103"/>
+      <c r="O7" s="225"/>
+      <c r="P7" s="226"/>
+      <c r="Q7" s="226"/>
+      <c r="R7" s="226"/>
+      <c r="S7" s="226"/>
+      <c r="T7" s="226"/>
+      <c r="U7" s="226"/>
+      <c r="V7" s="226"/>
+      <c r="W7" s="227"/>
+      <c r="X7" s="167" t="s">
         <v>185</v>
       </c>
-      <c r="Y7" s="75"/>
+      <c r="Y7" s="167"/>
       <c r="Z7" s="67"/>
       <c r="AA7" s="68"/>
       <c r="AB7" s="69"/>
@@ -2908,64 +2992,64 @@
       <c r="AI7" s="71"/>
       <c r="AJ7" s="65"/>
     </row>
-    <row r="8" spans="1:42" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="O8" s="163" t="s">
+    <row r="8" spans="1:46" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O8" s="84" t="s">
         <v>186</v>
       </c>
-      <c r="P8" s="163"/>
-      <c r="Q8" s="163"/>
-      <c r="R8" s="163"/>
-      <c r="S8" s="163"/>
-      <c r="T8" s="163"/>
-      <c r="U8" s="163"/>
-      <c r="V8" s="163"/>
-      <c r="W8" s="163"/>
-      <c r="X8" s="163"/>
-      <c r="Y8" s="163"/>
-      <c r="Z8" s="163"/>
-      <c r="AA8" s="163"/>
-      <c r="AB8" s="163"/>
-      <c r="AC8" s="163"/>
-      <c r="AD8" s="163"/>
-      <c r="AE8" s="163"/>
-      <c r="AF8" s="163"/>
-      <c r="AG8" s="163"/>
-      <c r="AH8" s="163"/>
-      <c r="AI8" s="163"/>
+      <c r="P8" s="84"/>
+      <c r="Q8" s="84"/>
+      <c r="R8" s="84"/>
+      <c r="S8" s="84"/>
+      <c r="T8" s="84"/>
+      <c r="U8" s="84"/>
+      <c r="V8" s="84"/>
+      <c r="W8" s="84"/>
+      <c r="X8" s="84"/>
+      <c r="Y8" s="84"/>
+      <c r="Z8" s="84"/>
+      <c r="AA8" s="84"/>
+      <c r="AB8" s="84"/>
+      <c r="AC8" s="84"/>
+      <c r="AD8" s="84"/>
+      <c r="AE8" s="84"/>
+      <c r="AF8" s="84"/>
+      <c r="AG8" s="84"/>
+      <c r="AH8" s="84"/>
+      <c r="AI8" s="84"/>
       <c r="AJ8" s="65"/>
     </row>
-    <row r="9" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="85" t="s">
+      <c r="B9" s="115" t="s">
         <v>103</v>
       </c>
-      <c r="C9" s="85"/>
-      <c r="D9" s="85"/>
-      <c r="E9" s="85"/>
-      <c r="F9" s="85"/>
-      <c r="G9" s="85"/>
-      <c r="H9" s="85"/>
-      <c r="I9" s="85"/>
-      <c r="J9" s="85"/>
-      <c r="K9" s="72"/>
-      <c r="L9" s="73"/>
-      <c r="M9" s="73"/>
-      <c r="N9" s="73"/>
-      <c r="O9" s="73"/>
-      <c r="P9" s="73"/>
-      <c r="Q9" s="73"/>
-      <c r="R9" s="73"/>
-      <c r="S9" s="73"/>
-      <c r="T9" s="73"/>
-      <c r="U9" s="73"/>
-      <c r="V9" s="73"/>
-      <c r="W9" s="74"/>
-      <c r="X9" s="75" t="s">
+      <c r="C9" s="115"/>
+      <c r="D9" s="115"/>
+      <c r="E9" s="115"/>
+      <c r="F9" s="115"/>
+      <c r="G9" s="115"/>
+      <c r="H9" s="115"/>
+      <c r="I9" s="115"/>
+      <c r="J9" s="115"/>
+      <c r="K9" s="225"/>
+      <c r="L9" s="226"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="226"/>
+      <c r="O9" s="226"/>
+      <c r="P9" s="226"/>
+      <c r="Q9" s="226"/>
+      <c r="R9" s="226"/>
+      <c r="S9" s="226"/>
+      <c r="T9" s="226"/>
+      <c r="U9" s="226"/>
+      <c r="V9" s="226"/>
+      <c r="W9" s="227"/>
+      <c r="X9" s="167" t="s">
         <v>185</v>
       </c>
-      <c r="Y9" s="75"/>
+      <c r="Y9" s="167"/>
       <c r="Z9" s="67"/>
       <c r="AA9" s="68"/>
       <c r="AB9" s="69"/>
@@ -2978,340 +3062,365 @@
       <c r="AI9" s="71"/>
       <c r="AJ9" s="65"/>
     </row>
-    <row r="10" spans="1:42" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="J10" s="163" t="s">
+    <row r="10" spans="1:46" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J10" s="84" t="s">
         <v>186</v>
       </c>
-      <c r="K10" s="163"/>
-      <c r="L10" s="163"/>
-      <c r="M10" s="163"/>
-      <c r="N10" s="163"/>
-      <c r="O10" s="163"/>
-      <c r="P10" s="163"/>
-      <c r="Q10" s="163"/>
-      <c r="R10" s="163"/>
-      <c r="S10" s="163"/>
-      <c r="T10" s="163"/>
-      <c r="U10" s="163"/>
-      <c r="V10" s="163"/>
-      <c r="W10" s="163"/>
-      <c r="X10" s="163"/>
-      <c r="Y10" s="163"/>
-      <c r="Z10" s="163"/>
-      <c r="AA10" s="163"/>
-      <c r="AB10" s="163"/>
-      <c r="AC10" s="163"/>
-      <c r="AD10" s="163"/>
-      <c r="AE10" s="163"/>
-      <c r="AF10" s="163"/>
-      <c r="AG10" s="163"/>
-      <c r="AH10" s="163"/>
-      <c r="AI10" s="163"/>
+      <c r="K10" s="84"/>
+      <c r="L10" s="84"/>
+      <c r="M10" s="84"/>
+      <c r="N10" s="84"/>
+      <c r="O10" s="84"/>
+      <c r="P10" s="84"/>
+      <c r="Q10" s="84"/>
+      <c r="R10" s="84"/>
+      <c r="S10" s="84"/>
+      <c r="T10" s="84"/>
+      <c r="U10" s="84"/>
+      <c r="V10" s="84"/>
+      <c r="W10" s="84"/>
+      <c r="X10" s="84"/>
+      <c r="Y10" s="84"/>
+      <c r="Z10" s="84"/>
+      <c r="AA10" s="84"/>
+      <c r="AB10" s="84"/>
+      <c r="AC10" s="84"/>
+      <c r="AD10" s="84"/>
+      <c r="AE10" s="84"/>
+      <c r="AF10" s="84"/>
+      <c r="AG10" s="84"/>
+      <c r="AH10" s="84"/>
+      <c r="AI10" s="84"/>
       <c r="AJ10" s="65"/>
     </row>
-    <row r="11" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="222" t="s">
+      <c r="B11" s="140" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="222"/>
-      <c r="D11" s="222"/>
-      <c r="E11" s="222"/>
-      <c r="F11" s="202"/>
-      <c r="G11" s="203"/>
-      <c r="H11" s="203"/>
-      <c r="I11" s="203"/>
-      <c r="J11" s="203"/>
-      <c r="K11" s="203"/>
-      <c r="L11" s="203"/>
-      <c r="M11" s="203"/>
-      <c r="N11" s="203"/>
-      <c r="O11" s="203"/>
-      <c r="P11" s="203"/>
-      <c r="Q11" s="203"/>
-      <c r="R11" s="203"/>
-      <c r="S11" s="203"/>
-      <c r="T11" s="203"/>
-      <c r="U11" s="203"/>
-      <c r="V11" s="203"/>
-      <c r="W11" s="203"/>
-      <c r="X11" s="203"/>
-      <c r="Y11" s="203"/>
-      <c r="Z11" s="203"/>
-      <c r="AA11" s="203"/>
-      <c r="AB11" s="203"/>
-      <c r="AC11" s="203"/>
-      <c r="AD11" s="203"/>
-      <c r="AE11" s="203"/>
-      <c r="AF11" s="203"/>
-      <c r="AG11" s="203"/>
-      <c r="AH11" s="204"/>
+      <c r="C11" s="140"/>
+      <c r="D11" s="140"/>
+      <c r="E11" s="140"/>
+      <c r="F11" s="145"/>
+      <c r="G11" s="146"/>
+      <c r="H11" s="146"/>
+      <c r="I11" s="146"/>
+      <c r="J11" s="146"/>
+      <c r="K11" s="146"/>
+      <c r="L11" s="146"/>
+      <c r="M11" s="146"/>
+      <c r="N11" s="146"/>
+      <c r="O11" s="146"/>
+      <c r="P11" s="146"/>
+      <c r="Q11" s="146"/>
+      <c r="R11" s="146"/>
+      <c r="S11" s="146"/>
+      <c r="T11" s="146"/>
+      <c r="U11" s="146"/>
+      <c r="V11" s="146"/>
+      <c r="W11" s="146"/>
+      <c r="X11" s="146"/>
+      <c r="Y11" s="146"/>
+      <c r="Z11" s="146"/>
+      <c r="AA11" s="146"/>
+      <c r="AB11" s="146"/>
+      <c r="AC11" s="146"/>
+      <c r="AD11" s="146"/>
+      <c r="AE11" s="146"/>
+      <c r="AF11" s="146"/>
+      <c r="AG11" s="146"/>
+      <c r="AH11" s="147"/>
       <c r="AI11" s="10"/>
       <c r="AJ11" s="65"/>
     </row>
-    <row r="12" spans="1:42" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F12" s="163" t="s">
+    <row r="12" spans="1:46" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F12" s="84" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="163"/>
-      <c r="H12" s="163"/>
-      <c r="I12" s="163"/>
-      <c r="J12" s="163"/>
-      <c r="K12" s="163"/>
-      <c r="L12" s="163"/>
-      <c r="M12" s="163"/>
-      <c r="N12" s="163"/>
-      <c r="O12" s="163"/>
-      <c r="P12" s="163"/>
-      <c r="Q12" s="163"/>
-      <c r="R12" s="163"/>
-      <c r="S12" s="163"/>
-      <c r="T12" s="163"/>
-      <c r="U12" s="163"/>
-      <c r="V12" s="163"/>
-      <c r="W12" s="163"/>
-      <c r="X12" s="163"/>
-      <c r="Y12" s="163"/>
-      <c r="Z12" s="163"/>
-      <c r="AA12" s="163"/>
-      <c r="AB12" s="163"/>
-      <c r="AC12" s="163"/>
-      <c r="AD12" s="163"/>
-      <c r="AE12" s="163"/>
-      <c r="AF12" s="163"/>
-      <c r="AG12" s="163"/>
-      <c r="AH12" s="163"/>
-      <c r="AI12" s="163"/>
-    </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
-      <c r="B13" s="85" t="s">
+      <c r="G12" s="84"/>
+      <c r="H12" s="84"/>
+      <c r="I12" s="84"/>
+      <c r="J12" s="84"/>
+      <c r="K12" s="84"/>
+      <c r="L12" s="84"/>
+      <c r="M12" s="84"/>
+      <c r="N12" s="84"/>
+      <c r="O12" s="84"/>
+      <c r="P12" s="84"/>
+      <c r="Q12" s="84"/>
+      <c r="R12" s="84"/>
+      <c r="S12" s="84"/>
+      <c r="T12" s="84"/>
+      <c r="U12" s="84"/>
+      <c r="V12" s="84"/>
+      <c r="W12" s="84"/>
+      <c r="X12" s="84"/>
+      <c r="Y12" s="84"/>
+      <c r="Z12" s="84"/>
+      <c r="AA12" s="84"/>
+      <c r="AB12" s="84"/>
+      <c r="AC12" s="84"/>
+      <c r="AD12" s="84"/>
+      <c r="AE12" s="84"/>
+      <c r="AF12" s="84"/>
+      <c r="AG12" s="84"/>
+      <c r="AH12" s="84"/>
+      <c r="AI12" s="84"/>
+    </row>
+    <row r="13" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="B13" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="85"/>
-      <c r="D13" s="85"/>
-      <c r="E13" s="85"/>
-      <c r="F13" s="85"/>
-      <c r="G13" s="85"/>
-      <c r="H13" s="205"/>
-      <c r="I13" s="211"/>
-      <c r="J13" s="212"/>
-      <c r="K13" s="212"/>
-      <c r="L13" s="212"/>
-      <c r="M13" s="212"/>
-      <c r="N13" s="212"/>
-      <c r="O13" s="212"/>
-      <c r="P13" s="212"/>
-      <c r="Q13" s="212"/>
-      <c r="R13" s="212"/>
-      <c r="S13" s="212"/>
-      <c r="T13" s="212"/>
-      <c r="U13" s="212"/>
-      <c r="V13" s="212"/>
-      <c r="W13" s="212"/>
-      <c r="X13" s="212"/>
-      <c r="Y13" s="212"/>
-      <c r="Z13" s="212"/>
-      <c r="AA13" s="212"/>
-      <c r="AB13" s="212"/>
-      <c r="AC13" s="212"/>
-      <c r="AD13" s="212"/>
-      <c r="AE13" s="212"/>
-      <c r="AF13" s="212"/>
-      <c r="AG13" s="212"/>
-      <c r="AH13" s="212"/>
-      <c r="AI13" s="213"/>
-    </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="C13" s="115"/>
+      <c r="D13" s="115"/>
+      <c r="E13" s="115"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="115"/>
+      <c r="H13" s="148"/>
+      <c r="I13" s="158"/>
+      <c r="J13" s="159"/>
+      <c r="K13" s="159"/>
+      <c r="L13" s="159"/>
+      <c r="M13" s="159"/>
+      <c r="N13" s="159"/>
+      <c r="O13" s="159"/>
+      <c r="P13" s="159"/>
+      <c r="Q13" s="159"/>
+      <c r="R13" s="159"/>
+      <c r="S13" s="159"/>
+      <c r="T13" s="159"/>
+      <c r="U13" s="159"/>
+      <c r="V13" s="159"/>
+      <c r="W13" s="159"/>
+      <c r="X13" s="159"/>
+      <c r="Y13" s="159"/>
+      <c r="Z13" s="159"/>
+      <c r="AA13" s="159"/>
+      <c r="AB13" s="159"/>
+      <c r="AC13" s="159"/>
+      <c r="AD13" s="159"/>
+      <c r="AE13" s="159"/>
+      <c r="AF13" s="159"/>
+      <c r="AG13" s="159"/>
+      <c r="AH13" s="159"/>
+      <c r="AI13" s="160"/>
+    </row>
+    <row r="14" spans="1:46" x14ac:dyDescent="0.25">
       <c r="F14" s="34"/>
       <c r="G14" s="34"/>
       <c r="H14" s="34"/>
-      <c r="I14" s="214"/>
-      <c r="J14" s="215"/>
-      <c r="K14" s="215"/>
-      <c r="L14" s="215"/>
-      <c r="M14" s="215"/>
-      <c r="N14" s="215"/>
-      <c r="O14" s="215"/>
-      <c r="P14" s="215"/>
-      <c r="Q14" s="215"/>
-      <c r="R14" s="215"/>
-      <c r="S14" s="215"/>
-      <c r="T14" s="215"/>
-      <c r="U14" s="215"/>
-      <c r="V14" s="215"/>
-      <c r="W14" s="215"/>
-      <c r="X14" s="215"/>
-      <c r="Y14" s="215"/>
-      <c r="Z14" s="215"/>
-      <c r="AA14" s="215"/>
-      <c r="AB14" s="215"/>
-      <c r="AC14" s="215"/>
-      <c r="AD14" s="215"/>
-      <c r="AE14" s="215"/>
-      <c r="AF14" s="215"/>
-      <c r="AG14" s="215"/>
-      <c r="AH14" s="215"/>
-      <c r="AI14" s="216"/>
-      <c r="AP14" s="30"/>
-    </row>
-    <row r="15" spans="1:42" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="I15" s="129" t="s">
+      <c r="I14" s="161"/>
+      <c r="J14" s="162"/>
+      <c r="K14" s="162"/>
+      <c r="L14" s="162"/>
+      <c r="M14" s="162"/>
+      <c r="N14" s="162"/>
+      <c r="O14" s="162"/>
+      <c r="P14" s="162"/>
+      <c r="Q14" s="162"/>
+      <c r="R14" s="162"/>
+      <c r="S14" s="162"/>
+      <c r="T14" s="162"/>
+      <c r="U14" s="162"/>
+      <c r="V14" s="162"/>
+      <c r="W14" s="162"/>
+      <c r="X14" s="162"/>
+      <c r="Y14" s="162"/>
+      <c r="Z14" s="162"/>
+      <c r="AA14" s="162"/>
+      <c r="AB14" s="162"/>
+      <c r="AC14" s="162"/>
+      <c r="AD14" s="162"/>
+      <c r="AE14" s="162"/>
+      <c r="AF14" s="162"/>
+      <c r="AG14" s="162"/>
+      <c r="AH14" s="162"/>
+      <c r="AI14" s="163"/>
+      <c r="AN14" s="233"/>
+      <c r="AO14" s="233"/>
+      <c r="AP14" s="234"/>
+      <c r="AQ14" s="233"/>
+      <c r="AR14" s="233"/>
+      <c r="AS14" s="233"/>
+      <c r="AT14" s="235"/>
+    </row>
+    <row r="15" spans="1:46" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I15" s="154" t="s">
         <v>102</v>
       </c>
-      <c r="J15" s="129"/>
-      <c r="K15" s="129"/>
-      <c r="L15" s="129"/>
-      <c r="M15" s="129"/>
-      <c r="N15" s="129"/>
-      <c r="O15" s="129"/>
-      <c r="P15" s="129"/>
-      <c r="Q15" s="129"/>
-      <c r="R15" s="129"/>
-      <c r="S15" s="129"/>
-      <c r="T15" s="129"/>
-      <c r="U15" s="129"/>
-      <c r="V15" s="129"/>
-      <c r="W15" s="129"/>
-      <c r="X15" s="129"/>
-      <c r="Y15" s="129"/>
-      <c r="Z15" s="129"/>
-      <c r="AA15" s="129"/>
-      <c r="AB15" s="129"/>
-      <c r="AC15" s="129"/>
-      <c r="AD15" s="129"/>
-      <c r="AE15" s="129"/>
-      <c r="AF15" s="129"/>
-      <c r="AG15" s="129"/>
-      <c r="AH15" s="129"/>
-      <c r="AI15" s="129"/>
-      <c r="AP15" s="30"/>
-    </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="J15" s="154"/>
+      <c r="K15" s="154"/>
+      <c r="L15" s="154"/>
+      <c r="M15" s="154"/>
+      <c r="N15" s="154"/>
+      <c r="O15" s="154"/>
+      <c r="P15" s="154"/>
+      <c r="Q15" s="154"/>
+      <c r="R15" s="154"/>
+      <c r="S15" s="154"/>
+      <c r="T15" s="154"/>
+      <c r="U15" s="154"/>
+      <c r="V15" s="154"/>
+      <c r="W15" s="154"/>
+      <c r="X15" s="154"/>
+      <c r="Y15" s="154"/>
+      <c r="Z15" s="154"/>
+      <c r="AA15" s="154"/>
+      <c r="AB15" s="154"/>
+      <c r="AC15" s="154"/>
+      <c r="AD15" s="154"/>
+      <c r="AE15" s="154"/>
+      <c r="AF15" s="154"/>
+      <c r="AG15" s="154"/>
+      <c r="AH15" s="154"/>
+      <c r="AI15" s="154"/>
+      <c r="AN15" s="233"/>
+      <c r="AO15" s="233"/>
+      <c r="AP15" s="234"/>
+      <c r="AQ15" s="233"/>
+      <c r="AR15" s="233"/>
+      <c r="AS15" s="233"/>
+      <c r="AT15" s="235"/>
+    </row>
+    <row r="16" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="160" t="s">
+      <c r="B16" s="103" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="160"/>
-      <c r="D16" s="160"/>
-      <c r="E16" s="160"/>
-      <c r="F16" s="160"/>
-      <c r="G16" s="160"/>
-      <c r="H16" s="160"/>
-      <c r="I16" s="160"/>
-      <c r="J16" s="160"/>
-      <c r="K16" s="160"/>
-      <c r="L16" s="160"/>
-      <c r="M16" s="160"/>
-      <c r="N16" s="160"/>
-      <c r="O16" s="160"/>
-      <c r="P16" s="160"/>
-      <c r="Q16" s="205"/>
-      <c r="R16" s="114" t="s">
+      <c r="C16" s="103"/>
+      <c r="D16" s="103"/>
+      <c r="E16" s="103"/>
+      <c r="F16" s="103"/>
+      <c r="G16" s="103"/>
+      <c r="H16" s="103"/>
+      <c r="I16" s="103"/>
+      <c r="J16" s="103"/>
+      <c r="K16" s="103"/>
+      <c r="L16" s="103"/>
+      <c r="M16" s="103"/>
+      <c r="N16" s="103"/>
+      <c r="O16" s="103"/>
+      <c r="P16" s="103"/>
+      <c r="Q16" s="148"/>
+      <c r="R16" s="104" t="s">
         <v>40</v>
       </c>
-      <c r="S16" s="115"/>
-      <c r="T16" s="116"/>
-      <c r="AP16" s="30"/>
-    </row>
-    <row r="17" spans="1:45" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="AP17" s="30"/>
-    </row>
-    <row r="18" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="S16" s="105"/>
+      <c r="T16" s="106"/>
+      <c r="AN16" s="233"/>
+      <c r="AO16" s="233"/>
+      <c r="AP16" s="234"/>
+      <c r="AQ16" s="233"/>
+      <c r="AR16" s="233"/>
+      <c r="AS16" s="233"/>
+      <c r="AT16" s="235"/>
+    </row>
+    <row r="17" spans="1:46" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AN17" s="233"/>
+      <c r="AO17" s="233"/>
+      <c r="AP17" s="234"/>
+      <c r="AQ17" s="233"/>
+      <c r="AR17" s="233"/>
+      <c r="AS17" s="233"/>
+      <c r="AT17" s="235"/>
+    </row>
+    <row r="18" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="160" t="s">
+      <c r="B18" s="103" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="160"/>
-      <c r="D18" s="160"/>
-      <c r="E18" s="160"/>
-      <c r="F18" s="160"/>
-      <c r="G18" s="160"/>
-      <c r="H18" s="160"/>
-      <c r="I18" s="160"/>
-      <c r="J18" s="160"/>
-      <c r="K18" s="160"/>
-      <c r="L18" s="160"/>
-      <c r="M18" s="160"/>
-      <c r="N18" s="160"/>
-      <c r="O18" s="160"/>
-      <c r="P18" s="160"/>
-      <c r="Q18" s="107"/>
-      <c r="R18" s="108"/>
-      <c r="S18" s="108"/>
-      <c r="T18" s="108"/>
-      <c r="U18" s="108"/>
-      <c r="V18" s="109"/>
+      <c r="C18" s="103"/>
+      <c r="D18" s="103"/>
+      <c r="E18" s="103"/>
+      <c r="F18" s="103"/>
+      <c r="G18" s="103"/>
+      <c r="H18" s="103"/>
+      <c r="I18" s="103"/>
+      <c r="J18" s="103"/>
+      <c r="K18" s="103"/>
+      <c r="L18" s="103"/>
+      <c r="M18" s="103"/>
+      <c r="N18" s="103"/>
+      <c r="O18" s="103"/>
+      <c r="P18" s="103"/>
+      <c r="Q18" s="155"/>
+      <c r="R18" s="156"/>
+      <c r="S18" s="156"/>
+      <c r="T18" s="156"/>
+      <c r="U18" s="156"/>
+      <c r="V18" s="157"/>
       <c r="W18" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="X18" s="110"/>
-      <c r="Y18" s="161"/>
-      <c r="Z18" s="162"/>
-      <c r="AA18" s="161"/>
-      <c r="AB18" s="162"/>
-      <c r="AC18" s="111"/>
+      <c r="X18" s="139"/>
+      <c r="Y18" s="119"/>
+      <c r="Z18" s="116"/>
+      <c r="AA18" s="119"/>
+      <c r="AB18" s="116"/>
+      <c r="AC18" s="117"/>
       <c r="AD18" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="AE18" s="217"/>
-      <c r="AF18" s="218"/>
-      <c r="AG18" s="218"/>
-      <c r="AH18" s="218"/>
-      <c r="AI18" s="219"/>
+      <c r="AE18" s="164"/>
+      <c r="AF18" s="165"/>
+      <c r="AG18" s="165"/>
+      <c r="AH18" s="165"/>
+      <c r="AI18" s="166"/>
       <c r="AP18" s="30"/>
-    </row>
-    <row r="19" spans="1:45" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="163" t="s">
+      <c r="AT18" s="32"/>
+    </row>
+    <row r="19" spans="1:46" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="163"/>
-      <c r="D19" s="163"/>
-      <c r="E19" s="163"/>
-      <c r="F19" s="163"/>
-      <c r="G19" s="163"/>
-      <c r="H19" s="163"/>
-      <c r="I19" s="163"/>
-      <c r="J19" s="163"/>
-      <c r="K19" s="163"/>
-      <c r="L19" s="163"/>
-      <c r="M19" s="163"/>
-      <c r="N19" s="163"/>
-      <c r="O19" s="163"/>
-      <c r="P19" s="163"/>
-      <c r="Q19" s="163" t="s">
+      <c r="C19" s="84"/>
+      <c r="D19" s="84"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="84"/>
+      <c r="G19" s="84"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="84"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="84"/>
+      <c r="N19" s="84"/>
+      <c r="O19" s="84"/>
+      <c r="P19" s="84"/>
+      <c r="Q19" s="84" t="s">
         <v>12</v>
       </c>
-      <c r="R19" s="163"/>
-      <c r="S19" s="163"/>
-      <c r="T19" s="163"/>
-      <c r="U19" s="163"/>
-      <c r="V19" s="163"/>
+      <c r="R19" s="84"/>
+      <c r="S19" s="84"/>
+      <c r="T19" s="84"/>
+      <c r="U19" s="84"/>
+      <c r="V19" s="84"/>
       <c r="W19" s="3"/>
-      <c r="X19" s="165" t="s">
+      <c r="X19" s="132" t="s">
         <v>17</v>
       </c>
-      <c r="Y19" s="165"/>
-      <c r="Z19" s="165" t="s">
+      <c r="Y19" s="132"/>
+      <c r="Z19" s="132" t="s">
         <v>18</v>
       </c>
-      <c r="AA19" s="165"/>
-      <c r="AB19" s="165" t="s">
+      <c r="AA19" s="132"/>
+      <c r="AB19" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="AC19" s="165"/>
-      <c r="AE19" s="170" t="s">
+      <c r="AC19" s="132"/>
+      <c r="AE19" s="133" t="s">
         <v>13</v>
       </c>
-      <c r="AF19" s="170"/>
-      <c r="AG19" s="170"/>
-      <c r="AH19" s="170"/>
-      <c r="AI19" s="170"/>
+      <c r="AF19" s="133"/>
+      <c r="AG19" s="133"/>
+      <c r="AH19" s="133"/>
+      <c r="AI19" s="133"/>
       <c r="AJ19" s="31"/>
       <c r="AO19" s="30" t="s">
         <v>66</v>
@@ -3328,24 +3437,25 @@
       <c r="AS19" s="32" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="20" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT19" s="32"/>
+    </row>
+    <row r="20" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="160" t="s">
+      <c r="B20" s="103" t="s">
         <v>59</v>
       </c>
-      <c r="C20" s="160"/>
-      <c r="D20" s="160"/>
-      <c r="E20" s="160"/>
-      <c r="F20" s="160"/>
-      <c r="G20" s="160"/>
-      <c r="H20" s="160"/>
-      <c r="I20" s="160"/>
-      <c r="J20" s="160"/>
-      <c r="K20" s="160"/>
-      <c r="L20" s="160"/>
+      <c r="C20" s="103"/>
+      <c r="D20" s="103"/>
+      <c r="E20" s="103"/>
+      <c r="F20" s="103"/>
+      <c r="G20" s="103"/>
+      <c r="H20" s="103"/>
+      <c r="I20" s="103"/>
+      <c r="J20" s="103"/>
+      <c r="K20" s="103"/>
+      <c r="L20" s="103"/>
       <c r="M20" s="4"/>
       <c r="X20" s="12"/>
       <c r="Y20" s="12"/>
@@ -3353,11 +3463,11 @@
       <c r="AA20" s="12"/>
       <c r="AB20" s="12"/>
       <c r="AC20" s="12"/>
-      <c r="AE20" s="170"/>
-      <c r="AF20" s="170"/>
-      <c r="AG20" s="170"/>
-      <c r="AH20" s="170"/>
-      <c r="AI20" s="170"/>
+      <c r="AE20" s="133"/>
+      <c r="AF20" s="133"/>
+      <c r="AG20" s="133"/>
+      <c r="AH20" s="133"/>
+      <c r="AI20" s="133"/>
       <c r="AJ20" s="33" t="s">
         <v>63</v>
       </c>
@@ -3379,49 +3489,50 @@
       <c r="AS20" s="32" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="21" spans="1:45" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C21" s="220" t="s">
+      <c r="AT20" s="32"/>
+    </row>
+    <row r="21" spans="1:46" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C21" s="143" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="220"/>
-      <c r="E21" s="220"/>
-      <c r="F21" s="220"/>
-      <c r="G21" s="220"/>
-      <c r="H21" s="220"/>
-      <c r="J21" s="221" t="s">
+      <c r="D21" s="143"/>
+      <c r="E21" s="143"/>
+      <c r="F21" s="143"/>
+      <c r="G21" s="143"/>
+      <c r="H21" s="143"/>
+      <c r="J21" s="144" t="s">
         <v>78</v>
       </c>
-      <c r="K21" s="221"/>
-      <c r="L21" s="221"/>
-      <c r="M21" s="221"/>
-      <c r="N21" s="221" t="s">
+      <c r="K21" s="144"/>
+      <c r="L21" s="144"/>
+      <c r="M21" s="144"/>
+      <c r="N21" s="144" t="s">
         <v>97</v>
       </c>
-      <c r="O21" s="221"/>
-      <c r="P21" s="221"/>
-      <c r="Q21" s="221"/>
+      <c r="O21" s="144"/>
+      <c r="P21" s="144"/>
+      <c r="Q21" s="144"/>
       <c r="R21" s="14"/>
-      <c r="U21" s="220" t="s">
+      <c r="U21" s="143" t="s">
         <v>15</v>
       </c>
-      <c r="V21" s="220"/>
-      <c r="W21" s="220"/>
-      <c r="X21" s="220"/>
-      <c r="Y21" s="220"/>
-      <c r="Z21" s="220"/>
-      <c r="AB21" s="221" t="s">
+      <c r="V21" s="143"/>
+      <c r="W21" s="143"/>
+      <c r="X21" s="143"/>
+      <c r="Y21" s="143"/>
+      <c r="Z21" s="143"/>
+      <c r="AB21" s="144" t="s">
         <v>78</v>
       </c>
-      <c r="AC21" s="221"/>
-      <c r="AD21" s="221"/>
-      <c r="AE21" s="221"/>
-      <c r="AF21" s="221" t="s">
+      <c r="AC21" s="144"/>
+      <c r="AD21" s="144"/>
+      <c r="AE21" s="144"/>
+      <c r="AF21" s="144" t="s">
         <v>97</v>
       </c>
-      <c r="AG21" s="221"/>
-      <c r="AH21" s="221"/>
-      <c r="AI21" s="221"/>
+      <c r="AG21" s="144"/>
+      <c r="AH21" s="144"/>
+      <c r="AI21" s="144"/>
       <c r="AJ21" s="31" t="s">
         <v>61</v>
       </c>
@@ -3443,54 +3554,55 @@
       <c r="AS21" s="32" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="22" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="149" t="s">
+      <c r="AT21" s="32"/>
+    </row>
+    <row r="22" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="72" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="130"/>
-      <c r="C22" s="110"/>
-      <c r="D22" s="161"/>
-      <c r="E22" s="162"/>
-      <c r="F22" s="161"/>
-      <c r="G22" s="162"/>
-      <c r="H22" s="111"/>
-      <c r="I22" s="158" t="s">
+      <c r="B22" s="75"/>
+      <c r="C22" s="139"/>
+      <c r="D22" s="119"/>
+      <c r="E22" s="116"/>
+      <c r="F22" s="119"/>
+      <c r="G22" s="116"/>
+      <c r="H22" s="117"/>
+      <c r="I22" s="141" t="s">
         <v>98</v>
       </c>
-      <c r="J22" s="159"/>
-      <c r="K22" s="117"/>
-      <c r="L22" s="117"/>
-      <c r="M22" s="139" t="s">
+      <c r="J22" s="142"/>
+      <c r="K22" s="74"/>
+      <c r="L22" s="74"/>
+      <c r="M22" s="86" t="s">
         <v>99</v>
       </c>
-      <c r="N22" s="159"/>
-      <c r="O22" s="117"/>
-      <c r="P22" s="117"/>
+      <c r="N22" s="142"/>
+      <c r="O22" s="74"/>
+      <c r="P22" s="74"/>
       <c r="Q22" s="6"/>
       <c r="R22" s="14"/>
-      <c r="S22" s="149" t="s">
+      <c r="S22" s="72" t="s">
         <v>116</v>
       </c>
-      <c r="T22" s="130"/>
-      <c r="U22" s="110"/>
-      <c r="V22" s="161"/>
-      <c r="W22" s="162"/>
-      <c r="X22" s="161"/>
-      <c r="Y22" s="162"/>
-      <c r="Z22" s="111"/>
-      <c r="AA22" s="158" t="s">
+      <c r="T22" s="75"/>
+      <c r="U22" s="139"/>
+      <c r="V22" s="119"/>
+      <c r="W22" s="116"/>
+      <c r="X22" s="119"/>
+      <c r="Y22" s="116"/>
+      <c r="Z22" s="117"/>
+      <c r="AA22" s="141" t="s">
         <v>98</v>
       </c>
-      <c r="AB22" s="159"/>
-      <c r="AC22" s="117"/>
-      <c r="AD22" s="117"/>
-      <c r="AE22" s="139" t="s">
+      <c r="AB22" s="142"/>
+      <c r="AC22" s="74"/>
+      <c r="AD22" s="74"/>
+      <c r="AE22" s="86" t="s">
         <v>99</v>
       </c>
-      <c r="AF22" s="159"/>
-      <c r="AG22" s="117"/>
-      <c r="AH22" s="117"/>
+      <c r="AF22" s="142"/>
+      <c r="AG22" s="74"/>
+      <c r="AH22" s="74"/>
       <c r="AI22" s="6"/>
       <c r="AJ22" s="33" t="s">
         <v>62</v>
@@ -3514,37 +3626,38 @@
         <v>81</v>
       </c>
       <c r="AS22" s="32"/>
-    </row>
-    <row r="23" spans="1:45" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C23" s="163" t="s">
+      <c r="AT22" s="32"/>
+    </row>
+    <row r="23" spans="1:46" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="D23" s="163"/>
-      <c r="E23" s="163" t="s">
+      <c r="D23" s="84"/>
+      <c r="E23" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="F23" s="163"/>
-      <c r="G23" s="163" t="s">
+      <c r="F23" s="84"/>
+      <c r="G23" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="H23" s="163"/>
+      <c r="H23" s="84"/>
       <c r="L23" s="34"/>
       <c r="M23" s="5"/>
       <c r="N23" s="3"/>
       <c r="O23" s="13"/>
       <c r="R23" s="14"/>
-      <c r="U23" s="163" t="s">
+      <c r="U23" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="V23" s="163"/>
-      <c r="W23" s="163" t="s">
+      <c r="V23" s="84"/>
+      <c r="W23" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="X23" s="163"/>
-      <c r="Y23" s="163" t="s">
+      <c r="X23" s="84"/>
+      <c r="Y23" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="Z23" s="163"/>
+      <c r="Z23" s="84"/>
       <c r="AD23" s="34"/>
       <c r="AE23" s="5"/>
       <c r="AF23" s="3"/>
@@ -3574,53 +3687,54 @@
         <v>82</v>
       </c>
       <c r="AS23" s="30"/>
-    </row>
-    <row r="24" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="149" t="s">
+      <c r="AT23" s="32"/>
+    </row>
+    <row r="24" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="B24" s="130"/>
-      <c r="C24" s="110"/>
-      <c r="D24" s="161"/>
-      <c r="E24" s="162"/>
-      <c r="F24" s="161"/>
-      <c r="G24" s="162"/>
-      <c r="H24" s="111"/>
-      <c r="I24" s="158" t="s">
+      <c r="B24" s="75"/>
+      <c r="C24" s="139"/>
+      <c r="D24" s="119"/>
+      <c r="E24" s="116"/>
+      <c r="F24" s="119"/>
+      <c r="G24" s="116"/>
+      <c r="H24" s="117"/>
+      <c r="I24" s="141" t="s">
         <v>98</v>
       </c>
-      <c r="J24" s="159"/>
-      <c r="K24" s="117"/>
-      <c r="L24" s="117"/>
-      <c r="M24" s="139" t="s">
+      <c r="J24" s="142"/>
+      <c r="K24" s="74"/>
+      <c r="L24" s="74"/>
+      <c r="M24" s="86" t="s">
         <v>99</v>
       </c>
-      <c r="N24" s="159"/>
-      <c r="O24" s="117"/>
-      <c r="P24" s="117"/>
+      <c r="N24" s="142"/>
+      <c r="O24" s="74"/>
+      <c r="P24" s="74"/>
       <c r="R24" s="14"/>
-      <c r="S24" s="149" t="s">
+      <c r="S24" s="72" t="s">
         <v>117</v>
       </c>
-      <c r="T24" s="130"/>
-      <c r="U24" s="110"/>
-      <c r="V24" s="161"/>
-      <c r="W24" s="162"/>
-      <c r="X24" s="161"/>
-      <c r="Y24" s="162"/>
-      <c r="Z24" s="111"/>
-      <c r="AA24" s="158" t="s">
+      <c r="T24" s="75"/>
+      <c r="U24" s="139"/>
+      <c r="V24" s="119"/>
+      <c r="W24" s="116"/>
+      <c r="X24" s="119"/>
+      <c r="Y24" s="116"/>
+      <c r="Z24" s="117"/>
+      <c r="AA24" s="141" t="s">
         <v>98</v>
       </c>
-      <c r="AB24" s="159"/>
-      <c r="AC24" s="117"/>
-      <c r="AD24" s="117"/>
-      <c r="AE24" s="139" t="s">
+      <c r="AB24" s="142"/>
+      <c r="AC24" s="74"/>
+      <c r="AD24" s="74"/>
+      <c r="AE24" s="86" t="s">
         <v>99</v>
       </c>
-      <c r="AF24" s="159"/>
-      <c r="AG24" s="117"/>
-      <c r="AH24" s="117"/>
+      <c r="AF24" s="142"/>
+      <c r="AG24" s="74"/>
+      <c r="AH24" s="74"/>
       <c r="AJ24" s="33" t="s">
         <v>52</v>
       </c>
@@ -3643,20 +3757,21 @@
         <v>83</v>
       </c>
       <c r="AS24" s="30"/>
-    </row>
-    <row r="25" spans="1:45" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C25" s="163" t="s">
+      <c r="AT24" s="32"/>
+    </row>
+    <row r="25" spans="1:46" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="163"/>
-      <c r="E25" s="163" t="s">
+      <c r="D25" s="84"/>
+      <c r="E25" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="F25" s="163"/>
-      <c r="G25" s="163" t="s">
+      <c r="F25" s="84"/>
+      <c r="G25" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="H25" s="163"/>
+      <c r="H25" s="84"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="34"/>
@@ -3664,18 +3779,18 @@
       <c r="N25" s="3"/>
       <c r="O25" s="13"/>
       <c r="R25" s="14"/>
-      <c r="U25" s="163" t="s">
+      <c r="U25" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="V25" s="163"/>
-      <c r="W25" s="163" t="s">
+      <c r="V25" s="84"/>
+      <c r="W25" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="X25" s="163"/>
-      <c r="Y25" s="163" t="s">
+      <c r="X25" s="84"/>
+      <c r="Y25" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="Z25" s="163"/>
+      <c r="Z25" s="84"/>
       <c r="AB25" s="3"/>
       <c r="AC25" s="3"/>
       <c r="AD25" s="34"/>
@@ -3701,53 +3816,54 @@
         <v>84</v>
       </c>
       <c r="AS25" s="30"/>
-    </row>
-    <row r="26" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="149" t="s">
+      <c r="AT25" s="32"/>
+    </row>
+    <row r="26" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="72" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="130"/>
-      <c r="C26" s="110"/>
-      <c r="D26" s="161"/>
-      <c r="E26" s="162"/>
-      <c r="F26" s="161"/>
-      <c r="G26" s="162"/>
-      <c r="H26" s="111"/>
-      <c r="I26" s="158" t="s">
+      <c r="B26" s="75"/>
+      <c r="C26" s="139"/>
+      <c r="D26" s="119"/>
+      <c r="E26" s="116"/>
+      <c r="F26" s="119"/>
+      <c r="G26" s="116"/>
+      <c r="H26" s="117"/>
+      <c r="I26" s="141" t="s">
         <v>98</v>
       </c>
-      <c r="J26" s="159"/>
-      <c r="K26" s="117"/>
-      <c r="L26" s="117"/>
-      <c r="M26" s="139" t="s">
+      <c r="J26" s="142"/>
+      <c r="K26" s="74"/>
+      <c r="L26" s="74"/>
+      <c r="M26" s="86" t="s">
         <v>99</v>
       </c>
-      <c r="N26" s="159"/>
-      <c r="O26" s="117"/>
-      <c r="P26" s="117"/>
+      <c r="N26" s="142"/>
+      <c r="O26" s="74"/>
+      <c r="P26" s="74"/>
       <c r="R26" s="14"/>
-      <c r="S26" s="149" t="s">
+      <c r="S26" s="72" t="s">
         <v>118</v>
       </c>
-      <c r="T26" s="130"/>
-      <c r="U26" s="110"/>
-      <c r="V26" s="161"/>
-      <c r="W26" s="162"/>
-      <c r="X26" s="161"/>
-      <c r="Y26" s="162"/>
-      <c r="Z26" s="111"/>
-      <c r="AA26" s="158" t="s">
+      <c r="T26" s="75"/>
+      <c r="U26" s="139"/>
+      <c r="V26" s="119"/>
+      <c r="W26" s="116"/>
+      <c r="X26" s="119"/>
+      <c r="Y26" s="116"/>
+      <c r="Z26" s="117"/>
+      <c r="AA26" s="141" t="s">
         <v>98</v>
       </c>
-      <c r="AB26" s="159"/>
-      <c r="AC26" s="117"/>
-      <c r="AD26" s="117"/>
-      <c r="AE26" s="139" t="s">
+      <c r="AB26" s="142"/>
+      <c r="AC26" s="74"/>
+      <c r="AD26" s="74"/>
+      <c r="AE26" s="86" t="s">
         <v>99</v>
       </c>
-      <c r="AF26" s="159"/>
-      <c r="AG26" s="117"/>
-      <c r="AH26" s="117"/>
+      <c r="AF26" s="142"/>
+      <c r="AG26" s="74"/>
+      <c r="AH26" s="74"/>
       <c r="AJ26" s="33" t="s">
         <v>55</v>
       </c>
@@ -3764,20 +3880,21 @@
         <v>85</v>
       </c>
       <c r="AS26" s="30"/>
-    </row>
-    <row r="27" spans="1:45" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C27" s="163" t="s">
+      <c r="AT26" s="32"/>
+    </row>
+    <row r="27" spans="1:46" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C27" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="D27" s="163"/>
-      <c r="E27" s="163" t="s">
+      <c r="D27" s="84"/>
+      <c r="E27" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="F27" s="163"/>
-      <c r="G27" s="163" t="s">
+      <c r="F27" s="84"/>
+      <c r="G27" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="H27" s="163"/>
+      <c r="H27" s="84"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="34"/>
@@ -3785,18 +3902,18 @@
       <c r="N27" s="3"/>
       <c r="O27" s="13"/>
       <c r="R27" s="14"/>
-      <c r="U27" s="163" t="s">
+      <c r="U27" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="V27" s="163"/>
-      <c r="W27" s="163" t="s">
+      <c r="V27" s="84"/>
+      <c r="W27" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="X27" s="163"/>
-      <c r="Y27" s="163" t="s">
+      <c r="X27" s="84"/>
+      <c r="Y27" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="Z27" s="163"/>
+      <c r="Z27" s="84"/>
       <c r="AB27" s="3"/>
       <c r="AC27" s="3"/>
       <c r="AD27" s="34"/>
@@ -3819,53 +3936,54 @@
         <v>86</v>
       </c>
       <c r="AS27" s="30"/>
-    </row>
-    <row r="28" spans="1:45" x14ac:dyDescent="0.25">
-      <c r="A28" s="149" t="s">
+      <c r="AT27" s="32"/>
+    </row>
+    <row r="28" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A28" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="B28" s="130"/>
-      <c r="C28" s="110"/>
-      <c r="D28" s="161"/>
-      <c r="E28" s="162"/>
-      <c r="F28" s="161"/>
-      <c r="G28" s="162"/>
-      <c r="H28" s="111"/>
-      <c r="I28" s="158" t="s">
+      <c r="B28" s="75"/>
+      <c r="C28" s="139"/>
+      <c r="D28" s="119"/>
+      <c r="E28" s="116"/>
+      <c r="F28" s="119"/>
+      <c r="G28" s="116"/>
+      <c r="H28" s="117"/>
+      <c r="I28" s="141" t="s">
         <v>98</v>
       </c>
-      <c r="J28" s="159"/>
-      <c r="K28" s="117"/>
-      <c r="L28" s="117"/>
-      <c r="M28" s="139" t="s">
+      <c r="J28" s="142"/>
+      <c r="K28" s="74"/>
+      <c r="L28" s="74"/>
+      <c r="M28" s="86" t="s">
         <v>99</v>
       </c>
-      <c r="N28" s="159"/>
-      <c r="O28" s="117"/>
-      <c r="P28" s="117"/>
+      <c r="N28" s="142"/>
+      <c r="O28" s="74"/>
+      <c r="P28" s="74"/>
       <c r="R28" s="14"/>
-      <c r="S28" s="149" t="s">
+      <c r="S28" s="72" t="s">
         <v>119</v>
       </c>
-      <c r="T28" s="130"/>
-      <c r="U28" s="110"/>
-      <c r="V28" s="161"/>
-      <c r="W28" s="162"/>
-      <c r="X28" s="161"/>
-      <c r="Y28" s="162"/>
-      <c r="Z28" s="111"/>
-      <c r="AA28" s="158" t="s">
+      <c r="T28" s="75"/>
+      <c r="U28" s="139"/>
+      <c r="V28" s="119"/>
+      <c r="W28" s="116"/>
+      <c r="X28" s="119"/>
+      <c r="Y28" s="116"/>
+      <c r="Z28" s="117"/>
+      <c r="AA28" s="141" t="s">
         <v>98</v>
       </c>
-      <c r="AB28" s="159"/>
-      <c r="AC28" s="117"/>
-      <c r="AD28" s="117"/>
-      <c r="AE28" s="139" t="s">
+      <c r="AB28" s="142"/>
+      <c r="AC28" s="74"/>
+      <c r="AD28" s="74"/>
+      <c r="AE28" s="86" t="s">
         <v>99</v>
       </c>
-      <c r="AF28" s="159"/>
-      <c r="AG28" s="117"/>
-      <c r="AH28" s="117"/>
+      <c r="AF28" s="142"/>
+      <c r="AG28" s="74"/>
+      <c r="AH28" s="74"/>
       <c r="AJ28" s="33" t="s">
         <v>56</v>
       </c>
@@ -3882,20 +4000,21 @@
         <v>87</v>
       </c>
       <c r="AS28" s="30"/>
-    </row>
-    <row r="29" spans="1:45" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C29" s="163" t="s">
+      <c r="AT28" s="32"/>
+    </row>
+    <row r="29" spans="1:46" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="D29" s="163"/>
-      <c r="E29" s="163" t="s">
+      <c r="D29" s="84"/>
+      <c r="E29" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="F29" s="163"/>
-      <c r="G29" s="163" t="s">
+      <c r="F29" s="84"/>
+      <c r="G29" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="H29" s="163"/>
+      <c r="H29" s="84"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
@@ -3904,18 +4023,18 @@
       <c r="P29" s="15"/>
       <c r="Q29" s="3"/>
       <c r="R29" s="14"/>
-      <c r="U29" s="163" t="s">
+      <c r="U29" s="84" t="s">
         <v>17</v>
       </c>
-      <c r="V29" s="163"/>
-      <c r="W29" s="163" t="s">
+      <c r="V29" s="84"/>
+      <c r="W29" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="X29" s="163"/>
-      <c r="Y29" s="163" t="s">
+      <c r="X29" s="84"/>
+      <c r="Y29" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="Z29" s="163"/>
+      <c r="Z29" s="84"/>
       <c r="AB29" s="3"/>
       <c r="AC29" s="3"/>
       <c r="AD29" s="3"/>
@@ -3939,8 +4058,9 @@
         <v>88</v>
       </c>
       <c r="AS29" s="30"/>
-    </row>
-    <row r="30" spans="1:45" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AT29" s="32"/>
+    </row>
+    <row r="30" spans="1:46" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C30" s="34"/>
       <c r="D30" s="34"/>
       <c r="E30" s="34"/>
@@ -3984,27 +4104,28 @@
         <v>89</v>
       </c>
       <c r="AS30" s="30"/>
-    </row>
-    <row r="31" spans="1:45" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="85"/>
-      <c r="C31" s="85"/>
-      <c r="D31" s="85"/>
-      <c r="E31" s="85"/>
-      <c r="F31" s="85"/>
-      <c r="G31" s="85"/>
-      <c r="H31" s="85"/>
-      <c r="I31" s="85"/>
-      <c r="J31" s="85"/>
-      <c r="K31" s="85"/>
-      <c r="L31" s="85"/>
-      <c r="M31" s="85"/>
-      <c r="N31" s="85"/>
-      <c r="O31" s="85"/>
-      <c r="P31" s="85"/>
+      <c r="AT30" s="32"/>
+    </row>
+    <row r="31" spans="1:46" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="115"/>
+      <c r="C31" s="115"/>
+      <c r="D31" s="115"/>
+      <c r="E31" s="115"/>
+      <c r="F31" s="115"/>
+      <c r="G31" s="115"/>
+      <c r="H31" s="115"/>
+      <c r="I31" s="115"/>
+      <c r="J31" s="115"/>
+      <c r="K31" s="115"/>
+      <c r="L31" s="115"/>
+      <c r="M31" s="115"/>
+      <c r="N31" s="115"/>
+      <c r="O31" s="115"/>
+      <c r="P31" s="115"/>
       <c r="Q31" s="3"/>
-      <c r="R31" s="164"/>
-      <c r="S31" s="164"/>
-      <c r="T31" s="164"/>
+      <c r="R31" s="218"/>
+      <c r="S31" s="218"/>
+      <c r="T31" s="218"/>
       <c r="U31" s="34"/>
       <c r="V31" s="34"/>
       <c r="W31" s="34"/>
@@ -4030,44 +4151,45 @@
         <v>90</v>
       </c>
       <c r="AS31" s="30"/>
-    </row>
-    <row r="32" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AT31" s="32"/>
+    </row>
+    <row r="32" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B32" s="85" t="s">
+      <c r="B32" s="115" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="85"/>
-      <c r="D32" s="85"/>
-      <c r="E32" s="85"/>
-      <c r="F32" s="85"/>
-      <c r="G32" s="85"/>
-      <c r="H32" s="85"/>
-      <c r="I32" s="85"/>
-      <c r="J32" s="85"/>
-      <c r="K32" s="85"/>
-      <c r="L32" s="85"/>
-      <c r="M32" s="85"/>
-      <c r="N32" s="85"/>
-      <c r="O32" s="85"/>
-      <c r="P32" s="85"/>
-      <c r="T32" s="163"/>
-      <c r="U32" s="163"/>
-      <c r="V32" s="163"/>
-      <c r="W32" s="163"/>
-      <c r="X32" s="163"/>
-      <c r="Y32" s="163"/>
-      <c r="Z32" s="163"/>
-      <c r="AA32" s="163"/>
-      <c r="AB32" s="163"/>
-      <c r="AC32" s="163"/>
-      <c r="AD32" s="163"/>
-      <c r="AE32" s="163"/>
-      <c r="AF32" s="163"/>
-      <c r="AG32" s="163"/>
-      <c r="AH32" s="163"/>
-      <c r="AI32" s="163"/>
+      <c r="C32" s="115"/>
+      <c r="D32" s="115"/>
+      <c r="E32" s="115"/>
+      <c r="F32" s="115"/>
+      <c r="G32" s="115"/>
+      <c r="H32" s="115"/>
+      <c r="I32" s="115"/>
+      <c r="J32" s="115"/>
+      <c r="K32" s="115"/>
+      <c r="L32" s="115"/>
+      <c r="M32" s="115"/>
+      <c r="N32" s="115"/>
+      <c r="O32" s="115"/>
+      <c r="P32" s="115"/>
+      <c r="T32" s="84"/>
+      <c r="U32" s="84"/>
+      <c r="V32" s="84"/>
+      <c r="W32" s="84"/>
+      <c r="X32" s="84"/>
+      <c r="Y32" s="84"/>
+      <c r="Z32" s="84"/>
+      <c r="AA32" s="84"/>
+      <c r="AB32" s="84"/>
+      <c r="AC32" s="84"/>
+      <c r="AD32" s="84"/>
+      <c r="AE32" s="84"/>
+      <c r="AF32" s="84"/>
+      <c r="AG32" s="84"/>
+      <c r="AH32" s="84"/>
+      <c r="AI32" s="84"/>
       <c r="AJ32" s="33" t="s">
         <v>57</v>
       </c>
@@ -4078,6 +4200,7 @@
         <v>91</v>
       </c>
       <c r="AS32" s="30"/>
+      <c r="AT32" s="32"/>
     </row>
     <row r="33" spans="1:60" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="AJ33" s="33" t="s">
@@ -4094,52 +4217,53 @@
         <v>156</v>
       </c>
       <c r="AS33" s="30"/>
+      <c r="AT33" s="32"/>
     </row>
     <row r="34" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="A34" s="149" t="s">
+      <c r="A34" s="72" t="s">
         <v>129</v>
       </c>
-      <c r="B34" s="149"/>
-      <c r="C34" s="160" t="s">
+      <c r="B34" s="72"/>
+      <c r="C34" s="103" t="s">
         <v>49</v>
       </c>
-      <c r="D34" s="160"/>
-      <c r="E34" s="160"/>
-      <c r="F34" s="160"/>
-      <c r="G34" s="160"/>
-      <c r="H34" s="160"/>
-      <c r="I34" s="160"/>
-      <c r="J34" s="160"/>
-      <c r="K34" s="160" t="s">
+      <c r="D34" s="103"/>
+      <c r="E34" s="103"/>
+      <c r="F34" s="103"/>
+      <c r="G34" s="103"/>
+      <c r="H34" s="103"/>
+      <c r="I34" s="103"/>
+      <c r="J34" s="103"/>
+      <c r="K34" s="103" t="s">
         <v>130</v>
       </c>
-      <c r="L34" s="160"/>
-      <c r="M34" s="160"/>
-      <c r="N34" s="160"/>
-      <c r="O34" s="160"/>
-      <c r="P34" s="160"/>
-      <c r="Q34" s="160"/>
-      <c r="R34" s="160"/>
-      <c r="S34" s="160" t="s">
+      <c r="L34" s="103"/>
+      <c r="M34" s="103"/>
+      <c r="N34" s="103"/>
+      <c r="O34" s="103"/>
+      <c r="P34" s="103"/>
+      <c r="Q34" s="103"/>
+      <c r="R34" s="103"/>
+      <c r="S34" s="103" t="s">
         <v>131</v>
       </c>
-      <c r="T34" s="160"/>
-      <c r="U34" s="160"/>
-      <c r="V34" s="160"/>
-      <c r="W34" s="160"/>
-      <c r="X34" s="160"/>
-      <c r="Y34" s="160"/>
-      <c r="Z34" s="160"/>
-      <c r="AB34" s="174" t="s">
+      <c r="T34" s="103"/>
+      <c r="U34" s="103"/>
+      <c r="V34" s="103"/>
+      <c r="W34" s="103"/>
+      <c r="X34" s="103"/>
+      <c r="Y34" s="103"/>
+      <c r="Z34" s="103"/>
+      <c r="AB34" s="118" t="s">
         <v>132</v>
       </c>
-      <c r="AC34" s="174"/>
-      <c r="AD34" s="174"/>
-      <c r="AE34" s="174"/>
-      <c r="AF34" s="174"/>
-      <c r="AG34" s="174"/>
-      <c r="AH34" s="174"/>
-      <c r="AI34" s="174"/>
+      <c r="AC34" s="118"/>
+      <c r="AD34" s="118"/>
+      <c r="AE34" s="118"/>
+      <c r="AF34" s="118"/>
+      <c r="AG34" s="118"/>
+      <c r="AH34" s="118"/>
+      <c r="AI34" s="118"/>
       <c r="AJ34" s="66"/>
       <c r="AO34" s="30">
         <v>14</v>
@@ -4152,45 +4276,46 @@
         <v>92</v>
       </c>
       <c r="AS34" s="30"/>
+      <c r="AT34" s="32"/>
     </row>
     <row r="35" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="A35" s="149" t="s">
+      <c r="A35" s="72" t="s">
         <v>133</v>
       </c>
-      <c r="B35" s="149"/>
-      <c r="C35" s="82"/>
-      <c r="D35" s="83"/>
-      <c r="E35" s="83"/>
-      <c r="F35" s="83"/>
-      <c r="G35" s="83"/>
-      <c r="H35" s="83"/>
-      <c r="I35" s="84"/>
+      <c r="B35" s="72"/>
+      <c r="C35" s="78"/>
+      <c r="D35" s="79"/>
+      <c r="E35" s="79"/>
+      <c r="F35" s="79"/>
+      <c r="G35" s="79"/>
+      <c r="H35" s="79"/>
+      <c r="I35" s="80"/>
       <c r="J35" s="3"/>
-      <c r="K35" s="79"/>
-      <c r="L35" s="80"/>
-      <c r="M35" s="80"/>
-      <c r="N35" s="80"/>
-      <c r="O35" s="80"/>
-      <c r="P35" s="80"/>
-      <c r="Q35" s="81"/>
+      <c r="K35" s="87"/>
+      <c r="L35" s="88"/>
+      <c r="M35" s="88"/>
+      <c r="N35" s="88"/>
+      <c r="O35" s="88"/>
+      <c r="P35" s="88"/>
+      <c r="Q35" s="89"/>
       <c r="R35" s="4"/>
-      <c r="S35" s="120"/>
-      <c r="T35" s="121"/>
-      <c r="U35" s="121"/>
-      <c r="V35" s="121"/>
-      <c r="W35" s="121"/>
-      <c r="X35" s="121"/>
-      <c r="Y35" s="121"/>
-      <c r="Z35" s="122"/>
+      <c r="S35" s="90"/>
+      <c r="T35" s="91"/>
+      <c r="U35" s="91"/>
+      <c r="V35" s="91"/>
+      <c r="W35" s="91"/>
+      <c r="X35" s="91"/>
+      <c r="Y35" s="91"/>
+      <c r="Z35" s="92"/>
       <c r="AA35" s="4"/>
-      <c r="AB35" s="131"/>
-      <c r="AC35" s="132"/>
-      <c r="AD35" s="132"/>
-      <c r="AE35" s="132"/>
-      <c r="AF35" s="132"/>
-      <c r="AG35" s="132"/>
-      <c r="AH35" s="132"/>
-      <c r="AI35" s="133"/>
+      <c r="AB35" s="93"/>
+      <c r="AC35" s="94"/>
+      <c r="AD35" s="94"/>
+      <c r="AE35" s="94"/>
+      <c r="AF35" s="94"/>
+      <c r="AG35" s="94"/>
+      <c r="AH35" s="94"/>
+      <c r="AI35" s="95"/>
       <c r="AJ35" s="31"/>
       <c r="AO35" s="30">
         <v>16</v>
@@ -4221,47 +4346,47 @@
     <row r="36" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
-      <c r="C36" s="136" t="s">
+      <c r="C36" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="D36" s="136"/>
-      <c r="E36" s="136"/>
-      <c r="F36" s="136"/>
-      <c r="G36" s="136"/>
-      <c r="H36" s="136"/>
-      <c r="I36" s="136"/>
+      <c r="D36" s="85"/>
+      <c r="E36" s="85"/>
+      <c r="F36" s="85"/>
+      <c r="G36" s="85"/>
+      <c r="H36" s="85"/>
+      <c r="I36" s="85"/>
       <c r="J36" s="53"/>
-      <c r="K36" s="137" t="s">
+      <c r="K36" s="99" t="s">
         <v>50</v>
       </c>
-      <c r="L36" s="137"/>
-      <c r="M36" s="137"/>
-      <c r="N36" s="137"/>
-      <c r="O36" s="137"/>
-      <c r="P36" s="137"/>
-      <c r="Q36" s="137"/>
+      <c r="L36" s="99"/>
+      <c r="M36" s="99"/>
+      <c r="N36" s="99"/>
+      <c r="O36" s="99"/>
+      <c r="P36" s="99"/>
+      <c r="Q36" s="99"/>
       <c r="R36" s="4"/>
-      <c r="S36" s="150" t="s">
+      <c r="S36" s="101" t="s">
         <v>47</v>
       </c>
-      <c r="T36" s="150"/>
-      <c r="U36" s="144"/>
-      <c r="V36" s="145"/>
-      <c r="W36" s="151" t="s">
+      <c r="T36" s="101"/>
+      <c r="U36" s="134"/>
+      <c r="V36" s="135"/>
+      <c r="W36" s="136" t="s">
         <v>48</v>
       </c>
-      <c r="X36" s="152"/>
-      <c r="Y36" s="144"/>
-      <c r="Z36" s="145"/>
+      <c r="X36" s="137"/>
+      <c r="Y36" s="134"/>
+      <c r="Z36" s="135"/>
       <c r="AA36" s="4"/>
-      <c r="AB36" s="134"/>
-      <c r="AC36" s="105"/>
-      <c r="AD36" s="105"/>
-      <c r="AE36" s="105"/>
-      <c r="AF36" s="105"/>
-      <c r="AG36" s="105"/>
-      <c r="AH36" s="105"/>
-      <c r="AI36" s="135"/>
+      <c r="AB36" s="96"/>
+      <c r="AC36" s="97"/>
+      <c r="AD36" s="97"/>
+      <c r="AE36" s="97"/>
+      <c r="AF36" s="97"/>
+      <c r="AG36" s="97"/>
+      <c r="AH36" s="97"/>
+      <c r="AI36" s="98"/>
       <c r="AJ36" s="31" t="s">
         <v>123</v>
       </c>
@@ -4301,24 +4426,24 @@
       <c r="H37" s="46"/>
       <c r="I37" s="46"/>
       <c r="J37" s="46"/>
-      <c r="K37" s="138"/>
-      <c r="L37" s="138"/>
-      <c r="M37" s="138"/>
-      <c r="N37" s="138"/>
-      <c r="O37" s="138"/>
-      <c r="P37" s="138"/>
-      <c r="Q37" s="138"/>
+      <c r="K37" s="100"/>
+      <c r="L37" s="100"/>
+      <c r="M37" s="100"/>
+      <c r="N37" s="100"/>
+      <c r="O37" s="100"/>
+      <c r="P37" s="100"/>
+      <c r="Q37" s="100"/>
       <c r="R37" s="4"/>
-      <c r="S37" s="153" t="s">
+      <c r="S37" s="76" t="s">
         <v>124</v>
       </c>
-      <c r="T37" s="154"/>
-      <c r="U37" s="154"/>
-      <c r="V37" s="154"/>
-      <c r="W37" s="154"/>
-      <c r="X37" s="154"/>
-      <c r="Y37" s="154"/>
-      <c r="Z37" s="154"/>
+      <c r="T37" s="138"/>
+      <c r="U37" s="138"/>
+      <c r="V37" s="138"/>
+      <c r="W37" s="138"/>
+      <c r="X37" s="138"/>
+      <c r="Y37" s="138"/>
+      <c r="Z37" s="138"/>
       <c r="AA37" s="4"/>
       <c r="AB37" s="47"/>
       <c r="AC37" s="47"/>
@@ -4354,47 +4479,47 @@
       <c r="BH37" s="43"/>
     </row>
     <row r="38" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="106" t="s">
+      <c r="A38" s="168" t="s">
         <v>125</v>
       </c>
-      <c r="B38" s="155"/>
-      <c r="C38" s="112" t="s">
+      <c r="B38" s="169"/>
+      <c r="C38" s="107" t="s">
         <v>183</v>
       </c>
-      <c r="D38" s="113"/>
-      <c r="E38" s="113"/>
-      <c r="F38" s="113"/>
-      <c r="G38" s="113"/>
-      <c r="H38" s="113"/>
-      <c r="I38" s="113"/>
-      <c r="J38" s="113"/>
-      <c r="K38" s="113"/>
-      <c r="L38" s="113"/>
-      <c r="M38" s="113"/>
+      <c r="D38" s="108"/>
+      <c r="E38" s="108"/>
+      <c r="F38" s="108"/>
+      <c r="G38" s="108"/>
+      <c r="H38" s="108"/>
+      <c r="I38" s="108"/>
+      <c r="J38" s="108"/>
+      <c r="K38" s="108"/>
+      <c r="L38" s="108"/>
+      <c r="M38" s="108"/>
       <c r="N38" s="50"/>
-      <c r="O38" s="114" t="s">
+      <c r="O38" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="P38" s="115"/>
-      <c r="Q38" s="116"/>
+      <c r="P38" s="105"/>
+      <c r="Q38" s="106"/>
       <c r="R38" s="56"/>
-      <c r="S38" s="117"/>
-      <c r="T38" s="117"/>
-      <c r="U38" s="117"/>
-      <c r="V38" s="117"/>
-      <c r="W38" s="117"/>
-      <c r="X38" s="117"/>
-      <c r="Y38" s="117"/>
-      <c r="Z38" s="117"/>
+      <c r="S38" s="74"/>
+      <c r="T38" s="74"/>
+      <c r="U38" s="74"/>
+      <c r="V38" s="74"/>
+      <c r="W38" s="74"/>
+      <c r="X38" s="74"/>
+      <c r="Y38" s="74"/>
+      <c r="Z38" s="74"/>
       <c r="AA38" s="4"/>
-      <c r="AB38" s="139"/>
-      <c r="AC38" s="139"/>
-      <c r="AD38" s="139"/>
-      <c r="AE38" s="139"/>
-      <c r="AF38" s="139"/>
-      <c r="AG38" s="139"/>
-      <c r="AH38" s="139"/>
-      <c r="AI38" s="139"/>
+      <c r="AB38" s="86"/>
+      <c r="AC38" s="86"/>
+      <c r="AD38" s="86"/>
+      <c r="AE38" s="86"/>
+      <c r="AF38" s="86"/>
+      <c r="AG38" s="86"/>
+      <c r="AH38" s="86"/>
+      <c r="AI38" s="86"/>
       <c r="AJ38" s="31"/>
       <c r="AO38" s="30">
         <v>19</v>
@@ -4425,32 +4550,32 @@
     <row r="39" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="39"/>
       <c r="B39" s="39"/>
-      <c r="C39" s="113"/>
-      <c r="D39" s="113"/>
-      <c r="E39" s="113"/>
-      <c r="F39" s="113"/>
-      <c r="G39" s="113"/>
-      <c r="H39" s="113"/>
-      <c r="I39" s="113"/>
-      <c r="J39" s="113"/>
-      <c r="K39" s="113"/>
-      <c r="L39" s="113"/>
-      <c r="M39" s="113"/>
+      <c r="C39" s="108"/>
+      <c r="D39" s="108"/>
+      <c r="E39" s="108"/>
+      <c r="F39" s="108"/>
+      <c r="G39" s="108"/>
+      <c r="H39" s="108"/>
+      <c r="I39" s="108"/>
+      <c r="J39" s="108"/>
+      <c r="K39" s="108"/>
+      <c r="L39" s="108"/>
+      <c r="M39" s="108"/>
       <c r="N39" s="50"/>
       <c r="O39" s="50"/>
       <c r="P39" s="50"/>
       <c r="Q39" s="50"/>
       <c r="R39" s="51"/>
-      <c r="S39" s="118" t="s">
+      <c r="S39" s="102" t="s">
         <v>182</v>
       </c>
-      <c r="T39" s="118"/>
-      <c r="U39" s="118"/>
-      <c r="V39" s="118"/>
-      <c r="W39" s="118"/>
-      <c r="X39" s="118"/>
-      <c r="Y39" s="118"/>
-      <c r="Z39" s="118"/>
+      <c r="T39" s="102"/>
+      <c r="U39" s="102"/>
+      <c r="V39" s="102"/>
+      <c r="W39" s="102"/>
+      <c r="X39" s="102"/>
+      <c r="Y39" s="102"/>
+      <c r="Z39" s="102"/>
       <c r="AA39" s="4"/>
       <c r="AB39" s="40"/>
       <c r="AC39" s="40"/>
@@ -4464,8 +4589,8 @@
       <c r="AK39" s="17"/>
       <c r="AL39" s="17"/>
       <c r="AM39" s="17"/>
-      <c r="AN39" s="17"/>
-      <c r="AO39" s="17"/>
+      <c r="AN39" s="236"/>
+      <c r="AO39" s="236"/>
       <c r="AP39" s="30"/>
       <c r="AQ39" s="30" t="s">
         <v>144</v>
@@ -4492,45 +4617,45 @@
       <c r="BH39" s="43"/>
     </row>
     <row r="40" spans="1:60" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="130" t="s">
+      <c r="A40" s="75" t="s">
         <v>126</v>
       </c>
-      <c r="B40" s="130"/>
-      <c r="C40" s="76" t="s">
+      <c r="B40" s="75"/>
+      <c r="C40" s="109" t="s">
         <v>127</v>
       </c>
-      <c r="D40" s="77"/>
-      <c r="E40" s="77"/>
-      <c r="F40" s="77"/>
-      <c r="G40" s="77"/>
-      <c r="H40" s="77"/>
-      <c r="I40" s="77"/>
-      <c r="J40" s="77"/>
-      <c r="K40" s="77"/>
-      <c r="L40" s="77"/>
-      <c r="M40" s="77"/>
+      <c r="D40" s="110"/>
+      <c r="E40" s="110"/>
+      <c r="F40" s="110"/>
+      <c r="G40" s="110"/>
+      <c r="H40" s="110"/>
+      <c r="I40" s="110"/>
+      <c r="J40" s="110"/>
+      <c r="K40" s="110"/>
+      <c r="L40" s="110"/>
+      <c r="M40" s="110"/>
       <c r="N40" s="62"/>
-      <c r="O40" s="114" t="s">
+      <c r="O40" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="P40" s="115"/>
-      <c r="Q40" s="116"/>
-      <c r="S40" s="117"/>
-      <c r="T40" s="117"/>
-      <c r="U40" s="117"/>
-      <c r="V40" s="117"/>
-      <c r="W40" s="117"/>
-      <c r="X40" s="117"/>
-      <c r="Y40" s="117"/>
-      <c r="Z40" s="117"/>
-      <c r="AB40" s="153"/>
-      <c r="AC40" s="153"/>
-      <c r="AD40" s="153"/>
-      <c r="AE40" s="153"/>
-      <c r="AF40" s="153"/>
-      <c r="AG40" s="153"/>
-      <c r="AH40" s="153"/>
-      <c r="AI40" s="153"/>
+      <c r="P40" s="105"/>
+      <c r="Q40" s="106"/>
+      <c r="S40" s="74"/>
+      <c r="T40" s="74"/>
+      <c r="U40" s="74"/>
+      <c r="V40" s="74"/>
+      <c r="W40" s="74"/>
+      <c r="X40" s="74"/>
+      <c r="Y40" s="74"/>
+      <c r="Z40" s="74"/>
+      <c r="AB40" s="76"/>
+      <c r="AC40" s="76"/>
+      <c r="AD40" s="76"/>
+      <c r="AE40" s="76"/>
+      <c r="AF40" s="76"/>
+      <c r="AG40" s="76"/>
+      <c r="AH40" s="76"/>
+      <c r="AI40" s="76"/>
       <c r="AJ40" s="57"/>
       <c r="AK40" s="58"/>
       <c r="AL40" s="58"/>
@@ -4587,14 +4712,14 @@
       <c r="X41" s="64"/>
       <c r="Y41" s="52"/>
       <c r="Z41" s="52"/>
-      <c r="AB41" s="153"/>
-      <c r="AC41" s="153"/>
-      <c r="AD41" s="153"/>
-      <c r="AE41" s="153"/>
-      <c r="AF41" s="153"/>
-      <c r="AG41" s="153"/>
-      <c r="AH41" s="153"/>
-      <c r="AI41" s="153"/>
+      <c r="AB41" s="76"/>
+      <c r="AC41" s="76"/>
+      <c r="AD41" s="76"/>
+      <c r="AE41" s="76"/>
+      <c r="AF41" s="76"/>
+      <c r="AG41" s="76"/>
+      <c r="AH41" s="76"/>
+      <c r="AI41" s="76"/>
       <c r="AJ41" s="57"/>
       <c r="AK41" s="58"/>
       <c r="AL41" s="58"/>
@@ -4630,23 +4755,23 @@
       <c r="A42" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B42" s="85" t="s">
+      <c r="B42" s="115" t="s">
         <v>26</v>
       </c>
-      <c r="C42" s="85"/>
-      <c r="D42" s="85"/>
-      <c r="E42" s="85"/>
-      <c r="F42" s="85"/>
-      <c r="G42" s="85"/>
-      <c r="H42" s="85"/>
-      <c r="I42" s="85"/>
-      <c r="J42" s="85"/>
-      <c r="K42" s="85"/>
-      <c r="L42" s="85"/>
-      <c r="M42" s="85"/>
-      <c r="N42" s="85"/>
-      <c r="O42" s="85"/>
-      <c r="P42" s="85"/>
+      <c r="C42" s="115"/>
+      <c r="D42" s="115"/>
+      <c r="E42" s="115"/>
+      <c r="F42" s="115"/>
+      <c r="G42" s="115"/>
+      <c r="H42" s="115"/>
+      <c r="I42" s="115"/>
+      <c r="J42" s="115"/>
+      <c r="K42" s="115"/>
+      <c r="L42" s="115"/>
+      <c r="M42" s="115"/>
+      <c r="N42" s="115"/>
+      <c r="O42" s="115"/>
+      <c r="P42" s="115"/>
       <c r="AJ42" s="31"/>
       <c r="AO42" s="30">
         <v>25</v>
@@ -4677,38 +4802,38 @@
       <c r="BH42" s="43"/>
     </row>
     <row r="43" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="B43" s="86"/>
-      <c r="C43" s="87"/>
-      <c r="D43" s="87"/>
-      <c r="E43" s="87"/>
-      <c r="F43" s="87"/>
-      <c r="G43" s="87"/>
-      <c r="H43" s="87"/>
-      <c r="I43" s="87"/>
-      <c r="J43" s="87"/>
-      <c r="K43" s="87"/>
-      <c r="L43" s="87"/>
-      <c r="M43" s="87"/>
-      <c r="N43" s="87"/>
-      <c r="O43" s="88"/>
-      <c r="Q43" s="92"/>
-      <c r="R43" s="93"/>
-      <c r="S43" s="93"/>
-      <c r="T43" s="93"/>
-      <c r="U43" s="93"/>
-      <c r="V43" s="93"/>
-      <c r="W43" s="93"/>
-      <c r="X43" s="94"/>
-      <c r="Z43" s="123"/>
-      <c r="AA43" s="124"/>
-      <c r="AB43" s="124"/>
-      <c r="AC43" s="124"/>
-      <c r="AD43" s="124"/>
-      <c r="AE43" s="124"/>
-      <c r="AF43" s="124"/>
-      <c r="AG43" s="124"/>
-      <c r="AH43" s="124"/>
-      <c r="AI43" s="125"/>
+      <c r="B43" s="186"/>
+      <c r="C43" s="187"/>
+      <c r="D43" s="187"/>
+      <c r="E43" s="187"/>
+      <c r="F43" s="187"/>
+      <c r="G43" s="187"/>
+      <c r="H43" s="187"/>
+      <c r="I43" s="187"/>
+      <c r="J43" s="187"/>
+      <c r="K43" s="187"/>
+      <c r="L43" s="187"/>
+      <c r="M43" s="187"/>
+      <c r="N43" s="187"/>
+      <c r="O43" s="188"/>
+      <c r="Q43" s="194"/>
+      <c r="R43" s="195"/>
+      <c r="S43" s="195"/>
+      <c r="T43" s="195"/>
+      <c r="U43" s="195"/>
+      <c r="V43" s="195"/>
+      <c r="W43" s="195"/>
+      <c r="X43" s="196"/>
+      <c r="Z43" s="121"/>
+      <c r="AA43" s="122"/>
+      <c r="AB43" s="122"/>
+      <c r="AC43" s="122"/>
+      <c r="AD43" s="122"/>
+      <c r="AE43" s="122"/>
+      <c r="AF43" s="122"/>
+      <c r="AG43" s="122"/>
+      <c r="AH43" s="122"/>
+      <c r="AI43" s="123"/>
       <c r="AJ43" s="31"/>
       <c r="AO43" s="30">
         <v>26</v>
@@ -4724,38 +4849,38 @@
       </c>
     </row>
     <row r="44" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="B44" s="89"/>
-      <c r="C44" s="90"/>
-      <c r="D44" s="90"/>
-      <c r="E44" s="90"/>
-      <c r="F44" s="90"/>
-      <c r="G44" s="90"/>
-      <c r="H44" s="90"/>
-      <c r="I44" s="90"/>
-      <c r="J44" s="90"/>
-      <c r="K44" s="90"/>
-      <c r="L44" s="90"/>
-      <c r="M44" s="90"/>
-      <c r="N44" s="90"/>
-      <c r="O44" s="91"/>
-      <c r="Q44" s="95"/>
-      <c r="R44" s="96"/>
-      <c r="S44" s="96"/>
-      <c r="T44" s="96"/>
-      <c r="U44" s="96"/>
-      <c r="V44" s="96"/>
-      <c r="W44" s="96"/>
-      <c r="X44" s="97"/>
-      <c r="Z44" s="126"/>
-      <c r="AA44" s="127"/>
-      <c r="AB44" s="127"/>
-      <c r="AC44" s="127"/>
-      <c r="AD44" s="127"/>
-      <c r="AE44" s="127"/>
-      <c r="AF44" s="127"/>
-      <c r="AG44" s="127"/>
-      <c r="AH44" s="127"/>
-      <c r="AI44" s="128"/>
+      <c r="B44" s="189"/>
+      <c r="C44" s="190"/>
+      <c r="D44" s="190"/>
+      <c r="E44" s="190"/>
+      <c r="F44" s="190"/>
+      <c r="G44" s="190"/>
+      <c r="H44" s="190"/>
+      <c r="I44" s="190"/>
+      <c r="J44" s="190"/>
+      <c r="K44" s="190"/>
+      <c r="L44" s="190"/>
+      <c r="M44" s="190"/>
+      <c r="N44" s="190"/>
+      <c r="O44" s="191"/>
+      <c r="Q44" s="197"/>
+      <c r="R44" s="198"/>
+      <c r="S44" s="198"/>
+      <c r="T44" s="198"/>
+      <c r="U44" s="198"/>
+      <c r="V44" s="198"/>
+      <c r="W44" s="198"/>
+      <c r="X44" s="199"/>
+      <c r="Z44" s="124"/>
+      <c r="AA44" s="125"/>
+      <c r="AB44" s="125"/>
+      <c r="AC44" s="125"/>
+      <c r="AD44" s="125"/>
+      <c r="AE44" s="125"/>
+      <c r="AF44" s="125"/>
+      <c r="AG44" s="125"/>
+      <c r="AH44" s="125"/>
+      <c r="AI44" s="126"/>
       <c r="AJ44" s="31"/>
       <c r="AO44" s="30">
         <v>27</v>
@@ -4770,42 +4895,42 @@
       </c>
     </row>
     <row r="45" spans="1:60" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="163" t="s">
+      <c r="B45" s="84" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="163"/>
-      <c r="D45" s="163"/>
-      <c r="E45" s="163"/>
-      <c r="F45" s="163"/>
-      <c r="G45" s="163"/>
-      <c r="H45" s="163"/>
-      <c r="I45" s="163"/>
-      <c r="J45" s="163"/>
-      <c r="K45" s="163"/>
-      <c r="L45" s="163"/>
-      <c r="M45" s="163"/>
-      <c r="N45" s="163"/>
-      <c r="O45" s="163"/>
-      <c r="Q45" s="98"/>
-      <c r="R45" s="99"/>
-      <c r="S45" s="99"/>
-      <c r="T45" s="99"/>
-      <c r="U45" s="99"/>
-      <c r="V45" s="99"/>
-      <c r="W45" s="99"/>
-      <c r="X45" s="100"/>
-      <c r="Z45" s="163" t="s">
+      <c r="C45" s="84"/>
+      <c r="D45" s="84"/>
+      <c r="E45" s="84"/>
+      <c r="F45" s="84"/>
+      <c r="G45" s="84"/>
+      <c r="H45" s="84"/>
+      <c r="I45" s="84"/>
+      <c r="J45" s="84"/>
+      <c r="K45" s="84"/>
+      <c r="L45" s="84"/>
+      <c r="M45" s="84"/>
+      <c r="N45" s="84"/>
+      <c r="O45" s="84"/>
+      <c r="Q45" s="200"/>
+      <c r="R45" s="201"/>
+      <c r="S45" s="201"/>
+      <c r="T45" s="201"/>
+      <c r="U45" s="201"/>
+      <c r="V45" s="201"/>
+      <c r="W45" s="201"/>
+      <c r="X45" s="202"/>
+      <c r="Z45" s="84" t="s">
         <v>28</v>
       </c>
-      <c r="AA45" s="163"/>
-      <c r="AB45" s="163"/>
-      <c r="AC45" s="163"/>
-      <c r="AD45" s="163"/>
-      <c r="AE45" s="163"/>
-      <c r="AF45" s="163"/>
-      <c r="AG45" s="163"/>
-      <c r="AH45" s="163"/>
-      <c r="AI45" s="163"/>
+      <c r="AA45" s="84"/>
+      <c r="AB45" s="84"/>
+      <c r="AC45" s="84"/>
+      <c r="AD45" s="84"/>
+      <c r="AE45" s="84"/>
+      <c r="AF45" s="84"/>
+      <c r="AG45" s="84"/>
+      <c r="AH45" s="84"/>
+      <c r="AI45" s="84"/>
       <c r="AJ45" s="31"/>
       <c r="AO45" s="30">
         <v>28</v>
@@ -4824,22 +4949,22 @@
       <c r="O46" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="Q46" s="186" t="s">
+      <c r="Q46" s="120" t="s">
         <v>29</v>
       </c>
-      <c r="R46" s="186"/>
-      <c r="S46" s="186"/>
-      <c r="T46" s="186"/>
-      <c r="U46" s="186"/>
-      <c r="V46" s="186"/>
-      <c r="W46" s="186"/>
-      <c r="X46" s="186"/>
+      <c r="R46" s="120"/>
+      <c r="S46" s="120"/>
+      <c r="T46" s="120"/>
+      <c r="U46" s="120"/>
+      <c r="V46" s="120"/>
+      <c r="W46" s="120"/>
+      <c r="X46" s="120"/>
       <c r="AJ46" s="31"/>
       <c r="AO46" s="30">
         <v>29</v>
       </c>
       <c r="AP46" s="30"/>
-      <c r="AQ46" s="29" t="s">
+      <c r="AQ46" s="30" t="s">
         <v>151</v>
       </c>
       <c r="AR46" s="30"/>
@@ -4870,33 +4995,33 @@
       <c r="P47" s="18"/>
       <c r="Q47" s="18"/>
       <c r="R47" s="18"/>
-      <c r="S47" s="166"/>
-      <c r="T47" s="167"/>
-      <c r="U47" s="167"/>
-      <c r="V47" s="168"/>
+      <c r="S47" s="129"/>
+      <c r="T47" s="130"/>
+      <c r="U47" s="130"/>
+      <c r="V47" s="131"/>
       <c r="W47" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="X47" s="110"/>
-      <c r="Y47" s="161"/>
-      <c r="Z47" s="162"/>
-      <c r="AA47" s="161"/>
-      <c r="AB47" s="168"/>
-      <c r="AC47" s="169"/>
+      <c r="X47" s="139"/>
+      <c r="Y47" s="119"/>
+      <c r="Z47" s="116"/>
+      <c r="AA47" s="119"/>
+      <c r="AB47" s="131"/>
+      <c r="AC47" s="215"/>
       <c r="AD47" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="AE47" s="166"/>
-      <c r="AF47" s="167"/>
-      <c r="AG47" s="167"/>
-      <c r="AH47" s="167"/>
-      <c r="AI47" s="168"/>
+      <c r="AE47" s="129"/>
+      <c r="AF47" s="130"/>
+      <c r="AG47" s="130"/>
+      <c r="AH47" s="130"/>
+      <c r="AI47" s="131"/>
       <c r="AJ47" s="31"/>
       <c r="AO47" s="30">
         <v>30</v>
       </c>
       <c r="AP47" s="30"/>
-      <c r="AQ47" s="29" t="s">
+      <c r="AQ47" s="237" t="s">
         <v>120</v>
       </c>
       <c r="AR47" s="30"/>
@@ -4906,37 +5031,37 @@
       </c>
     </row>
     <row r="48" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="S48" s="165" t="s">
+      <c r="S48" s="132" t="s">
         <v>12</v>
       </c>
-      <c r="T48" s="165"/>
-      <c r="U48" s="165"/>
-      <c r="V48" s="165"/>
-      <c r="X48" s="165" t="s">
+      <c r="T48" s="132"/>
+      <c r="U48" s="132"/>
+      <c r="V48" s="132"/>
+      <c r="X48" s="132" t="s">
         <v>17</v>
       </c>
-      <c r="Y48" s="165"/>
-      <c r="Z48" s="165" t="s">
+      <c r="Y48" s="132"/>
+      <c r="Z48" s="132" t="s">
         <v>18</v>
       </c>
-      <c r="AA48" s="165"/>
-      <c r="AB48" s="165" t="s">
+      <c r="AA48" s="132"/>
+      <c r="AB48" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="AC48" s="165"/>
-      <c r="AE48" s="170" t="s">
+      <c r="AC48" s="132"/>
+      <c r="AE48" s="133" t="s">
         <v>13</v>
       </c>
-      <c r="AF48" s="170"/>
-      <c r="AG48" s="170"/>
-      <c r="AH48" s="170"/>
-      <c r="AI48" s="170"/>
+      <c r="AF48" s="133"/>
+      <c r="AG48" s="133"/>
+      <c r="AH48" s="133"/>
+      <c r="AI48" s="133"/>
       <c r="AJ48" s="31"/>
       <c r="AO48" s="30">
         <v>31</v>
       </c>
       <c r="AP48" s="30"/>
-      <c r="AQ48" s="29" t="s">
+      <c r="AQ48" s="237" t="s">
         <v>121</v>
       </c>
       <c r="AS48" s="30"/>
@@ -4962,25 +5087,25 @@
       <c r="P49" s="6"/>
       <c r="Q49" s="6"/>
       <c r="R49" s="6"/>
-      <c r="S49" s="170"/>
-      <c r="T49" s="170"/>
-      <c r="U49" s="170"/>
-      <c r="V49" s="170"/>
+      <c r="S49" s="133"/>
+      <c r="T49" s="133"/>
+      <c r="U49" s="133"/>
+      <c r="V49" s="133"/>
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
       <c r="AA49" s="3"/>
       <c r="AB49" s="3"/>
       <c r="AC49" s="3"/>
       <c r="AD49" s="17"/>
-      <c r="AE49" s="170"/>
-      <c r="AF49" s="170"/>
-      <c r="AG49" s="170"/>
-      <c r="AH49" s="170"/>
-      <c r="AI49" s="170"/>
+      <c r="AE49" s="133"/>
+      <c r="AF49" s="133"/>
+      <c r="AG49" s="133"/>
+      <c r="AH49" s="133"/>
+      <c r="AI49" s="133"/>
       <c r="AJ49" s="31"/>
       <c r="AO49" s="30"/>
       <c r="AP49" s="30"/>
-      <c r="AQ49" s="29" t="s">
+      <c r="AQ49" s="237" t="s">
         <v>122</v>
       </c>
       <c r="AS49" s="30"/>
@@ -4992,19 +5117,19 @@
       <c r="A50" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B50" s="85" t="s">
+      <c r="B50" s="115" t="s">
         <v>31</v>
       </c>
-      <c r="C50" s="85"/>
-      <c r="D50" s="85"/>
-      <c r="E50" s="85"/>
-      <c r="F50" s="85"/>
-      <c r="G50" s="85"/>
-      <c r="H50" s="85"/>
-      <c r="I50" s="85"/>
-      <c r="J50" s="85"/>
-      <c r="K50" s="85"/>
-      <c r="L50" s="85"/>
+      <c r="C50" s="115"/>
+      <c r="D50" s="115"/>
+      <c r="E50" s="115"/>
+      <c r="F50" s="115"/>
+      <c r="G50" s="115"/>
+      <c r="H50" s="115"/>
+      <c r="I50" s="115"/>
+      <c r="J50" s="115"/>
+      <c r="K50" s="115"/>
+      <c r="L50" s="115"/>
       <c r="Z50" s="3"/>
       <c r="AA50" s="3"/>
       <c r="AB50" s="3"/>
@@ -5017,7 +5142,7 @@
       <c r="AJ50" s="31"/>
       <c r="AO50" s="30"/>
       <c r="AP50" s="30"/>
-      <c r="AQ50" s="29" t="s">
+      <c r="AQ50" s="237" t="s">
         <v>189</v>
       </c>
       <c r="AR50" s="30"/>
@@ -5040,10 +5165,10 @@
       </c>
     </row>
     <row r="52" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A52" s="149" t="s">
+      <c r="A52" s="72" t="s">
         <v>180</v>
       </c>
-      <c r="B52" s="149"/>
+      <c r="B52" s="72"/>
       <c r="C52" s="41" t="s">
         <v>32</v>
       </c>
@@ -5074,20 +5199,20 @@
       </c>
       <c r="S52" s="25"/>
       <c r="T52" s="27"/>
-      <c r="X52" s="149" t="s">
+      <c r="X52" s="72" t="s">
         <v>181</v>
       </c>
-      <c r="Y52" s="130"/>
-      <c r="Z52" s="123"/>
-      <c r="AA52" s="124"/>
-      <c r="AB52" s="124"/>
-      <c r="AC52" s="124"/>
-      <c r="AD52" s="124"/>
-      <c r="AE52" s="124"/>
-      <c r="AF52" s="124"/>
-      <c r="AG52" s="124"/>
-      <c r="AH52" s="124"/>
-      <c r="AI52" s="125"/>
+      <c r="Y52" s="75"/>
+      <c r="Z52" s="121"/>
+      <c r="AA52" s="122"/>
+      <c r="AB52" s="122"/>
+      <c r="AC52" s="122"/>
+      <c r="AD52" s="122"/>
+      <c r="AE52" s="122"/>
+      <c r="AF52" s="122"/>
+      <c r="AG52" s="122"/>
+      <c r="AH52" s="122"/>
+      <c r="AI52" s="123"/>
       <c r="AJ52" s="31"/>
       <c r="AO52" s="30"/>
       <c r="AP52" s="30"/>
@@ -5102,32 +5227,32 @@
     </row>
     <row r="53" spans="1:46" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G53" s="3"/>
-      <c r="H53" s="228" t="s">
+      <c r="H53" s="128" t="s">
         <v>36</v>
       </c>
-      <c r="I53" s="228"/>
-      <c r="J53" s="228"/>
-      <c r="L53" s="163" t="s">
+      <c r="I53" s="128"/>
+      <c r="J53" s="128"/>
+      <c r="L53" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="M53" s="163"/>
-      <c r="N53" s="163"/>
-      <c r="O53" s="163"/>
-      <c r="P53" s="163"/>
-      <c r="Q53" s="163"/>
-      <c r="R53" s="163"/>
-      <c r="S53" s="163"/>
-      <c r="T53" s="163"/>
-      <c r="Z53" s="126"/>
-      <c r="AA53" s="127"/>
-      <c r="AB53" s="127"/>
-      <c r="AC53" s="127"/>
-      <c r="AD53" s="127"/>
-      <c r="AE53" s="127"/>
-      <c r="AF53" s="127"/>
-      <c r="AG53" s="127"/>
-      <c r="AH53" s="127"/>
-      <c r="AI53" s="128"/>
+      <c r="M53" s="84"/>
+      <c r="N53" s="84"/>
+      <c r="O53" s="84"/>
+      <c r="P53" s="84"/>
+      <c r="Q53" s="84"/>
+      <c r="R53" s="84"/>
+      <c r="S53" s="84"/>
+      <c r="T53" s="84"/>
+      <c r="Z53" s="124"/>
+      <c r="AA53" s="125"/>
+      <c r="AB53" s="125"/>
+      <c r="AC53" s="125"/>
+      <c r="AD53" s="125"/>
+      <c r="AE53" s="125"/>
+      <c r="AF53" s="125"/>
+      <c r="AG53" s="125"/>
+      <c r="AH53" s="125"/>
+      <c r="AI53" s="126"/>
       <c r="AJ53" s="31"/>
       <c r="AO53" s="30"/>
       <c r="AP53" s="30"/>
@@ -5141,11 +5266,11 @@
       </c>
     </row>
     <row r="54" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="C54" s="85" t="s">
+      <c r="C54" s="115" t="s">
         <v>32</v>
       </c>
-      <c r="D54" s="85"/>
-      <c r="E54" s="85"/>
+      <c r="D54" s="115"/>
+      <c r="E54" s="115"/>
       <c r="F54" s="55">
         <v>8</v>
       </c>
@@ -5171,22 +5296,24 @@
       </c>
       <c r="S54" s="25"/>
       <c r="T54" s="27"/>
-      <c r="Z54" s="227" t="s">
+      <c r="Z54" s="127" t="s">
         <v>28</v>
       </c>
-      <c r="AA54" s="227"/>
-      <c r="AB54" s="227"/>
-      <c r="AC54" s="227"/>
-      <c r="AD54" s="227"/>
-      <c r="AE54" s="227"/>
-      <c r="AF54" s="227"/>
-      <c r="AG54" s="227"/>
-      <c r="AH54" s="227"/>
-      <c r="AI54" s="227"/>
+      <c r="AA54" s="127"/>
+      <c r="AB54" s="127"/>
+      <c r="AC54" s="127"/>
+      <c r="AD54" s="127"/>
+      <c r="AE54" s="127"/>
+      <c r="AF54" s="127"/>
+      <c r="AG54" s="127"/>
+      <c r="AH54" s="127"/>
+      <c r="AI54" s="127"/>
       <c r="AJ54" s="31"/>
       <c r="AO54" s="30"/>
       <c r="AP54" s="30"/>
-      <c r="AQ54" s="30"/>
+      <c r="AQ54" s="30" t="s">
+        <v>194</v>
+      </c>
       <c r="AR54" s="30"/>
       <c r="AS54" s="30"/>
       <c r="AT54" s="29" t="s">
@@ -5195,26 +5322,28 @@
     </row>
     <row r="55" spans="1:46" x14ac:dyDescent="0.25">
       <c r="G55" s="3"/>
-      <c r="H55" s="129" t="s">
+      <c r="H55" s="154" t="s">
         <v>36</v>
       </c>
-      <c r="I55" s="129"/>
-      <c r="J55" s="129"/>
-      <c r="L55" s="163" t="s">
+      <c r="I55" s="154"/>
+      <c r="J55" s="154"/>
+      <c r="L55" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="M55" s="163"/>
-      <c r="N55" s="163"/>
-      <c r="O55" s="163"/>
-      <c r="P55" s="163"/>
-      <c r="Q55" s="163"/>
-      <c r="R55" s="163"/>
-      <c r="S55" s="163"/>
-      <c r="T55" s="163"/>
+      <c r="M55" s="84"/>
+      <c r="N55" s="84"/>
+      <c r="O55" s="84"/>
+      <c r="P55" s="84"/>
+      <c r="Q55" s="84"/>
+      <c r="R55" s="84"/>
+      <c r="S55" s="84"/>
+      <c r="T55" s="84"/>
       <c r="AJ55" s="31"/>
       <c r="AO55" s="30"/>
       <c r="AP55" s="30"/>
-      <c r="AQ55" s="30"/>
+      <c r="AQ55" s="30" t="s">
+        <v>195</v>
+      </c>
       <c r="AR55" s="30"/>
       <c r="AS55" s="30"/>
       <c r="AT55" s="29" t="s">
@@ -5222,43 +5351,43 @@
       </c>
     </row>
     <row r="56" spans="1:46" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="225" t="s">
+      <c r="A56" s="113" t="s">
         <v>58</v>
       </c>
-      <c r="B56" s="225"/>
-      <c r="C56" s="225"/>
-      <c r="D56" s="225"/>
-      <c r="E56" s="225"/>
-      <c r="F56" s="225"/>
-      <c r="G56" s="225"/>
-      <c r="H56" s="225"/>
-      <c r="I56" s="225"/>
-      <c r="J56" s="225"/>
-      <c r="K56" s="225"/>
-      <c r="L56" s="225"/>
-      <c r="M56" s="225"/>
-      <c r="N56" s="225"/>
-      <c r="O56" s="225"/>
-      <c r="P56" s="225"/>
-      <c r="Q56" s="225"/>
-      <c r="R56" s="225"/>
-      <c r="S56" s="225"/>
-      <c r="T56" s="225"/>
-      <c r="U56" s="225"/>
-      <c r="V56" s="225"/>
-      <c r="W56" s="225"/>
-      <c r="X56" s="225"/>
-      <c r="Y56" s="225"/>
-      <c r="Z56" s="225"/>
-      <c r="AA56" s="225"/>
-      <c r="AB56" s="225"/>
-      <c r="AC56" s="225"/>
-      <c r="AD56" s="225"/>
-      <c r="AE56" s="225"/>
-      <c r="AF56" s="225"/>
-      <c r="AG56" s="225"/>
-      <c r="AH56" s="225"/>
-      <c r="AI56" s="225"/>
+      <c r="B56" s="113"/>
+      <c r="C56" s="113"/>
+      <c r="D56" s="113"/>
+      <c r="E56" s="113"/>
+      <c r="F56" s="113"/>
+      <c r="G56" s="113"/>
+      <c r="H56" s="113"/>
+      <c r="I56" s="113"/>
+      <c r="J56" s="113"/>
+      <c r="K56" s="113"/>
+      <c r="L56" s="113"/>
+      <c r="M56" s="113"/>
+      <c r="N56" s="113"/>
+      <c r="O56" s="113"/>
+      <c r="P56" s="113"/>
+      <c r="Q56" s="113"/>
+      <c r="R56" s="113"/>
+      <c r="S56" s="113"/>
+      <c r="T56" s="113"/>
+      <c r="U56" s="113"/>
+      <c r="V56" s="113"/>
+      <c r="W56" s="113"/>
+      <c r="X56" s="113"/>
+      <c r="Y56" s="113"/>
+      <c r="Z56" s="113"/>
+      <c r="AA56" s="113"/>
+      <c r="AB56" s="113"/>
+      <c r="AC56" s="113"/>
+      <c r="AD56" s="113"/>
+      <c r="AE56" s="113"/>
+      <c r="AF56" s="113"/>
+      <c r="AG56" s="113"/>
+      <c r="AH56" s="113"/>
+      <c r="AI56" s="113"/>
       <c r="AJ56" s="31"/>
       <c r="AO56" s="30"/>
       <c r="AP56" s="30"/>
@@ -5270,41 +5399,41 @@
       </c>
     </row>
     <row r="57" spans="1:46" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="226"/>
-      <c r="B57" s="226"/>
-      <c r="C57" s="226"/>
-      <c r="D57" s="226"/>
-      <c r="E57" s="226"/>
-      <c r="F57" s="226"/>
-      <c r="G57" s="226"/>
-      <c r="H57" s="226"/>
-      <c r="I57" s="226"/>
-      <c r="J57" s="226"/>
-      <c r="K57" s="226"/>
-      <c r="L57" s="226"/>
-      <c r="M57" s="226"/>
-      <c r="N57" s="226"/>
-      <c r="O57" s="226"/>
-      <c r="P57" s="226"/>
-      <c r="Q57" s="226"/>
-      <c r="R57" s="226"/>
-      <c r="S57" s="226"/>
-      <c r="T57" s="226"/>
-      <c r="U57" s="226"/>
-      <c r="V57" s="226"/>
-      <c r="W57" s="226"/>
-      <c r="X57" s="226"/>
-      <c r="Y57" s="226"/>
-      <c r="Z57" s="226"/>
-      <c r="AA57" s="226"/>
-      <c r="AB57" s="226"/>
-      <c r="AC57" s="226"/>
-      <c r="AD57" s="226"/>
-      <c r="AE57" s="226"/>
-      <c r="AF57" s="226"/>
-      <c r="AG57" s="226"/>
-      <c r="AH57" s="226"/>
-      <c r="AI57" s="226"/>
+      <c r="A57" s="114"/>
+      <c r="B57" s="114"/>
+      <c r="C57" s="114"/>
+      <c r="D57" s="114"/>
+      <c r="E57" s="114"/>
+      <c r="F57" s="114"/>
+      <c r="G57" s="114"/>
+      <c r="H57" s="114"/>
+      <c r="I57" s="114"/>
+      <c r="J57" s="114"/>
+      <c r="K57" s="114"/>
+      <c r="L57" s="114"/>
+      <c r="M57" s="114"/>
+      <c r="N57" s="114"/>
+      <c r="O57" s="114"/>
+      <c r="P57" s="114"/>
+      <c r="Q57" s="114"/>
+      <c r="R57" s="114"/>
+      <c r="S57" s="114"/>
+      <c r="T57" s="114"/>
+      <c r="U57" s="114"/>
+      <c r="V57" s="114"/>
+      <c r="W57" s="114"/>
+      <c r="X57" s="114"/>
+      <c r="Y57" s="114"/>
+      <c r="Z57" s="114"/>
+      <c r="AA57" s="114"/>
+      <c r="AB57" s="114"/>
+      <c r="AC57" s="114"/>
+      <c r="AD57" s="114"/>
+      <c r="AE57" s="114"/>
+      <c r="AF57" s="114"/>
+      <c r="AG57" s="114"/>
+      <c r="AH57" s="114"/>
+      <c r="AI57" s="114"/>
       <c r="AJ57" s="31"/>
       <c r="AO57" s="30"/>
       <c r="AP57" s="30"/>
@@ -5316,43 +5445,43 @@
       </c>
     </row>
     <row r="58" spans="1:46" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="171" t="s">
+      <c r="A58" s="206" t="s">
         <v>101</v>
       </c>
-      <c r="B58" s="172"/>
-      <c r="C58" s="172"/>
-      <c r="D58" s="172"/>
-      <c r="E58" s="172"/>
-      <c r="F58" s="172"/>
-      <c r="G58" s="172"/>
-      <c r="H58" s="172"/>
-      <c r="I58" s="172"/>
-      <c r="J58" s="172"/>
-      <c r="K58" s="172"/>
-      <c r="L58" s="172"/>
-      <c r="M58" s="172"/>
-      <c r="N58" s="172"/>
-      <c r="O58" s="172"/>
-      <c r="P58" s="172"/>
-      <c r="Q58" s="172"/>
-      <c r="R58" s="172"/>
-      <c r="S58" s="172"/>
-      <c r="T58" s="172"/>
-      <c r="U58" s="172"/>
-      <c r="V58" s="172"/>
-      <c r="W58" s="172"/>
-      <c r="X58" s="172"/>
-      <c r="Y58" s="172"/>
-      <c r="Z58" s="172"/>
-      <c r="AA58" s="172"/>
-      <c r="AB58" s="172"/>
-      <c r="AC58" s="172"/>
-      <c r="AD58" s="172"/>
-      <c r="AE58" s="172"/>
-      <c r="AF58" s="172"/>
-      <c r="AG58" s="172"/>
-      <c r="AH58" s="172"/>
-      <c r="AI58" s="172"/>
+      <c r="B58" s="207"/>
+      <c r="C58" s="207"/>
+      <c r="D58" s="207"/>
+      <c r="E58" s="207"/>
+      <c r="F58" s="207"/>
+      <c r="G58" s="207"/>
+      <c r="H58" s="207"/>
+      <c r="I58" s="207"/>
+      <c r="J58" s="207"/>
+      <c r="K58" s="207"/>
+      <c r="L58" s="207"/>
+      <c r="M58" s="207"/>
+      <c r="N58" s="207"/>
+      <c r="O58" s="207"/>
+      <c r="P58" s="207"/>
+      <c r="Q58" s="207"/>
+      <c r="R58" s="207"/>
+      <c r="S58" s="207"/>
+      <c r="T58" s="207"/>
+      <c r="U58" s="207"/>
+      <c r="V58" s="207"/>
+      <c r="W58" s="207"/>
+      <c r="X58" s="207"/>
+      <c r="Y58" s="207"/>
+      <c r="Z58" s="207"/>
+      <c r="AA58" s="207"/>
+      <c r="AB58" s="207"/>
+      <c r="AC58" s="207"/>
+      <c r="AD58" s="207"/>
+      <c r="AE58" s="207"/>
+      <c r="AF58" s="207"/>
+      <c r="AG58" s="207"/>
+      <c r="AH58" s="207"/>
+      <c r="AI58" s="207"/>
       <c r="AJ58" s="31"/>
       <c r="AO58" s="30"/>
       <c r="AP58" s="30"/>
@@ -5364,41 +5493,41 @@
       </c>
     </row>
     <row r="59" spans="1:46" x14ac:dyDescent="0.25">
-      <c r="A59" s="173"/>
-      <c r="B59" s="173"/>
-      <c r="C59" s="173"/>
-      <c r="D59" s="173"/>
-      <c r="E59" s="173"/>
-      <c r="F59" s="173"/>
-      <c r="G59" s="173"/>
-      <c r="H59" s="173"/>
-      <c r="I59" s="173"/>
-      <c r="J59" s="173"/>
-      <c r="K59" s="173"/>
-      <c r="L59" s="173"/>
-      <c r="M59" s="173"/>
-      <c r="N59" s="173"/>
-      <c r="O59" s="173"/>
-      <c r="P59" s="173"/>
-      <c r="Q59" s="173"/>
-      <c r="R59" s="173"/>
-      <c r="S59" s="173"/>
-      <c r="T59" s="173"/>
-      <c r="U59" s="173"/>
-      <c r="V59" s="173"/>
-      <c r="W59" s="173"/>
-      <c r="X59" s="173"/>
-      <c r="Y59" s="173"/>
-      <c r="Z59" s="173"/>
-      <c r="AA59" s="173"/>
-      <c r="AB59" s="173"/>
-      <c r="AC59" s="173"/>
-      <c r="AD59" s="173"/>
-      <c r="AE59" s="173"/>
-      <c r="AF59" s="173"/>
-      <c r="AG59" s="173"/>
-      <c r="AH59" s="173"/>
-      <c r="AI59" s="173"/>
+      <c r="A59" s="208"/>
+      <c r="B59" s="208"/>
+      <c r="C59" s="208"/>
+      <c r="D59" s="208"/>
+      <c r="E59" s="208"/>
+      <c r="F59" s="208"/>
+      <c r="G59" s="208"/>
+      <c r="H59" s="208"/>
+      <c r="I59" s="208"/>
+      <c r="J59" s="208"/>
+      <c r="K59" s="208"/>
+      <c r="L59" s="208"/>
+      <c r="M59" s="208"/>
+      <c r="N59" s="208"/>
+      <c r="O59" s="208"/>
+      <c r="P59" s="208"/>
+      <c r="Q59" s="208"/>
+      <c r="R59" s="208"/>
+      <c r="S59" s="208"/>
+      <c r="T59" s="208"/>
+      <c r="U59" s="208"/>
+      <c r="V59" s="208"/>
+      <c r="W59" s="208"/>
+      <c r="X59" s="208"/>
+      <c r="Y59" s="208"/>
+      <c r="Z59" s="208"/>
+      <c r="AA59" s="208"/>
+      <c r="AB59" s="208"/>
+      <c r="AC59" s="208"/>
+      <c r="AD59" s="208"/>
+      <c r="AE59" s="208"/>
+      <c r="AF59" s="208"/>
+      <c r="AG59" s="208"/>
+      <c r="AH59" s="208"/>
+      <c r="AI59" s="208"/>
       <c r="AJ59" s="31"/>
       <c r="AO59" s="30"/>
       <c r="AP59" s="30"/>
@@ -5421,43 +5550,43 @@
       </c>
     </row>
     <row r="61" spans="1:46" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A61" s="188" t="s">
+      <c r="A61" s="203" t="s">
         <v>114</v>
       </c>
-      <c r="B61" s="188"/>
-      <c r="C61" s="188"/>
-      <c r="D61" s="188"/>
-      <c r="E61" s="188"/>
-      <c r="F61" s="188"/>
-      <c r="G61" s="188"/>
-      <c r="H61" s="188"/>
-      <c r="I61" s="188"/>
-      <c r="J61" s="188"/>
-      <c r="K61" s="188"/>
-      <c r="L61" s="188"/>
-      <c r="M61" s="188"/>
-      <c r="N61" s="188"/>
-      <c r="O61" s="188"/>
-      <c r="P61" s="188"/>
-      <c r="Q61" s="188"/>
-      <c r="R61" s="188"/>
-      <c r="S61" s="188"/>
-      <c r="T61" s="188"/>
-      <c r="U61" s="188"/>
-      <c r="V61" s="188"/>
-      <c r="W61" s="188"/>
-      <c r="X61" s="188"/>
-      <c r="Y61" s="188"/>
-      <c r="Z61" s="188"/>
-      <c r="AA61" s="188"/>
-      <c r="AB61" s="188"/>
-      <c r="AC61" s="188"/>
-      <c r="AD61" s="188"/>
-      <c r="AE61" s="188"/>
-      <c r="AF61" s="188"/>
-      <c r="AG61" s="188"/>
-      <c r="AH61" s="188"/>
-      <c r="AI61" s="188"/>
+      <c r="B61" s="203"/>
+      <c r="C61" s="203"/>
+      <c r="D61" s="203"/>
+      <c r="E61" s="203"/>
+      <c r="F61" s="203"/>
+      <c r="G61" s="203"/>
+      <c r="H61" s="203"/>
+      <c r="I61" s="203"/>
+      <c r="J61" s="203"/>
+      <c r="K61" s="203"/>
+      <c r="L61" s="203"/>
+      <c r="M61" s="203"/>
+      <c r="N61" s="203"/>
+      <c r="O61" s="203"/>
+      <c r="P61" s="203"/>
+      <c r="Q61" s="203"/>
+      <c r="R61" s="203"/>
+      <c r="S61" s="203"/>
+      <c r="T61" s="203"/>
+      <c r="U61" s="203"/>
+      <c r="V61" s="203"/>
+      <c r="W61" s="203"/>
+      <c r="X61" s="203"/>
+      <c r="Y61" s="203"/>
+      <c r="Z61" s="203"/>
+      <c r="AA61" s="203"/>
+      <c r="AB61" s="203"/>
+      <c r="AC61" s="203"/>
+      <c r="AD61" s="203"/>
+      <c r="AE61" s="203"/>
+      <c r="AF61" s="203"/>
+      <c r="AG61" s="203"/>
+      <c r="AH61" s="203"/>
+      <c r="AI61" s="203"/>
       <c r="AJ61" s="31"/>
       <c r="AO61" s="30"/>
       <c r="AP61" s="30"/>
@@ -5514,84 +5643,84 @@
       </c>
     </row>
     <row r="63" spans="1:46" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="189" t="s">
+      <c r="A63" s="204" t="s">
         <v>188</v>
       </c>
-      <c r="B63" s="189"/>
-      <c r="C63" s="189"/>
-      <c r="D63" s="189"/>
-      <c r="E63" s="189"/>
-      <c r="F63" s="189"/>
-      <c r="G63" s="189"/>
-      <c r="H63" s="189"/>
-      <c r="I63" s="189"/>
-      <c r="J63" s="189"/>
-      <c r="K63" s="189"/>
-      <c r="L63" s="189"/>
-      <c r="M63" s="189"/>
-      <c r="N63" s="189"/>
-      <c r="O63" s="189"/>
-      <c r="P63" s="189"/>
-      <c r="Q63" s="189"/>
-      <c r="R63" s="189"/>
-      <c r="S63" s="189"/>
-      <c r="T63" s="189"/>
-      <c r="U63" s="189"/>
-      <c r="V63" s="189"/>
-      <c r="W63" s="189"/>
-      <c r="X63" s="189"/>
-      <c r="Y63" s="189"/>
-      <c r="Z63" s="189"/>
-      <c r="AA63" s="189"/>
-      <c r="AB63" s="189"/>
-      <c r="AC63" s="189"/>
-      <c r="AD63" s="189"/>
-      <c r="AE63" s="189"/>
-      <c r="AF63" s="189"/>
-      <c r="AG63" s="189"/>
-      <c r="AH63" s="189"/>
-      <c r="AI63" s="189"/>
+      <c r="B63" s="204"/>
+      <c r="C63" s="204"/>
+      <c r="D63" s="204"/>
+      <c r="E63" s="204"/>
+      <c r="F63" s="204"/>
+      <c r="G63" s="204"/>
+      <c r="H63" s="204"/>
+      <c r="I63" s="204"/>
+      <c r="J63" s="204"/>
+      <c r="K63" s="204"/>
+      <c r="L63" s="204"/>
+      <c r="M63" s="204"/>
+      <c r="N63" s="204"/>
+      <c r="O63" s="204"/>
+      <c r="P63" s="204"/>
+      <c r="Q63" s="204"/>
+      <c r="R63" s="204"/>
+      <c r="S63" s="204"/>
+      <c r="T63" s="204"/>
+      <c r="U63" s="204"/>
+      <c r="V63" s="204"/>
+      <c r="W63" s="204"/>
+      <c r="X63" s="204"/>
+      <c r="Y63" s="204"/>
+      <c r="Z63" s="204"/>
+      <c r="AA63" s="204"/>
+      <c r="AB63" s="204"/>
+      <c r="AC63" s="204"/>
+      <c r="AD63" s="204"/>
+      <c r="AE63" s="204"/>
+      <c r="AF63" s="204"/>
+      <c r="AG63" s="204"/>
+      <c r="AH63" s="204"/>
+      <c r="AI63" s="204"/>
       <c r="AS63" s="30"/>
       <c r="AT63" s="29" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="64" spans="1:46" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="190"/>
-      <c r="B64" s="190"/>
-      <c r="C64" s="190"/>
-      <c r="D64" s="190"/>
-      <c r="E64" s="190"/>
-      <c r="F64" s="190"/>
-      <c r="G64" s="190"/>
-      <c r="H64" s="190"/>
-      <c r="I64" s="190"/>
-      <c r="J64" s="190"/>
-      <c r="K64" s="190"/>
-      <c r="L64" s="190"/>
-      <c r="M64" s="190"/>
-      <c r="N64" s="190"/>
-      <c r="O64" s="190"/>
-      <c r="P64" s="190"/>
-      <c r="Q64" s="190"/>
-      <c r="R64" s="190"/>
-      <c r="S64" s="190"/>
-      <c r="T64" s="190"/>
-      <c r="U64" s="190"/>
-      <c r="V64" s="190"/>
-      <c r="W64" s="190"/>
-      <c r="X64" s="190"/>
-      <c r="Y64" s="190"/>
-      <c r="Z64" s="190"/>
-      <c r="AA64" s="190"/>
-      <c r="AB64" s="190"/>
-      <c r="AC64" s="190"/>
-      <c r="AD64" s="190"/>
-      <c r="AE64" s="190"/>
-      <c r="AF64" s="190"/>
-      <c r="AG64" s="190"/>
-      <c r="AH64" s="190"/>
-      <c r="AI64" s="190"/>
+      <c r="A64" s="205"/>
+      <c r="B64" s="205"/>
+      <c r="C64" s="205"/>
+      <c r="D64" s="205"/>
+      <c r="E64" s="205"/>
+      <c r="F64" s="205"/>
+      <c r="G64" s="205"/>
+      <c r="H64" s="205"/>
+      <c r="I64" s="205"/>
+      <c r="J64" s="205"/>
+      <c r="K64" s="205"/>
+      <c r="L64" s="205"/>
+      <c r="M64" s="205"/>
+      <c r="N64" s="205"/>
+      <c r="O64" s="205"/>
+      <c r="P64" s="205"/>
+      <c r="Q64" s="205"/>
+      <c r="R64" s="205"/>
+      <c r="S64" s="205"/>
+      <c r="T64" s="205"/>
+      <c r="U64" s="205"/>
+      <c r="V64" s="205"/>
+      <c r="W64" s="205"/>
+      <c r="X64" s="205"/>
+      <c r="Y64" s="205"/>
+      <c r="Z64" s="205"/>
+      <c r="AA64" s="205"/>
+      <c r="AB64" s="205"/>
+      <c r="AC64" s="205"/>
+      <c r="AD64" s="205"/>
+      <c r="AE64" s="205"/>
+      <c r="AF64" s="205"/>
+      <c r="AG64" s="205"/>
+      <c r="AH64" s="205"/>
+      <c r="AI64" s="205"/>
       <c r="AS64" s="30"/>
       <c r="AT64" s="29" t="s">
         <v>174</v>
@@ -5638,37 +5767,37 @@
       </c>
     </row>
     <row r="66" spans="1:60" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="187" t="s">
+      <c r="B66" s="193" t="s">
         <v>1</v>
       </c>
-      <c r="C66" s="187"/>
-      <c r="D66" s="187"/>
-      <c r="E66" s="187"/>
-      <c r="F66" s="187"/>
-      <c r="G66" s="187"/>
-      <c r="H66" s="187"/>
-      <c r="I66" s="187"/>
-      <c r="J66" s="187"/>
-      <c r="K66" s="187"/>
-      <c r="L66" s="187"/>
-      <c r="M66" s="187"/>
-      <c r="N66" s="187"/>
-      <c r="O66" s="175" t="str">
+      <c r="C66" s="193"/>
+      <c r="D66" s="193"/>
+      <c r="E66" s="193"/>
+      <c r="F66" s="193"/>
+      <c r="G66" s="193"/>
+      <c r="H66" s="193"/>
+      <c r="I66" s="193"/>
+      <c r="J66" s="193"/>
+      <c r="K66" s="193"/>
+      <c r="L66" s="193"/>
+      <c r="M66" s="193"/>
+      <c r="N66" s="193"/>
+      <c r="O66" s="209" t="str">
         <f>IF(O7="","",O7)</f>
         <v/>
       </c>
-      <c r="P66" s="176"/>
-      <c r="Q66" s="176"/>
-      <c r="R66" s="176"/>
-      <c r="S66" s="176"/>
-      <c r="T66" s="176"/>
-      <c r="U66" s="176"/>
-      <c r="V66" s="176"/>
-      <c r="W66" s="177"/>
-      <c r="X66" s="75" t="s">
+      <c r="P66" s="210"/>
+      <c r="Q66" s="210"/>
+      <c r="R66" s="210"/>
+      <c r="S66" s="210"/>
+      <c r="T66" s="210"/>
+      <c r="U66" s="210"/>
+      <c r="V66" s="210"/>
+      <c r="W66" s="211"/>
+      <c r="X66" s="167" t="s">
         <v>185</v>
       </c>
-      <c r="Y66" s="75"/>
+      <c r="Y66" s="167"/>
       <c r="Z66" s="67"/>
       <c r="AA66" s="68"/>
       <c r="AB66" s="69"/>
@@ -5698,64 +5827,64 @@
       <c r="L67" s="11"/>
       <c r="M67" s="11"/>
       <c r="N67" s="11"/>
-      <c r="O67" s="185"/>
-      <c r="P67" s="185"/>
-      <c r="Q67" s="185"/>
-      <c r="R67" s="185"/>
-      <c r="S67" s="185"/>
-      <c r="T67" s="185"/>
-      <c r="U67" s="185"/>
-      <c r="V67" s="185"/>
-      <c r="W67" s="185"/>
-      <c r="X67" s="186"/>
-      <c r="Y67" s="186"/>
-      <c r="Z67" s="186"/>
-      <c r="AA67" s="186"/>
-      <c r="AB67" s="186"/>
-      <c r="AC67" s="186"/>
-      <c r="AD67" s="186"/>
-      <c r="AE67" s="186"/>
-      <c r="AF67" s="186"/>
-      <c r="AG67" s="186"/>
-      <c r="AH67" s="186"/>
-      <c r="AI67" s="186"/>
+      <c r="O67" s="192"/>
+      <c r="P67" s="192"/>
+      <c r="Q67" s="192"/>
+      <c r="R67" s="192"/>
+      <c r="S67" s="192"/>
+      <c r="T67" s="192"/>
+      <c r="U67" s="192"/>
+      <c r="V67" s="192"/>
+      <c r="W67" s="192"/>
+      <c r="X67" s="120"/>
+      <c r="Y67" s="120"/>
+      <c r="Z67" s="120"/>
+      <c r="AA67" s="120"/>
+      <c r="AB67" s="120"/>
+      <c r="AC67" s="120"/>
+      <c r="AD67" s="120"/>
+      <c r="AE67" s="120"/>
+      <c r="AF67" s="120"/>
+      <c r="AG67" s="120"/>
+      <c r="AH67" s="120"/>
+      <c r="AI67" s="120"/>
       <c r="AS67" s="30"/>
       <c r="AT67" s="29" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="68" spans="1:60" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="191" t="s">
+      <c r="B68" s="170" t="s">
         <v>103</v>
       </c>
-      <c r="C68" s="191"/>
-      <c r="D68" s="191"/>
-      <c r="E68" s="191"/>
-      <c r="F68" s="191"/>
-      <c r="G68" s="191"/>
-      <c r="H68" s="191"/>
-      <c r="I68" s="191"/>
-      <c r="J68" s="191"/>
-      <c r="K68" s="178" t="str">
+      <c r="C68" s="170"/>
+      <c r="D68" s="170"/>
+      <c r="E68" s="170"/>
+      <c r="F68" s="170"/>
+      <c r="G68" s="170"/>
+      <c r="H68" s="170"/>
+      <c r="I68" s="170"/>
+      <c r="J68" s="170"/>
+      <c r="K68" s="212" t="str">
         <f>IF(K9="","",K9)</f>
         <v/>
       </c>
-      <c r="L68" s="179"/>
-      <c r="M68" s="179"/>
-      <c r="N68" s="179"/>
-      <c r="O68" s="179"/>
-      <c r="P68" s="179"/>
-      <c r="Q68" s="179"/>
-      <c r="R68" s="179"/>
-      <c r="S68" s="179"/>
-      <c r="T68" s="179"/>
-      <c r="U68" s="179"/>
-      <c r="V68" s="179"/>
-      <c r="W68" s="180"/>
-      <c r="X68" s="75" t="s">
+      <c r="L68" s="213"/>
+      <c r="M68" s="213"/>
+      <c r="N68" s="213"/>
+      <c r="O68" s="213"/>
+      <c r="P68" s="213"/>
+      <c r="Q68" s="213"/>
+      <c r="R68" s="213"/>
+      <c r="S68" s="213"/>
+      <c r="T68" s="213"/>
+      <c r="U68" s="213"/>
+      <c r="V68" s="213"/>
+      <c r="W68" s="214"/>
+      <c r="X68" s="167" t="s">
         <v>185</v>
       </c>
-      <c r="Y68" s="75"/>
+      <c r="Y68" s="167"/>
       <c r="Z68" s="67"/>
       <c r="AA68" s="68"/>
       <c r="AB68" s="69"/>
@@ -5780,93 +5909,93 @@
       <c r="G69" s="11"/>
       <c r="H69" s="11"/>
       <c r="I69" s="11"/>
-      <c r="J69" s="186"/>
-      <c r="K69" s="186"/>
-      <c r="L69" s="186"/>
-      <c r="M69" s="186"/>
-      <c r="N69" s="186"/>
-      <c r="O69" s="186"/>
-      <c r="P69" s="186"/>
-      <c r="Q69" s="186"/>
-      <c r="R69" s="186"/>
-      <c r="S69" s="186"/>
-      <c r="T69" s="186"/>
-      <c r="U69" s="186"/>
-      <c r="V69" s="186"/>
-      <c r="W69" s="186"/>
-      <c r="X69" s="186"/>
-      <c r="Y69" s="186"/>
-      <c r="Z69" s="186"/>
-      <c r="AA69" s="186"/>
-      <c r="AB69" s="186"/>
-      <c r="AC69" s="186"/>
-      <c r="AD69" s="186"/>
-      <c r="AE69" s="186"/>
-      <c r="AF69" s="186"/>
-      <c r="AG69" s="186"/>
-      <c r="AH69" s="186"/>
-      <c r="AI69" s="186"/>
+      <c r="J69" s="120"/>
+      <c r="K69" s="120"/>
+      <c r="L69" s="120"/>
+      <c r="M69" s="120"/>
+      <c r="N69" s="120"/>
+      <c r="O69" s="120"/>
+      <c r="P69" s="120"/>
+      <c r="Q69" s="120"/>
+      <c r="R69" s="120"/>
+      <c r="S69" s="120"/>
+      <c r="T69" s="120"/>
+      <c r="U69" s="120"/>
+      <c r="V69" s="120"/>
+      <c r="W69" s="120"/>
+      <c r="X69" s="120"/>
+      <c r="Y69" s="120"/>
+      <c r="Z69" s="120"/>
+      <c r="AA69" s="120"/>
+      <c r="AB69" s="120"/>
+      <c r="AC69" s="120"/>
+      <c r="AD69" s="120"/>
+      <c r="AE69" s="120"/>
+      <c r="AF69" s="120"/>
+      <c r="AG69" s="120"/>
+      <c r="AH69" s="120"/>
+      <c r="AI69" s="120"/>
       <c r="AS69" s="30"/>
       <c r="AT69" s="29" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="70" spans="1:60" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="187" t="s">
+      <c r="B70" s="193" t="s">
         <v>60</v>
       </c>
-      <c r="C70" s="187"/>
-      <c r="D70" s="187"/>
-      <c r="E70" s="187"/>
-      <c r="F70" s="187"/>
-      <c r="G70" s="187"/>
-      <c r="H70" s="187"/>
-      <c r="I70" s="187"/>
-      <c r="J70" s="187"/>
-      <c r="K70" s="187"/>
-      <c r="L70" s="187"/>
-      <c r="M70" s="187"/>
-      <c r="N70" s="187"/>
-      <c r="O70" s="187"/>
-      <c r="P70" s="187"/>
-      <c r="Q70" s="197" t="str">
+      <c r="C70" s="193"/>
+      <c r="D70" s="193"/>
+      <c r="E70" s="193"/>
+      <c r="F70" s="193"/>
+      <c r="G70" s="193"/>
+      <c r="H70" s="193"/>
+      <c r="I70" s="193"/>
+      <c r="J70" s="193"/>
+      <c r="K70" s="193"/>
+      <c r="L70" s="193"/>
+      <c r="M70" s="193"/>
+      <c r="N70" s="193"/>
+      <c r="O70" s="193"/>
+      <c r="P70" s="193"/>
+      <c r="Q70" s="176" t="str">
         <f>IF(Q18="","",Q18)</f>
         <v/>
       </c>
-      <c r="R70" s="198"/>
-      <c r="S70" s="198"/>
-      <c r="T70" s="198"/>
-      <c r="U70" s="198"/>
-      <c r="V70" s="199"/>
+      <c r="R70" s="177"/>
+      <c r="S70" s="177"/>
+      <c r="T70" s="177"/>
+      <c r="U70" s="177"/>
+      <c r="V70" s="178"/>
       <c r="W70" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="X70" s="200" t="str">
+      <c r="X70" s="179" t="str">
         <f>IF(X18="","",X18)</f>
         <v/>
       </c>
-      <c r="Y70" s="201"/>
-      <c r="Z70" s="192" t="str">
+      <c r="Y70" s="180"/>
+      <c r="Z70" s="171" t="str">
         <f>IF(Z18="","",Z18)</f>
         <v/>
       </c>
-      <c r="AA70" s="201"/>
-      <c r="AB70" s="192" t="str">
+      <c r="AA70" s="180"/>
+      <c r="AB70" s="171" t="str">
         <f>IF(AB18="","",AB18)</f>
         <v/>
       </c>
-      <c r="AC70" s="193"/>
+      <c r="AC70" s="172"/>
       <c r="AD70" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="AE70" s="194" t="str">
+      <c r="AE70" s="173" t="str">
         <f>IF(AE18="","",AE18)</f>
         <v/>
       </c>
-      <c r="AF70" s="195"/>
-      <c r="AG70" s="195"/>
-      <c r="AH70" s="195"/>
-      <c r="AI70" s="196"/>
+      <c r="AF70" s="174"/>
+      <c r="AG70" s="174"/>
+      <c r="AH70" s="174"/>
+      <c r="AI70" s="175"/>
       <c r="AS70" s="30"/>
       <c r="AT70" s="32"/>
     </row>
@@ -5906,48 +6035,50 @@
       <c r="AH71" s="38"/>
       <c r="AI71" s="38"/>
       <c r="AS71" s="30"/>
+      <c r="AT71" s="32"/>
     </row>
     <row r="72" spans="1:60" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="181" t="s">
+      <c r="B72" s="182" t="s">
         <v>4</v>
       </c>
-      <c r="C72" s="181"/>
-      <c r="D72" s="181"/>
-      <c r="E72" s="181"/>
-      <c r="F72" s="182" t="str">
+      <c r="C72" s="182"/>
+      <c r="D72" s="182"/>
+      <c r="E72" s="182"/>
+      <c r="F72" s="183" t="str">
         <f>IF(F11="","",F11)</f>
         <v/>
       </c>
-      <c r="G72" s="183"/>
-      <c r="H72" s="183"/>
-      <c r="I72" s="183"/>
-      <c r="J72" s="183"/>
-      <c r="K72" s="183"/>
-      <c r="L72" s="183"/>
-      <c r="M72" s="183"/>
-      <c r="N72" s="183"/>
-      <c r="O72" s="183"/>
-      <c r="P72" s="183"/>
-      <c r="Q72" s="183"/>
-      <c r="R72" s="183"/>
-      <c r="S72" s="183"/>
-      <c r="T72" s="183"/>
-      <c r="U72" s="183"/>
-      <c r="V72" s="183"/>
-      <c r="W72" s="183"/>
-      <c r="X72" s="183"/>
-      <c r="Y72" s="183"/>
-      <c r="Z72" s="183"/>
-      <c r="AA72" s="183"/>
-      <c r="AB72" s="183"/>
-      <c r="AC72" s="183"/>
-      <c r="AD72" s="183"/>
-      <c r="AE72" s="183"/>
-      <c r="AF72" s="183"/>
-      <c r="AG72" s="183"/>
-      <c r="AH72" s="184"/>
+      <c r="G72" s="184"/>
+      <c r="H72" s="184"/>
+      <c r="I72" s="184"/>
+      <c r="J72" s="184"/>
+      <c r="K72" s="184"/>
+      <c r="L72" s="184"/>
+      <c r="M72" s="184"/>
+      <c r="N72" s="184"/>
+      <c r="O72" s="184"/>
+      <c r="P72" s="184"/>
+      <c r="Q72" s="184"/>
+      <c r="R72" s="184"/>
+      <c r="S72" s="184"/>
+      <c r="T72" s="184"/>
+      <c r="U72" s="184"/>
+      <c r="V72" s="184"/>
+      <c r="W72" s="184"/>
+      <c r="X72" s="184"/>
+      <c r="Y72" s="184"/>
+      <c r="Z72" s="184"/>
+      <c r="AA72" s="184"/>
+      <c r="AB72" s="184"/>
+      <c r="AC72" s="184"/>
+      <c r="AD72" s="184"/>
+      <c r="AE72" s="184"/>
+      <c r="AF72" s="184"/>
+      <c r="AG72" s="184"/>
+      <c r="AH72" s="185"/>
       <c r="AI72" s="35"/>
       <c r="AS72" s="30"/>
+      <c r="AT72" s="32"/>
     </row>
     <row r="73" spans="1:60" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="36"/>
@@ -5985,50 +6116,51 @@
       <c r="AH73" s="36"/>
       <c r="AI73" s="35"/>
       <c r="AS73" s="30"/>
+      <c r="AT73" s="32"/>
     </row>
     <row r="74" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="A74" s="149"/>
-      <c r="B74" s="149"/>
-      <c r="C74" s="160" t="s">
+      <c r="A74" s="72"/>
+      <c r="B74" s="72"/>
+      <c r="C74" s="103" t="s">
         <v>49</v>
       </c>
-      <c r="D74" s="160"/>
-      <c r="E74" s="160"/>
-      <c r="F74" s="160"/>
-      <c r="G74" s="160"/>
-      <c r="H74" s="160"/>
-      <c r="I74" s="160"/>
-      <c r="J74" s="160"/>
-      <c r="K74" s="160" t="s">
+      <c r="D74" s="103"/>
+      <c r="E74" s="103"/>
+      <c r="F74" s="103"/>
+      <c r="G74" s="103"/>
+      <c r="H74" s="103"/>
+      <c r="I74" s="103"/>
+      <c r="J74" s="103"/>
+      <c r="K74" s="103" t="s">
         <v>134</v>
       </c>
-      <c r="L74" s="160"/>
-      <c r="M74" s="160"/>
-      <c r="N74" s="160"/>
-      <c r="O74" s="160"/>
-      <c r="P74" s="160"/>
-      <c r="Q74" s="160"/>
-      <c r="R74" s="160"/>
-      <c r="S74" s="160" t="s">
+      <c r="L74" s="103"/>
+      <c r="M74" s="103"/>
+      <c r="N74" s="103"/>
+      <c r="O74" s="103"/>
+      <c r="P74" s="103"/>
+      <c r="Q74" s="103"/>
+      <c r="R74" s="103"/>
+      <c r="S74" s="103" t="s">
         <v>113</v>
       </c>
-      <c r="T74" s="160"/>
-      <c r="U74" s="160"/>
-      <c r="V74" s="160"/>
-      <c r="W74" s="160"/>
-      <c r="X74" s="160"/>
-      <c r="Y74" s="160"/>
-      <c r="Z74" s="160"/>
-      <c r="AB74" s="174" t="s">
+      <c r="T74" s="103"/>
+      <c r="U74" s="103"/>
+      <c r="V74" s="103"/>
+      <c r="W74" s="103"/>
+      <c r="X74" s="103"/>
+      <c r="Y74" s="103"/>
+      <c r="Z74" s="103"/>
+      <c r="AB74" s="118" t="s">
         <v>135</v>
       </c>
-      <c r="AC74" s="174"/>
-      <c r="AD74" s="174"/>
-      <c r="AE74" s="174"/>
-      <c r="AF74" s="174"/>
-      <c r="AG74" s="174"/>
-      <c r="AH74" s="174"/>
-      <c r="AI74" s="174"/>
+      <c r="AC74" s="118"/>
+      <c r="AD74" s="118"/>
+      <c r="AE74" s="118"/>
+      <c r="AF74" s="118"/>
+      <c r="AG74" s="118"/>
+      <c r="AH74" s="118"/>
+      <c r="AI74" s="118"/>
       <c r="AJ74" s="33" t="s">
         <v>57</v>
       </c>
@@ -6043,45 +6175,46 @@
         <v>91</v>
       </c>
       <c r="AS74" s="30"/>
+      <c r="AT74" s="32"/>
     </row>
     <row r="75" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="A75" s="149" t="s">
+      <c r="A75" s="72" t="s">
         <v>136</v>
       </c>
-      <c r="B75" s="149"/>
-      <c r="C75" s="82"/>
-      <c r="D75" s="83"/>
-      <c r="E75" s="83"/>
-      <c r="F75" s="83"/>
-      <c r="G75" s="83"/>
-      <c r="H75" s="83"/>
-      <c r="I75" s="84"/>
+      <c r="B75" s="72"/>
+      <c r="C75" s="78"/>
+      <c r="D75" s="79"/>
+      <c r="E75" s="79"/>
+      <c r="F75" s="79"/>
+      <c r="G75" s="79"/>
+      <c r="H75" s="79"/>
+      <c r="I75" s="80"/>
       <c r="J75" s="3"/>
-      <c r="K75" s="79"/>
-      <c r="L75" s="80"/>
-      <c r="M75" s="80"/>
-      <c r="N75" s="80"/>
-      <c r="O75" s="80"/>
-      <c r="P75" s="80"/>
-      <c r="Q75" s="81"/>
+      <c r="K75" s="87"/>
+      <c r="L75" s="88"/>
+      <c r="M75" s="88"/>
+      <c r="N75" s="88"/>
+      <c r="O75" s="88"/>
+      <c r="P75" s="88"/>
+      <c r="Q75" s="89"/>
       <c r="R75" s="4"/>
-      <c r="S75" s="120"/>
-      <c r="T75" s="121"/>
-      <c r="U75" s="121"/>
-      <c r="V75" s="121"/>
-      <c r="W75" s="121"/>
-      <c r="X75" s="121"/>
-      <c r="Y75" s="121"/>
-      <c r="Z75" s="122"/>
+      <c r="S75" s="90"/>
+      <c r="T75" s="91"/>
+      <c r="U75" s="91"/>
+      <c r="V75" s="91"/>
+      <c r="W75" s="91"/>
+      <c r="X75" s="91"/>
+      <c r="Y75" s="91"/>
+      <c r="Z75" s="92"/>
       <c r="AA75" s="4"/>
-      <c r="AB75" s="131"/>
-      <c r="AC75" s="132"/>
-      <c r="AD75" s="132"/>
-      <c r="AE75" s="132"/>
-      <c r="AF75" s="132"/>
-      <c r="AG75" s="132"/>
-      <c r="AH75" s="132"/>
-      <c r="AI75" s="133"/>
+      <c r="AB75" s="93"/>
+      <c r="AC75" s="94"/>
+      <c r="AD75" s="94"/>
+      <c r="AE75" s="94"/>
+      <c r="AF75" s="94"/>
+      <c r="AG75" s="94"/>
+      <c r="AH75" s="94"/>
+      <c r="AI75" s="95"/>
       <c r="AJ75" s="31"/>
       <c r="AO75" s="30">
         <v>16</v>
@@ -6112,47 +6245,47 @@
     <row r="76" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
-      <c r="C76" s="136" t="s">
+      <c r="C76" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="D76" s="136"/>
-      <c r="E76" s="136"/>
-      <c r="F76" s="136"/>
-      <c r="G76" s="136"/>
-      <c r="H76" s="136"/>
-      <c r="I76" s="136"/>
+      <c r="D76" s="85"/>
+      <c r="E76" s="85"/>
+      <c r="F76" s="85"/>
+      <c r="G76" s="85"/>
+      <c r="H76" s="85"/>
+      <c r="I76" s="85"/>
       <c r="J76" s="53"/>
-      <c r="K76" s="137" t="s">
+      <c r="K76" s="99" t="s">
         <v>50</v>
       </c>
-      <c r="L76" s="137"/>
-      <c r="M76" s="137"/>
-      <c r="N76" s="137"/>
-      <c r="O76" s="137"/>
-      <c r="P76" s="137"/>
-      <c r="Q76" s="137"/>
+      <c r="L76" s="99"/>
+      <c r="M76" s="99"/>
+      <c r="N76" s="99"/>
+      <c r="O76" s="99"/>
+      <c r="P76" s="99"/>
+      <c r="Q76" s="99"/>
       <c r="R76" s="4"/>
-      <c r="S76" s="150" t="s">
+      <c r="S76" s="101" t="s">
         <v>47</v>
       </c>
-      <c r="T76" s="150"/>
-      <c r="U76" s="144"/>
-      <c r="V76" s="145"/>
-      <c r="W76" s="151" t="s">
+      <c r="T76" s="101"/>
+      <c r="U76" s="134"/>
+      <c r="V76" s="135"/>
+      <c r="W76" s="136" t="s">
         <v>48</v>
       </c>
-      <c r="X76" s="152"/>
-      <c r="Y76" s="144"/>
-      <c r="Z76" s="145"/>
+      <c r="X76" s="137"/>
+      <c r="Y76" s="134"/>
+      <c r="Z76" s="135"/>
       <c r="AA76" s="4"/>
-      <c r="AB76" s="134"/>
-      <c r="AC76" s="105"/>
-      <c r="AD76" s="105"/>
-      <c r="AE76" s="105"/>
-      <c r="AF76" s="105"/>
-      <c r="AG76" s="105"/>
-      <c r="AH76" s="105"/>
-      <c r="AI76" s="135"/>
+      <c r="AB76" s="96"/>
+      <c r="AC76" s="97"/>
+      <c r="AD76" s="97"/>
+      <c r="AE76" s="97"/>
+      <c r="AF76" s="97"/>
+      <c r="AG76" s="97"/>
+      <c r="AH76" s="97"/>
+      <c r="AI76" s="98"/>
       <c r="AJ76" s="31" t="s">
         <v>123</v>
       </c>
@@ -6192,24 +6325,24 @@
       <c r="H77" s="46"/>
       <c r="I77" s="46"/>
       <c r="J77" s="46"/>
-      <c r="K77" s="138"/>
-      <c r="L77" s="138"/>
-      <c r="M77" s="138"/>
-      <c r="N77" s="138"/>
-      <c r="O77" s="138"/>
-      <c r="P77" s="138"/>
-      <c r="Q77" s="138"/>
+      <c r="K77" s="100"/>
+      <c r="L77" s="100"/>
+      <c r="M77" s="100"/>
+      <c r="N77" s="100"/>
+      <c r="O77" s="100"/>
+      <c r="P77" s="100"/>
+      <c r="Q77" s="100"/>
       <c r="R77" s="4"/>
-      <c r="S77" s="153" t="s">
+      <c r="S77" s="76" t="s">
         <v>124</v>
       </c>
-      <c r="T77" s="154"/>
-      <c r="U77" s="154"/>
-      <c r="V77" s="154"/>
-      <c r="W77" s="154"/>
-      <c r="X77" s="154"/>
-      <c r="Y77" s="154"/>
-      <c r="Z77" s="154"/>
+      <c r="T77" s="138"/>
+      <c r="U77" s="138"/>
+      <c r="V77" s="138"/>
+      <c r="W77" s="138"/>
+      <c r="X77" s="138"/>
+      <c r="Y77" s="138"/>
+      <c r="Z77" s="138"/>
       <c r="AA77" s="4"/>
       <c r="AB77" s="47"/>
       <c r="AC77" s="47"/>
@@ -6241,45 +6374,45 @@
       <c r="BH77" s="43"/>
     </row>
     <row r="78" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="106"/>
-      <c r="B78" s="155"/>
-      <c r="C78" s="112" t="s">
+      <c r="A78" s="168"/>
+      <c r="B78" s="169"/>
+      <c r="C78" s="107" t="s">
         <v>183</v>
       </c>
-      <c r="D78" s="113"/>
-      <c r="E78" s="113"/>
-      <c r="F78" s="113"/>
-      <c r="G78" s="113"/>
-      <c r="H78" s="113"/>
-      <c r="I78" s="113"/>
-      <c r="J78" s="113"/>
-      <c r="K78" s="113"/>
-      <c r="L78" s="113"/>
-      <c r="M78" s="113"/>
+      <c r="D78" s="108"/>
+      <c r="E78" s="108"/>
+      <c r="F78" s="108"/>
+      <c r="G78" s="108"/>
+      <c r="H78" s="108"/>
+      <c r="I78" s="108"/>
+      <c r="J78" s="108"/>
+      <c r="K78" s="108"/>
+      <c r="L78" s="108"/>
+      <c r="M78" s="108"/>
       <c r="N78" s="50"/>
-      <c r="O78" s="114" t="s">
+      <c r="O78" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="P78" s="115"/>
-      <c r="Q78" s="116"/>
+      <c r="P78" s="105"/>
+      <c r="Q78" s="106"/>
       <c r="R78" s="56"/>
-      <c r="S78" s="117"/>
-      <c r="T78" s="117"/>
-      <c r="U78" s="117"/>
-      <c r="V78" s="117"/>
-      <c r="W78" s="117"/>
-      <c r="X78" s="117"/>
-      <c r="Y78" s="117"/>
-      <c r="Z78" s="117"/>
+      <c r="S78" s="74"/>
+      <c r="T78" s="74"/>
+      <c r="U78" s="74"/>
+      <c r="V78" s="74"/>
+      <c r="W78" s="74"/>
+      <c r="X78" s="74"/>
+      <c r="Y78" s="74"/>
+      <c r="Z78" s="74"/>
       <c r="AA78" s="4"/>
-      <c r="AB78" s="139"/>
-      <c r="AC78" s="139"/>
-      <c r="AD78" s="139"/>
-      <c r="AE78" s="139"/>
-      <c r="AF78" s="139"/>
-      <c r="AG78" s="139"/>
-      <c r="AH78" s="139"/>
-      <c r="AI78" s="139"/>
+      <c r="AB78" s="86"/>
+      <c r="AC78" s="86"/>
+      <c r="AD78" s="86"/>
+      <c r="AE78" s="86"/>
+      <c r="AF78" s="86"/>
+      <c r="AG78" s="86"/>
+      <c r="AH78" s="86"/>
+      <c r="AI78" s="86"/>
       <c r="AJ78" s="31"/>
       <c r="AO78" s="30">
         <v>19</v>
@@ -6310,32 +6443,32 @@
     <row r="79" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="39"/>
       <c r="B79" s="39"/>
-      <c r="C79" s="113"/>
-      <c r="D79" s="113"/>
-      <c r="E79" s="113"/>
-      <c r="F79" s="113"/>
-      <c r="G79" s="113"/>
-      <c r="H79" s="113"/>
-      <c r="I79" s="113"/>
-      <c r="J79" s="113"/>
-      <c r="K79" s="113"/>
-      <c r="L79" s="113"/>
-      <c r="M79" s="113"/>
+      <c r="C79" s="108"/>
+      <c r="D79" s="108"/>
+      <c r="E79" s="108"/>
+      <c r="F79" s="108"/>
+      <c r="G79" s="108"/>
+      <c r="H79" s="108"/>
+      <c r="I79" s="108"/>
+      <c r="J79" s="108"/>
+      <c r="K79" s="108"/>
+      <c r="L79" s="108"/>
+      <c r="M79" s="108"/>
       <c r="N79" s="50"/>
       <c r="O79" s="50"/>
       <c r="P79" s="50"/>
       <c r="Q79" s="50"/>
       <c r="R79" s="51"/>
-      <c r="S79" s="118" t="s">
+      <c r="S79" s="102" t="s">
         <v>182</v>
       </c>
-      <c r="T79" s="119"/>
-      <c r="U79" s="119"/>
-      <c r="V79" s="119"/>
-      <c r="W79" s="119"/>
-      <c r="X79" s="119"/>
-      <c r="Y79" s="119"/>
-      <c r="Z79" s="119"/>
+      <c r="T79" s="181"/>
+      <c r="U79" s="181"/>
+      <c r="V79" s="181"/>
+      <c r="W79" s="181"/>
+      <c r="X79" s="181"/>
+      <c r="Y79" s="181"/>
+      <c r="Z79" s="181"/>
       <c r="AA79" s="4"/>
       <c r="AB79" s="40"/>
       <c r="AC79" s="40"/>
@@ -6371,35 +6504,35 @@
       <c r="BH79" s="43"/>
     </row>
     <row r="80" spans="1:60" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="130"/>
-      <c r="B80" s="130"/>
-      <c r="C80" s="156" t="s">
+      <c r="A80" s="75"/>
+      <c r="B80" s="75"/>
+      <c r="C80" s="216" t="s">
         <v>127</v>
       </c>
-      <c r="D80" s="157"/>
-      <c r="E80" s="157"/>
-      <c r="F80" s="157"/>
-      <c r="G80" s="157"/>
-      <c r="H80" s="157"/>
-      <c r="I80" s="157"/>
-      <c r="J80" s="157"/>
-      <c r="K80" s="157"/>
-      <c r="L80" s="157"/>
+      <c r="D80" s="217"/>
+      <c r="E80" s="217"/>
+      <c r="F80" s="217"/>
+      <c r="G80" s="217"/>
+      <c r="H80" s="217"/>
+      <c r="I80" s="217"/>
+      <c r="J80" s="217"/>
+      <c r="K80" s="217"/>
+      <c r="L80" s="217"/>
       <c r="M80" s="42"/>
       <c r="N80" s="42"/>
-      <c r="O80" s="114" t="s">
+      <c r="O80" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="P80" s="115"/>
-      <c r="Q80" s="116"/>
-      <c r="S80" s="117"/>
-      <c r="T80" s="117"/>
-      <c r="U80" s="117"/>
-      <c r="V80" s="117"/>
-      <c r="W80" s="117"/>
-      <c r="X80" s="117"/>
-      <c r="Y80" s="117"/>
-      <c r="Z80" s="117"/>
+      <c r="P80" s="105"/>
+      <c r="Q80" s="106"/>
+      <c r="S80" s="74"/>
+      <c r="T80" s="74"/>
+      <c r="U80" s="74"/>
+      <c r="V80" s="74"/>
+      <c r="W80" s="74"/>
+      <c r="X80" s="74"/>
+      <c r="Y80" s="74"/>
+      <c r="Z80" s="74"/>
       <c r="AB80" s="47"/>
       <c r="AC80" s="47"/>
       <c r="AD80" s="47"/>
@@ -6479,43 +6612,43 @@
       <c r="BH81" s="43"/>
     </row>
     <row r="82" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="A82" s="149" t="s">
+      <c r="A82" s="72" t="s">
         <v>137</v>
       </c>
-      <c r="B82" s="149"/>
-      <c r="C82" s="82"/>
-      <c r="D82" s="83"/>
-      <c r="E82" s="83"/>
-      <c r="F82" s="83"/>
-      <c r="G82" s="83"/>
-      <c r="H82" s="83"/>
-      <c r="I82" s="84"/>
+      <c r="B82" s="72"/>
+      <c r="C82" s="78"/>
+      <c r="D82" s="79"/>
+      <c r="E82" s="79"/>
+      <c r="F82" s="79"/>
+      <c r="G82" s="79"/>
+      <c r="H82" s="79"/>
+      <c r="I82" s="80"/>
       <c r="J82" s="3"/>
-      <c r="K82" s="79"/>
-      <c r="L82" s="80"/>
-      <c r="M82" s="80"/>
-      <c r="N82" s="80"/>
-      <c r="O82" s="80"/>
-      <c r="P82" s="80"/>
-      <c r="Q82" s="81"/>
+      <c r="K82" s="87"/>
+      <c r="L82" s="88"/>
+      <c r="M82" s="88"/>
+      <c r="N82" s="88"/>
+      <c r="O82" s="88"/>
+      <c r="P82" s="88"/>
+      <c r="Q82" s="89"/>
       <c r="R82" s="4"/>
-      <c r="S82" s="120"/>
-      <c r="T82" s="121"/>
-      <c r="U82" s="121"/>
-      <c r="V82" s="121"/>
-      <c r="W82" s="121"/>
-      <c r="X82" s="121"/>
-      <c r="Y82" s="121"/>
-      <c r="Z82" s="122"/>
+      <c r="S82" s="90"/>
+      <c r="T82" s="91"/>
+      <c r="U82" s="91"/>
+      <c r="V82" s="91"/>
+      <c r="W82" s="91"/>
+      <c r="X82" s="91"/>
+      <c r="Y82" s="91"/>
+      <c r="Z82" s="92"/>
       <c r="AA82" s="4"/>
-      <c r="AB82" s="131"/>
-      <c r="AC82" s="132"/>
-      <c r="AD82" s="132"/>
-      <c r="AE82" s="132"/>
-      <c r="AF82" s="132"/>
-      <c r="AG82" s="132"/>
-      <c r="AH82" s="132"/>
-      <c r="AI82" s="133"/>
+      <c r="AB82" s="93"/>
+      <c r="AC82" s="94"/>
+      <c r="AD82" s="94"/>
+      <c r="AE82" s="94"/>
+      <c r="AF82" s="94"/>
+      <c r="AG82" s="94"/>
+      <c r="AH82" s="94"/>
+      <c r="AI82" s="95"/>
       <c r="AJ82" s="31"/>
       <c r="AO82" s="30">
         <v>16</v>
@@ -6546,47 +6679,47 @@
     <row r="83" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
-      <c r="C83" s="136" t="s">
+      <c r="C83" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="D83" s="136"/>
-      <c r="E83" s="136"/>
-      <c r="F83" s="136"/>
-      <c r="G83" s="136"/>
-      <c r="H83" s="136"/>
-      <c r="I83" s="136"/>
+      <c r="D83" s="85"/>
+      <c r="E83" s="85"/>
+      <c r="F83" s="85"/>
+      <c r="G83" s="85"/>
+      <c r="H83" s="85"/>
+      <c r="I83" s="85"/>
       <c r="J83" s="53"/>
-      <c r="K83" s="137" t="s">
+      <c r="K83" s="99" t="s">
         <v>50</v>
       </c>
-      <c r="L83" s="137"/>
-      <c r="M83" s="137"/>
-      <c r="N83" s="137"/>
-      <c r="O83" s="137"/>
-      <c r="P83" s="137"/>
-      <c r="Q83" s="137"/>
+      <c r="L83" s="99"/>
+      <c r="M83" s="99"/>
+      <c r="N83" s="99"/>
+      <c r="O83" s="99"/>
+      <c r="P83" s="99"/>
+      <c r="Q83" s="99"/>
       <c r="R83" s="4"/>
-      <c r="S83" s="150" t="s">
+      <c r="S83" s="101" t="s">
         <v>47</v>
       </c>
-      <c r="T83" s="150"/>
-      <c r="U83" s="144"/>
-      <c r="V83" s="145"/>
-      <c r="W83" s="151" t="s">
+      <c r="T83" s="101"/>
+      <c r="U83" s="134"/>
+      <c r="V83" s="135"/>
+      <c r="W83" s="136" t="s">
         <v>48</v>
       </c>
-      <c r="X83" s="152"/>
-      <c r="Y83" s="144"/>
-      <c r="Z83" s="145"/>
+      <c r="X83" s="137"/>
+      <c r="Y83" s="134"/>
+      <c r="Z83" s="135"/>
       <c r="AA83" s="4"/>
-      <c r="AB83" s="134"/>
-      <c r="AC83" s="105"/>
-      <c r="AD83" s="105"/>
-      <c r="AE83" s="105"/>
-      <c r="AF83" s="105"/>
-      <c r="AG83" s="105"/>
-      <c r="AH83" s="105"/>
-      <c r="AI83" s="135"/>
+      <c r="AB83" s="96"/>
+      <c r="AC83" s="97"/>
+      <c r="AD83" s="97"/>
+      <c r="AE83" s="97"/>
+      <c r="AF83" s="97"/>
+      <c r="AG83" s="97"/>
+      <c r="AH83" s="97"/>
+      <c r="AI83" s="98"/>
       <c r="AJ83" s="31" t="s">
         <v>123</v>
       </c>
@@ -6626,24 +6759,24 @@
       <c r="H84" s="46"/>
       <c r="I84" s="46"/>
       <c r="J84" s="46"/>
-      <c r="K84" s="138"/>
-      <c r="L84" s="138"/>
-      <c r="M84" s="138"/>
-      <c r="N84" s="138"/>
-      <c r="O84" s="138"/>
-      <c r="P84" s="138"/>
-      <c r="Q84" s="138"/>
+      <c r="K84" s="100"/>
+      <c r="L84" s="100"/>
+      <c r="M84" s="100"/>
+      <c r="N84" s="100"/>
+      <c r="O84" s="100"/>
+      <c r="P84" s="100"/>
+      <c r="Q84" s="100"/>
       <c r="R84" s="4"/>
-      <c r="S84" s="153" t="s">
+      <c r="S84" s="76" t="s">
         <v>124</v>
       </c>
-      <c r="T84" s="154"/>
-      <c r="U84" s="154"/>
-      <c r="V84" s="154"/>
-      <c r="W84" s="154"/>
-      <c r="X84" s="154"/>
-      <c r="Y84" s="154"/>
-      <c r="Z84" s="154"/>
+      <c r="T84" s="138"/>
+      <c r="U84" s="138"/>
+      <c r="V84" s="138"/>
+      <c r="W84" s="138"/>
+      <c r="X84" s="138"/>
+      <c r="Y84" s="138"/>
+      <c r="Z84" s="138"/>
       <c r="AA84" s="4"/>
       <c r="AB84" s="47"/>
       <c r="AC84" s="47"/>
@@ -6675,45 +6808,45 @@
       <c r="BH84" s="43"/>
     </row>
     <row r="85" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="106"/>
-      <c r="B85" s="155"/>
-      <c r="C85" s="112" t="s">
+      <c r="A85" s="168"/>
+      <c r="B85" s="169"/>
+      <c r="C85" s="107" t="s">
         <v>183</v>
       </c>
-      <c r="D85" s="113"/>
-      <c r="E85" s="113"/>
-      <c r="F85" s="113"/>
-      <c r="G85" s="113"/>
-      <c r="H85" s="113"/>
-      <c r="I85" s="113"/>
-      <c r="J85" s="113"/>
-      <c r="K85" s="113"/>
-      <c r="L85" s="113"/>
-      <c r="M85" s="113"/>
+      <c r="D85" s="108"/>
+      <c r="E85" s="108"/>
+      <c r="F85" s="108"/>
+      <c r="G85" s="108"/>
+      <c r="H85" s="108"/>
+      <c r="I85" s="108"/>
+      <c r="J85" s="108"/>
+      <c r="K85" s="108"/>
+      <c r="L85" s="108"/>
+      <c r="M85" s="108"/>
       <c r="N85" s="50"/>
-      <c r="O85" s="114" t="s">
+      <c r="O85" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="P85" s="115"/>
-      <c r="Q85" s="116"/>
+      <c r="P85" s="105"/>
+      <c r="Q85" s="106"/>
       <c r="R85" s="56"/>
-      <c r="S85" s="117"/>
-      <c r="T85" s="117"/>
-      <c r="U85" s="117"/>
-      <c r="V85" s="117"/>
-      <c r="W85" s="117"/>
-      <c r="X85" s="117"/>
-      <c r="Y85" s="117"/>
-      <c r="Z85" s="117"/>
+      <c r="S85" s="74"/>
+      <c r="T85" s="74"/>
+      <c r="U85" s="74"/>
+      <c r="V85" s="74"/>
+      <c r="W85" s="74"/>
+      <c r="X85" s="74"/>
+      <c r="Y85" s="74"/>
+      <c r="Z85" s="74"/>
       <c r="AA85" s="4"/>
-      <c r="AB85" s="139"/>
-      <c r="AC85" s="139"/>
-      <c r="AD85" s="139"/>
-      <c r="AE85" s="139"/>
-      <c r="AF85" s="139"/>
-      <c r="AG85" s="139"/>
-      <c r="AH85" s="139"/>
-      <c r="AI85" s="139"/>
+      <c r="AB85" s="86"/>
+      <c r="AC85" s="86"/>
+      <c r="AD85" s="86"/>
+      <c r="AE85" s="86"/>
+      <c r="AF85" s="86"/>
+      <c r="AG85" s="86"/>
+      <c r="AH85" s="86"/>
+      <c r="AI85" s="86"/>
       <c r="AJ85" s="31"/>
       <c r="AO85" s="30">
         <v>19</v>
@@ -6744,32 +6877,32 @@
     <row r="86" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="39"/>
       <c r="B86" s="39"/>
-      <c r="C86" s="113"/>
-      <c r="D86" s="113"/>
-      <c r="E86" s="113"/>
-      <c r="F86" s="113"/>
-      <c r="G86" s="113"/>
-      <c r="H86" s="113"/>
-      <c r="I86" s="113"/>
-      <c r="J86" s="113"/>
-      <c r="K86" s="113"/>
-      <c r="L86" s="113"/>
-      <c r="M86" s="113"/>
+      <c r="C86" s="108"/>
+      <c r="D86" s="108"/>
+      <c r="E86" s="108"/>
+      <c r="F86" s="108"/>
+      <c r="G86" s="108"/>
+      <c r="H86" s="108"/>
+      <c r="I86" s="108"/>
+      <c r="J86" s="108"/>
+      <c r="K86" s="108"/>
+      <c r="L86" s="108"/>
+      <c r="M86" s="108"/>
       <c r="N86" s="50"/>
       <c r="O86" s="50"/>
       <c r="P86" s="50"/>
       <c r="Q86" s="50"/>
       <c r="R86" s="51"/>
-      <c r="S86" s="118" t="s">
+      <c r="S86" s="102" t="s">
         <v>182</v>
       </c>
-      <c r="T86" s="119"/>
-      <c r="U86" s="119"/>
-      <c r="V86" s="119"/>
-      <c r="W86" s="119"/>
-      <c r="X86" s="119"/>
-      <c r="Y86" s="119"/>
-      <c r="Z86" s="119"/>
+      <c r="T86" s="181"/>
+      <c r="U86" s="181"/>
+      <c r="V86" s="181"/>
+      <c r="W86" s="181"/>
+      <c r="X86" s="181"/>
+      <c r="Y86" s="181"/>
+      <c r="Z86" s="181"/>
       <c r="AA86" s="4"/>
       <c r="AB86" s="40"/>
       <c r="AC86" s="40"/>
@@ -6805,35 +6938,35 @@
       <c r="BH86" s="43"/>
     </row>
     <row r="87" spans="1:60" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="130"/>
-      <c r="B87" s="130"/>
-      <c r="C87" s="156" t="s">
+      <c r="A87" s="75"/>
+      <c r="B87" s="75"/>
+      <c r="C87" s="216" t="s">
         <v>127</v>
       </c>
-      <c r="D87" s="157"/>
-      <c r="E87" s="157"/>
-      <c r="F87" s="157"/>
-      <c r="G87" s="157"/>
-      <c r="H87" s="157"/>
-      <c r="I87" s="157"/>
-      <c r="J87" s="157"/>
-      <c r="K87" s="157"/>
-      <c r="L87" s="157"/>
+      <c r="D87" s="217"/>
+      <c r="E87" s="217"/>
+      <c r="F87" s="217"/>
+      <c r="G87" s="217"/>
+      <c r="H87" s="217"/>
+      <c r="I87" s="217"/>
+      <c r="J87" s="217"/>
+      <c r="K87" s="217"/>
+      <c r="L87" s="217"/>
       <c r="M87" s="42"/>
       <c r="N87" s="42"/>
-      <c r="O87" s="114" t="s">
+      <c r="O87" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="P87" s="115"/>
-      <c r="Q87" s="116"/>
-      <c r="S87" s="117"/>
-      <c r="T87" s="117"/>
-      <c r="U87" s="117"/>
-      <c r="V87" s="117"/>
-      <c r="W87" s="117"/>
-      <c r="X87" s="117"/>
-      <c r="Y87" s="117"/>
-      <c r="Z87" s="117"/>
+      <c r="P87" s="105"/>
+      <c r="Q87" s="106"/>
+      <c r="S87" s="74"/>
+      <c r="T87" s="74"/>
+      <c r="U87" s="74"/>
+      <c r="V87" s="74"/>
+      <c r="W87" s="74"/>
+      <c r="X87" s="74"/>
+      <c r="Y87" s="74"/>
+      <c r="Z87" s="74"/>
       <c r="AB87" s="47"/>
       <c r="AC87" s="47"/>
       <c r="AD87" s="47"/>
@@ -6875,22 +7008,22 @@
       <c r="O88" s="42"/>
       <c r="P88" s="42"/>
       <c r="Q88" s="42"/>
-      <c r="S88" s="232"/>
-      <c r="T88" s="232"/>
-      <c r="U88" s="232"/>
-      <c r="V88" s="232"/>
-      <c r="W88" s="232"/>
-      <c r="X88" s="232"/>
-      <c r="Y88" s="232"/>
-      <c r="Z88" s="232"/>
-      <c r="AB88" s="163"/>
-      <c r="AC88" s="163"/>
-      <c r="AD88" s="163"/>
-      <c r="AE88" s="163"/>
-      <c r="AF88" s="163"/>
-      <c r="AG88" s="163"/>
-      <c r="AH88" s="163"/>
-      <c r="AI88" s="163"/>
+      <c r="S88" s="83"/>
+      <c r="T88" s="83"/>
+      <c r="U88" s="83"/>
+      <c r="V88" s="83"/>
+      <c r="W88" s="83"/>
+      <c r="X88" s="83"/>
+      <c r="Y88" s="83"/>
+      <c r="Z88" s="83"/>
+      <c r="AB88" s="84"/>
+      <c r="AC88" s="84"/>
+      <c r="AD88" s="84"/>
+      <c r="AE88" s="84"/>
+      <c r="AF88" s="84"/>
+      <c r="AG88" s="84"/>
+      <c r="AH88" s="84"/>
+      <c r="AI88" s="84"/>
       <c r="AJ88" s="57"/>
       <c r="AK88" s="58"/>
       <c r="AL88" s="58"/>
@@ -6923,43 +7056,43 @@
       <c r="BH88" s="61"/>
     </row>
     <row r="89" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="A89" s="149" t="s">
+      <c r="A89" s="72" t="s">
         <v>138</v>
       </c>
-      <c r="B89" s="149"/>
-      <c r="C89" s="82"/>
-      <c r="D89" s="83"/>
-      <c r="E89" s="83"/>
-      <c r="F89" s="83"/>
-      <c r="G89" s="83"/>
-      <c r="H89" s="83"/>
-      <c r="I89" s="84"/>
+      <c r="B89" s="72"/>
+      <c r="C89" s="78"/>
+      <c r="D89" s="79"/>
+      <c r="E89" s="79"/>
+      <c r="F89" s="79"/>
+      <c r="G89" s="79"/>
+      <c r="H89" s="79"/>
+      <c r="I89" s="80"/>
       <c r="J89" s="3"/>
-      <c r="K89" s="79"/>
-      <c r="L89" s="80"/>
-      <c r="M89" s="80"/>
-      <c r="N89" s="80"/>
-      <c r="O89" s="80"/>
-      <c r="P89" s="80"/>
-      <c r="Q89" s="81"/>
+      <c r="K89" s="87"/>
+      <c r="L89" s="88"/>
+      <c r="M89" s="88"/>
+      <c r="N89" s="88"/>
+      <c r="O89" s="88"/>
+      <c r="P89" s="88"/>
+      <c r="Q89" s="89"/>
       <c r="R89" s="4"/>
-      <c r="S89" s="120"/>
-      <c r="T89" s="121"/>
-      <c r="U89" s="121"/>
-      <c r="V89" s="121"/>
-      <c r="W89" s="121"/>
-      <c r="X89" s="121"/>
-      <c r="Y89" s="121"/>
-      <c r="Z89" s="122"/>
+      <c r="S89" s="90"/>
+      <c r="T89" s="91"/>
+      <c r="U89" s="91"/>
+      <c r="V89" s="91"/>
+      <c r="W89" s="91"/>
+      <c r="X89" s="91"/>
+      <c r="Y89" s="91"/>
+      <c r="Z89" s="92"/>
       <c r="AA89" s="4"/>
-      <c r="AB89" s="131"/>
-      <c r="AC89" s="132"/>
-      <c r="AD89" s="132"/>
-      <c r="AE89" s="132"/>
-      <c r="AF89" s="132"/>
-      <c r="AG89" s="132"/>
-      <c r="AH89" s="132"/>
-      <c r="AI89" s="133"/>
+      <c r="AB89" s="93"/>
+      <c r="AC89" s="94"/>
+      <c r="AD89" s="94"/>
+      <c r="AE89" s="94"/>
+      <c r="AF89" s="94"/>
+      <c r="AG89" s="94"/>
+      <c r="AH89" s="94"/>
+      <c r="AI89" s="95"/>
       <c r="AJ89" s="31"/>
       <c r="AO89" s="30">
         <v>16</v>
@@ -6990,47 +7123,47 @@
     <row r="90" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
-      <c r="C90" s="136" t="s">
+      <c r="C90" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="D90" s="136"/>
-      <c r="E90" s="136"/>
-      <c r="F90" s="136"/>
-      <c r="G90" s="136"/>
-      <c r="H90" s="136"/>
-      <c r="I90" s="136"/>
+      <c r="D90" s="85"/>
+      <c r="E90" s="85"/>
+      <c r="F90" s="85"/>
+      <c r="G90" s="85"/>
+      <c r="H90" s="85"/>
+      <c r="I90" s="85"/>
       <c r="J90" s="53"/>
-      <c r="K90" s="137" t="s">
+      <c r="K90" s="99" t="s">
         <v>50</v>
       </c>
-      <c r="L90" s="137"/>
-      <c r="M90" s="137"/>
-      <c r="N90" s="137"/>
-      <c r="O90" s="137"/>
-      <c r="P90" s="137"/>
-      <c r="Q90" s="137"/>
+      <c r="L90" s="99"/>
+      <c r="M90" s="99"/>
+      <c r="N90" s="99"/>
+      <c r="O90" s="99"/>
+      <c r="P90" s="99"/>
+      <c r="Q90" s="99"/>
       <c r="R90" s="4"/>
-      <c r="S90" s="150" t="s">
+      <c r="S90" s="101" t="s">
         <v>47</v>
       </c>
-      <c r="T90" s="150"/>
-      <c r="U90" s="144"/>
-      <c r="V90" s="145"/>
-      <c r="W90" s="151" t="s">
+      <c r="T90" s="101"/>
+      <c r="U90" s="134"/>
+      <c r="V90" s="135"/>
+      <c r="W90" s="136" t="s">
         <v>48</v>
       </c>
-      <c r="X90" s="152"/>
-      <c r="Y90" s="144"/>
-      <c r="Z90" s="145"/>
+      <c r="X90" s="137"/>
+      <c r="Y90" s="134"/>
+      <c r="Z90" s="135"/>
       <c r="AA90" s="4"/>
-      <c r="AB90" s="134"/>
-      <c r="AC90" s="105"/>
-      <c r="AD90" s="105"/>
-      <c r="AE90" s="105"/>
-      <c r="AF90" s="105"/>
-      <c r="AG90" s="105"/>
-      <c r="AH90" s="105"/>
-      <c r="AI90" s="135"/>
+      <c r="AB90" s="96"/>
+      <c r="AC90" s="97"/>
+      <c r="AD90" s="97"/>
+      <c r="AE90" s="97"/>
+      <c r="AF90" s="97"/>
+      <c r="AG90" s="97"/>
+      <c r="AH90" s="97"/>
+      <c r="AI90" s="98"/>
       <c r="AJ90" s="31" t="s">
         <v>123</v>
       </c>
@@ -7070,24 +7203,24 @@
       <c r="H91" s="46"/>
       <c r="I91" s="46"/>
       <c r="J91" s="46"/>
-      <c r="K91" s="138"/>
-      <c r="L91" s="138"/>
-      <c r="M91" s="138"/>
-      <c r="N91" s="138"/>
-      <c r="O91" s="138"/>
-      <c r="P91" s="138"/>
-      <c r="Q91" s="138"/>
+      <c r="K91" s="100"/>
+      <c r="L91" s="100"/>
+      <c r="M91" s="100"/>
+      <c r="N91" s="100"/>
+      <c r="O91" s="100"/>
+      <c r="P91" s="100"/>
+      <c r="Q91" s="100"/>
       <c r="R91" s="4"/>
-      <c r="S91" s="153" t="s">
+      <c r="S91" s="76" t="s">
         <v>124</v>
       </c>
-      <c r="T91" s="154"/>
-      <c r="U91" s="154"/>
-      <c r="V91" s="154"/>
-      <c r="W91" s="154"/>
-      <c r="X91" s="154"/>
-      <c r="Y91" s="154"/>
-      <c r="Z91" s="154"/>
+      <c r="T91" s="138"/>
+      <c r="U91" s="138"/>
+      <c r="V91" s="138"/>
+      <c r="W91" s="138"/>
+      <c r="X91" s="138"/>
+      <c r="Y91" s="138"/>
+      <c r="Z91" s="138"/>
       <c r="AA91" s="4"/>
       <c r="AB91" s="47"/>
       <c r="AC91" s="47"/>
@@ -7119,45 +7252,45 @@
       <c r="BH91" s="43"/>
     </row>
     <row r="92" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="106"/>
-      <c r="B92" s="155"/>
-      <c r="C92" s="112" t="s">
+      <c r="A92" s="168"/>
+      <c r="B92" s="169"/>
+      <c r="C92" s="107" t="s">
         <v>183</v>
       </c>
-      <c r="D92" s="113"/>
-      <c r="E92" s="113"/>
-      <c r="F92" s="113"/>
-      <c r="G92" s="113"/>
-      <c r="H92" s="113"/>
-      <c r="I92" s="113"/>
-      <c r="J92" s="113"/>
-      <c r="K92" s="113"/>
-      <c r="L92" s="113"/>
-      <c r="M92" s="113"/>
+      <c r="D92" s="108"/>
+      <c r="E92" s="108"/>
+      <c r="F92" s="108"/>
+      <c r="G92" s="108"/>
+      <c r="H92" s="108"/>
+      <c r="I92" s="108"/>
+      <c r="J92" s="108"/>
+      <c r="K92" s="108"/>
+      <c r="L92" s="108"/>
+      <c r="M92" s="108"/>
       <c r="N92" s="50"/>
-      <c r="O92" s="114" t="s">
+      <c r="O92" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="P92" s="115"/>
-      <c r="Q92" s="116"/>
+      <c r="P92" s="105"/>
+      <c r="Q92" s="106"/>
       <c r="R92" s="56"/>
-      <c r="S92" s="117"/>
-      <c r="T92" s="117"/>
-      <c r="U92" s="117"/>
-      <c r="V92" s="117"/>
-      <c r="W92" s="117"/>
-      <c r="X92" s="117"/>
-      <c r="Y92" s="117"/>
-      <c r="Z92" s="117"/>
+      <c r="S92" s="74"/>
+      <c r="T92" s="74"/>
+      <c r="U92" s="74"/>
+      <c r="V92" s="74"/>
+      <c r="W92" s="74"/>
+      <c r="X92" s="74"/>
+      <c r="Y92" s="74"/>
+      <c r="Z92" s="74"/>
       <c r="AA92" s="4"/>
-      <c r="AB92" s="139"/>
-      <c r="AC92" s="139"/>
-      <c r="AD92" s="139"/>
-      <c r="AE92" s="139"/>
-      <c r="AF92" s="139"/>
-      <c r="AG92" s="139"/>
-      <c r="AH92" s="139"/>
-      <c r="AI92" s="139"/>
+      <c r="AB92" s="86"/>
+      <c r="AC92" s="86"/>
+      <c r="AD92" s="86"/>
+      <c r="AE92" s="86"/>
+      <c r="AF92" s="86"/>
+      <c r="AG92" s="86"/>
+      <c r="AH92" s="86"/>
+      <c r="AI92" s="86"/>
       <c r="AJ92" s="31"/>
       <c r="AO92" s="30">
         <v>19</v>
@@ -7188,32 +7321,32 @@
     <row r="93" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="39"/>
       <c r="B93" s="39"/>
-      <c r="C93" s="113"/>
-      <c r="D93" s="113"/>
-      <c r="E93" s="113"/>
-      <c r="F93" s="113"/>
-      <c r="G93" s="113"/>
-      <c r="H93" s="113"/>
-      <c r="I93" s="113"/>
-      <c r="J93" s="113"/>
-      <c r="K93" s="113"/>
-      <c r="L93" s="113"/>
-      <c r="M93" s="113"/>
+      <c r="C93" s="108"/>
+      <c r="D93" s="108"/>
+      <c r="E93" s="108"/>
+      <c r="F93" s="108"/>
+      <c r="G93" s="108"/>
+      <c r="H93" s="108"/>
+      <c r="I93" s="108"/>
+      <c r="J93" s="108"/>
+      <c r="K93" s="108"/>
+      <c r="L93" s="108"/>
+      <c r="M93" s="108"/>
       <c r="N93" s="50"/>
       <c r="O93" s="50"/>
       <c r="P93" s="50"/>
       <c r="Q93" s="50"/>
       <c r="R93" s="51"/>
-      <c r="S93" s="118" t="s">
+      <c r="S93" s="102" t="s">
         <v>182</v>
       </c>
-      <c r="T93" s="119"/>
-      <c r="U93" s="119"/>
-      <c r="V93" s="119"/>
-      <c r="W93" s="119"/>
-      <c r="X93" s="119"/>
-      <c r="Y93" s="119"/>
-      <c r="Z93" s="119"/>
+      <c r="T93" s="181"/>
+      <c r="U93" s="181"/>
+      <c r="V93" s="181"/>
+      <c r="W93" s="181"/>
+      <c r="X93" s="181"/>
+      <c r="Y93" s="181"/>
+      <c r="Z93" s="181"/>
       <c r="AA93" s="4"/>
       <c r="AB93" s="40"/>
       <c r="AC93" s="40"/>
@@ -7249,35 +7382,35 @@
       <c r="BH93" s="43"/>
     </row>
     <row r="94" spans="1:60" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="130"/>
-      <c r="B94" s="130"/>
-      <c r="C94" s="156" t="s">
+      <c r="A94" s="75"/>
+      <c r="B94" s="75"/>
+      <c r="C94" s="216" t="s">
         <v>127</v>
       </c>
-      <c r="D94" s="157"/>
-      <c r="E94" s="157"/>
-      <c r="F94" s="157"/>
-      <c r="G94" s="157"/>
-      <c r="H94" s="157"/>
-      <c r="I94" s="157"/>
-      <c r="J94" s="157"/>
-      <c r="K94" s="157"/>
-      <c r="L94" s="157"/>
+      <c r="D94" s="217"/>
+      <c r="E94" s="217"/>
+      <c r="F94" s="217"/>
+      <c r="G94" s="217"/>
+      <c r="H94" s="217"/>
+      <c r="I94" s="217"/>
+      <c r="J94" s="217"/>
+      <c r="K94" s="217"/>
+      <c r="L94" s="217"/>
       <c r="M94" s="42"/>
       <c r="N94" s="42"/>
-      <c r="O94" s="114" t="s">
+      <c r="O94" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="P94" s="115"/>
-      <c r="Q94" s="116"/>
-      <c r="S94" s="117"/>
-      <c r="T94" s="117"/>
-      <c r="U94" s="117"/>
-      <c r="V94" s="117"/>
-      <c r="W94" s="117"/>
-      <c r="X94" s="117"/>
-      <c r="Y94" s="117"/>
-      <c r="Z94" s="117"/>
+      <c r="P94" s="105"/>
+      <c r="Q94" s="106"/>
+      <c r="S94" s="74"/>
+      <c r="T94" s="74"/>
+      <c r="U94" s="74"/>
+      <c r="V94" s="74"/>
+      <c r="W94" s="74"/>
+      <c r="X94" s="74"/>
+      <c r="Y94" s="74"/>
+      <c r="Z94" s="74"/>
       <c r="AB94" s="47"/>
       <c r="AC94" s="47"/>
       <c r="AD94" s="47"/>
@@ -7327,14 +7460,14 @@
       <c r="O95" s="42"/>
       <c r="P95" s="42"/>
       <c r="Q95" s="42"/>
-      <c r="S95" s="153"/>
-      <c r="T95" s="230"/>
-      <c r="U95" s="230"/>
-      <c r="V95" s="230"/>
-      <c r="W95" s="230"/>
-      <c r="X95" s="230"/>
-      <c r="Y95" s="230"/>
-      <c r="Z95" s="230"/>
+      <c r="S95" s="76"/>
+      <c r="T95" s="77"/>
+      <c r="U95" s="77"/>
+      <c r="V95" s="77"/>
+      <c r="W95" s="77"/>
+      <c r="X95" s="77"/>
+      <c r="Y95" s="77"/>
+      <c r="Z95" s="77"/>
       <c r="AB95" s="47"/>
       <c r="AC95" s="47"/>
       <c r="AD95" s="47"/>
@@ -7371,43 +7504,43 @@
       <c r="BH95" s="43"/>
     </row>
     <row r="96" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="A96" s="149" t="s">
+      <c r="A96" s="72" t="s">
         <v>139</v>
       </c>
-      <c r="B96" s="149"/>
-      <c r="C96" s="82"/>
-      <c r="D96" s="83"/>
-      <c r="E96" s="83"/>
-      <c r="F96" s="83"/>
-      <c r="G96" s="83"/>
-      <c r="H96" s="83"/>
-      <c r="I96" s="84"/>
+      <c r="B96" s="72"/>
+      <c r="C96" s="78"/>
+      <c r="D96" s="79"/>
+      <c r="E96" s="79"/>
+      <c r="F96" s="79"/>
+      <c r="G96" s="79"/>
+      <c r="H96" s="79"/>
+      <c r="I96" s="80"/>
       <c r="J96" s="3"/>
-      <c r="K96" s="79"/>
-      <c r="L96" s="80"/>
-      <c r="M96" s="80"/>
-      <c r="N96" s="80"/>
-      <c r="O96" s="80"/>
-      <c r="P96" s="80"/>
-      <c r="Q96" s="81"/>
+      <c r="K96" s="87"/>
+      <c r="L96" s="88"/>
+      <c r="M96" s="88"/>
+      <c r="N96" s="88"/>
+      <c r="O96" s="88"/>
+      <c r="P96" s="88"/>
+      <c r="Q96" s="89"/>
       <c r="R96" s="4"/>
-      <c r="S96" s="120"/>
-      <c r="T96" s="121"/>
-      <c r="U96" s="121"/>
-      <c r="V96" s="121"/>
-      <c r="W96" s="121"/>
-      <c r="X96" s="121"/>
-      <c r="Y96" s="121"/>
-      <c r="Z96" s="122"/>
+      <c r="S96" s="90"/>
+      <c r="T96" s="91"/>
+      <c r="U96" s="91"/>
+      <c r="V96" s="91"/>
+      <c r="W96" s="91"/>
+      <c r="X96" s="91"/>
+      <c r="Y96" s="91"/>
+      <c r="Z96" s="92"/>
       <c r="AA96" s="4"/>
-      <c r="AB96" s="131"/>
-      <c r="AC96" s="132"/>
-      <c r="AD96" s="132"/>
-      <c r="AE96" s="132"/>
-      <c r="AF96" s="132"/>
-      <c r="AG96" s="132"/>
-      <c r="AH96" s="132"/>
-      <c r="AI96" s="133"/>
+      <c r="AB96" s="93"/>
+      <c r="AC96" s="94"/>
+      <c r="AD96" s="94"/>
+      <c r="AE96" s="94"/>
+      <c r="AF96" s="94"/>
+      <c r="AG96" s="94"/>
+      <c r="AH96" s="94"/>
+      <c r="AI96" s="95"/>
       <c r="AJ96" s="31"/>
       <c r="AO96" s="30">
         <v>16</v>
@@ -7438,47 +7571,47 @@
     <row r="97" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
-      <c r="C97" s="136" t="s">
+      <c r="C97" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="D97" s="136"/>
-      <c r="E97" s="136"/>
-      <c r="F97" s="136"/>
-      <c r="G97" s="136"/>
-      <c r="H97" s="136"/>
-      <c r="I97" s="136"/>
+      <c r="D97" s="85"/>
+      <c r="E97" s="85"/>
+      <c r="F97" s="85"/>
+      <c r="G97" s="85"/>
+      <c r="H97" s="85"/>
+      <c r="I97" s="85"/>
       <c r="J97" s="53"/>
-      <c r="K97" s="137" t="s">
+      <c r="K97" s="99" t="s">
         <v>50</v>
       </c>
-      <c r="L97" s="137"/>
-      <c r="M97" s="137"/>
-      <c r="N97" s="137"/>
-      <c r="O97" s="137"/>
-      <c r="P97" s="137"/>
-      <c r="Q97" s="137"/>
+      <c r="L97" s="99"/>
+      <c r="M97" s="99"/>
+      <c r="N97" s="99"/>
+      <c r="O97" s="99"/>
+      <c r="P97" s="99"/>
+      <c r="Q97" s="99"/>
       <c r="R97" s="4"/>
-      <c r="S97" s="150" t="s">
+      <c r="S97" s="101" t="s">
         <v>47</v>
       </c>
-      <c r="T97" s="150"/>
-      <c r="U97" s="144"/>
-      <c r="V97" s="145"/>
-      <c r="W97" s="151" t="s">
+      <c r="T97" s="101"/>
+      <c r="U97" s="134"/>
+      <c r="V97" s="135"/>
+      <c r="W97" s="136" t="s">
         <v>48</v>
       </c>
-      <c r="X97" s="152"/>
-      <c r="Y97" s="144"/>
-      <c r="Z97" s="145"/>
+      <c r="X97" s="137"/>
+      <c r="Y97" s="134"/>
+      <c r="Z97" s="135"/>
       <c r="AA97" s="4"/>
-      <c r="AB97" s="134"/>
-      <c r="AC97" s="105"/>
-      <c r="AD97" s="105"/>
-      <c r="AE97" s="105"/>
-      <c r="AF97" s="105"/>
-      <c r="AG97" s="105"/>
-      <c r="AH97" s="105"/>
-      <c r="AI97" s="135"/>
+      <c r="AB97" s="96"/>
+      <c r="AC97" s="97"/>
+      <c r="AD97" s="97"/>
+      <c r="AE97" s="97"/>
+      <c r="AF97" s="97"/>
+      <c r="AG97" s="97"/>
+      <c r="AH97" s="97"/>
+      <c r="AI97" s="98"/>
       <c r="AJ97" s="31" t="s">
         <v>123</v>
       </c>
@@ -7518,24 +7651,24 @@
       <c r="H98" s="46"/>
       <c r="I98" s="46"/>
       <c r="J98" s="46"/>
-      <c r="K98" s="138"/>
-      <c r="L98" s="138"/>
-      <c r="M98" s="138"/>
-      <c r="N98" s="138"/>
-      <c r="O98" s="138"/>
-      <c r="P98" s="138"/>
-      <c r="Q98" s="138"/>
+      <c r="K98" s="100"/>
+      <c r="L98" s="100"/>
+      <c r="M98" s="100"/>
+      <c r="N98" s="100"/>
+      <c r="O98" s="100"/>
+      <c r="P98" s="100"/>
+      <c r="Q98" s="100"/>
       <c r="R98" s="4"/>
-      <c r="S98" s="153" t="s">
+      <c r="S98" s="76" t="s">
         <v>124</v>
       </c>
-      <c r="T98" s="154"/>
-      <c r="U98" s="154"/>
-      <c r="V98" s="154"/>
-      <c r="W98" s="154"/>
-      <c r="X98" s="154"/>
-      <c r="Y98" s="154"/>
-      <c r="Z98" s="154"/>
+      <c r="T98" s="138"/>
+      <c r="U98" s="138"/>
+      <c r="V98" s="138"/>
+      <c r="W98" s="138"/>
+      <c r="X98" s="138"/>
+      <c r="Y98" s="138"/>
+      <c r="Z98" s="138"/>
       <c r="AA98" s="4"/>
       <c r="AB98" s="47"/>
       <c r="AC98" s="47"/>
@@ -7567,45 +7700,45 @@
       <c r="BH98" s="43"/>
     </row>
     <row r="99" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="106"/>
-      <c r="B99" s="155"/>
-      <c r="C99" s="112" t="s">
+      <c r="A99" s="168"/>
+      <c r="B99" s="169"/>
+      <c r="C99" s="107" t="s">
         <v>183</v>
       </c>
-      <c r="D99" s="113"/>
-      <c r="E99" s="113"/>
-      <c r="F99" s="113"/>
-      <c r="G99" s="113"/>
-      <c r="H99" s="113"/>
-      <c r="I99" s="113"/>
-      <c r="J99" s="113"/>
-      <c r="K99" s="113"/>
-      <c r="L99" s="113"/>
-      <c r="M99" s="113"/>
+      <c r="D99" s="108"/>
+      <c r="E99" s="108"/>
+      <c r="F99" s="108"/>
+      <c r="G99" s="108"/>
+      <c r="H99" s="108"/>
+      <c r="I99" s="108"/>
+      <c r="J99" s="108"/>
+      <c r="K99" s="108"/>
+      <c r="L99" s="108"/>
+      <c r="M99" s="108"/>
       <c r="N99" s="50"/>
-      <c r="O99" s="114" t="s">
+      <c r="O99" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="P99" s="115"/>
-      <c r="Q99" s="116"/>
+      <c r="P99" s="105"/>
+      <c r="Q99" s="106"/>
       <c r="R99" s="56"/>
-      <c r="S99" s="117"/>
-      <c r="T99" s="117"/>
-      <c r="U99" s="117"/>
-      <c r="V99" s="117"/>
-      <c r="W99" s="117"/>
-      <c r="X99" s="117"/>
-      <c r="Y99" s="117"/>
-      <c r="Z99" s="117"/>
+      <c r="S99" s="74"/>
+      <c r="T99" s="74"/>
+      <c r="U99" s="74"/>
+      <c r="V99" s="74"/>
+      <c r="W99" s="74"/>
+      <c r="X99" s="74"/>
+      <c r="Y99" s="74"/>
+      <c r="Z99" s="74"/>
       <c r="AA99" s="4"/>
-      <c r="AB99" s="139"/>
-      <c r="AC99" s="139"/>
-      <c r="AD99" s="139"/>
-      <c r="AE99" s="139"/>
-      <c r="AF99" s="139"/>
-      <c r="AG99" s="139"/>
-      <c r="AH99" s="139"/>
-      <c r="AI99" s="139"/>
+      <c r="AB99" s="86"/>
+      <c r="AC99" s="86"/>
+      <c r="AD99" s="86"/>
+      <c r="AE99" s="86"/>
+      <c r="AF99" s="86"/>
+      <c r="AG99" s="86"/>
+      <c r="AH99" s="86"/>
+      <c r="AI99" s="86"/>
       <c r="AJ99" s="31"/>
       <c r="AO99" s="30">
         <v>19</v>
@@ -7636,32 +7769,32 @@
     <row r="100" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="39"/>
       <c r="B100" s="39"/>
-      <c r="C100" s="113"/>
-      <c r="D100" s="113"/>
-      <c r="E100" s="113"/>
-      <c r="F100" s="113"/>
-      <c r="G100" s="113"/>
-      <c r="H100" s="113"/>
-      <c r="I100" s="113"/>
-      <c r="J100" s="113"/>
-      <c r="K100" s="113"/>
-      <c r="L100" s="113"/>
-      <c r="M100" s="113"/>
+      <c r="C100" s="108"/>
+      <c r="D100" s="108"/>
+      <c r="E100" s="108"/>
+      <c r="F100" s="108"/>
+      <c r="G100" s="108"/>
+      <c r="H100" s="108"/>
+      <c r="I100" s="108"/>
+      <c r="J100" s="108"/>
+      <c r="K100" s="108"/>
+      <c r="L100" s="108"/>
+      <c r="M100" s="108"/>
       <c r="N100" s="50"/>
       <c r="O100" s="50"/>
       <c r="P100" s="50"/>
       <c r="Q100" s="50"/>
       <c r="R100" s="51"/>
-      <c r="S100" s="118" t="s">
+      <c r="S100" s="102" t="s">
         <v>182</v>
       </c>
-      <c r="T100" s="119"/>
-      <c r="U100" s="119"/>
-      <c r="V100" s="119"/>
-      <c r="W100" s="119"/>
-      <c r="X100" s="119"/>
-      <c r="Y100" s="119"/>
-      <c r="Z100" s="119"/>
+      <c r="T100" s="181"/>
+      <c r="U100" s="181"/>
+      <c r="V100" s="181"/>
+      <c r="W100" s="181"/>
+      <c r="X100" s="181"/>
+      <c r="Y100" s="181"/>
+      <c r="Z100" s="181"/>
       <c r="AA100" s="4"/>
       <c r="AB100" s="40"/>
       <c r="AC100" s="40"/>
@@ -7697,35 +7830,35 @@
       <c r="BH100" s="43"/>
     </row>
     <row r="101" spans="1:60" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="130"/>
-      <c r="B101" s="130"/>
-      <c r="C101" s="76" t="s">
+      <c r="A101" s="75"/>
+      <c r="B101" s="75"/>
+      <c r="C101" s="109" t="s">
         <v>127</v>
       </c>
-      <c r="D101" s="77"/>
-      <c r="E101" s="77"/>
-      <c r="F101" s="77"/>
-      <c r="G101" s="77"/>
-      <c r="H101" s="77"/>
-      <c r="I101" s="77"/>
-      <c r="J101" s="77"/>
-      <c r="K101" s="77"/>
-      <c r="L101" s="77"/>
-      <c r="M101" s="77"/>
+      <c r="D101" s="110"/>
+      <c r="E101" s="110"/>
+      <c r="F101" s="110"/>
+      <c r="G101" s="110"/>
+      <c r="H101" s="110"/>
+      <c r="I101" s="110"/>
+      <c r="J101" s="110"/>
+      <c r="K101" s="110"/>
+      <c r="L101" s="110"/>
+      <c r="M101" s="110"/>
       <c r="N101" s="42"/>
-      <c r="O101" s="114" t="s">
+      <c r="O101" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="P101" s="115"/>
-      <c r="Q101" s="116"/>
-      <c r="S101" s="117"/>
-      <c r="T101" s="117"/>
-      <c r="U101" s="117"/>
-      <c r="V101" s="117"/>
-      <c r="W101" s="117"/>
-      <c r="X101" s="117"/>
-      <c r="Y101" s="117"/>
-      <c r="Z101" s="117"/>
+      <c r="P101" s="105"/>
+      <c r="Q101" s="106"/>
+      <c r="S101" s="74"/>
+      <c r="T101" s="74"/>
+      <c r="U101" s="74"/>
+      <c r="V101" s="74"/>
+      <c r="W101" s="74"/>
+      <c r="X101" s="74"/>
+      <c r="Y101" s="74"/>
+      <c r="Z101" s="74"/>
       <c r="AB101" s="47"/>
       <c r="AC101" s="47"/>
       <c r="AD101" s="47"/>
@@ -7817,43 +7950,43 @@
       <c r="BH102" s="43"/>
     </row>
     <row r="103" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="A103" s="149" t="s">
+      <c r="A103" s="72" t="s">
         <v>140</v>
       </c>
-      <c r="B103" s="149"/>
-      <c r="C103" s="82"/>
-      <c r="D103" s="83"/>
-      <c r="E103" s="83"/>
-      <c r="F103" s="83"/>
-      <c r="G103" s="83"/>
-      <c r="H103" s="83"/>
-      <c r="I103" s="84"/>
+      <c r="B103" s="72"/>
+      <c r="C103" s="78"/>
+      <c r="D103" s="79"/>
+      <c r="E103" s="79"/>
+      <c r="F103" s="79"/>
+      <c r="G103" s="79"/>
+      <c r="H103" s="79"/>
+      <c r="I103" s="80"/>
       <c r="J103" s="3"/>
-      <c r="K103" s="79"/>
-      <c r="L103" s="80"/>
-      <c r="M103" s="80"/>
-      <c r="N103" s="80"/>
-      <c r="O103" s="80"/>
-      <c r="P103" s="80"/>
-      <c r="Q103" s="81"/>
+      <c r="K103" s="87"/>
+      <c r="L103" s="88"/>
+      <c r="M103" s="88"/>
+      <c r="N103" s="88"/>
+      <c r="O103" s="88"/>
+      <c r="P103" s="88"/>
+      <c r="Q103" s="89"/>
       <c r="R103" s="4"/>
-      <c r="S103" s="120"/>
-      <c r="T103" s="121"/>
-      <c r="U103" s="121"/>
-      <c r="V103" s="121"/>
-      <c r="W103" s="121"/>
-      <c r="X103" s="121"/>
-      <c r="Y103" s="121"/>
-      <c r="Z103" s="122"/>
+      <c r="S103" s="90"/>
+      <c r="T103" s="91"/>
+      <c r="U103" s="91"/>
+      <c r="V103" s="91"/>
+      <c r="W103" s="91"/>
+      <c r="X103" s="91"/>
+      <c r="Y103" s="91"/>
+      <c r="Z103" s="92"/>
       <c r="AA103" s="4"/>
-      <c r="AB103" s="131"/>
-      <c r="AC103" s="132"/>
-      <c r="AD103" s="132"/>
-      <c r="AE103" s="132"/>
-      <c r="AF103" s="132"/>
-      <c r="AG103" s="132"/>
-      <c r="AH103" s="132"/>
-      <c r="AI103" s="133"/>
+      <c r="AB103" s="93"/>
+      <c r="AC103" s="94"/>
+      <c r="AD103" s="94"/>
+      <c r="AE103" s="94"/>
+      <c r="AF103" s="94"/>
+      <c r="AG103" s="94"/>
+      <c r="AH103" s="94"/>
+      <c r="AI103" s="95"/>
       <c r="AJ103" s="31"/>
       <c r="AO103" s="30">
         <v>16</v>
@@ -7884,47 +8017,47 @@
     <row r="104" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
-      <c r="C104" s="136" t="s">
+      <c r="C104" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="D104" s="136"/>
-      <c r="E104" s="136"/>
-      <c r="F104" s="136"/>
-      <c r="G104" s="136"/>
-      <c r="H104" s="136"/>
-      <c r="I104" s="136"/>
+      <c r="D104" s="85"/>
+      <c r="E104" s="85"/>
+      <c r="F104" s="85"/>
+      <c r="G104" s="85"/>
+      <c r="H104" s="85"/>
+      <c r="I104" s="85"/>
       <c r="J104" s="53"/>
-      <c r="K104" s="137" t="s">
+      <c r="K104" s="99" t="s">
         <v>50</v>
       </c>
-      <c r="L104" s="137"/>
-      <c r="M104" s="137"/>
-      <c r="N104" s="137"/>
-      <c r="O104" s="137"/>
-      <c r="P104" s="137"/>
-      <c r="Q104" s="137"/>
+      <c r="L104" s="99"/>
+      <c r="M104" s="99"/>
+      <c r="N104" s="99"/>
+      <c r="O104" s="99"/>
+      <c r="P104" s="99"/>
+      <c r="Q104" s="99"/>
       <c r="R104" s="4"/>
-      <c r="S104" s="150" t="s">
+      <c r="S104" s="101" t="s">
         <v>47</v>
       </c>
-      <c r="T104" s="150"/>
-      <c r="U104" s="144"/>
-      <c r="V104" s="145"/>
-      <c r="W104" s="151" t="s">
+      <c r="T104" s="101"/>
+      <c r="U104" s="134"/>
+      <c r="V104" s="135"/>
+      <c r="W104" s="136" t="s">
         <v>48</v>
       </c>
-      <c r="X104" s="152"/>
-      <c r="Y104" s="144"/>
-      <c r="Z104" s="145"/>
+      <c r="X104" s="137"/>
+      <c r="Y104" s="134"/>
+      <c r="Z104" s="135"/>
       <c r="AA104" s="4"/>
-      <c r="AB104" s="134"/>
-      <c r="AC104" s="105"/>
-      <c r="AD104" s="105"/>
-      <c r="AE104" s="105"/>
-      <c r="AF104" s="105"/>
-      <c r="AG104" s="105"/>
-      <c r="AH104" s="105"/>
-      <c r="AI104" s="135"/>
+      <c r="AB104" s="96"/>
+      <c r="AC104" s="97"/>
+      <c r="AD104" s="97"/>
+      <c r="AE104" s="97"/>
+      <c r="AF104" s="97"/>
+      <c r="AG104" s="97"/>
+      <c r="AH104" s="97"/>
+      <c r="AI104" s="98"/>
       <c r="AJ104" s="31" t="s">
         <v>123</v>
       </c>
@@ -7964,24 +8097,24 @@
       <c r="H105" s="46"/>
       <c r="I105" s="46"/>
       <c r="J105" s="46"/>
-      <c r="K105" s="138"/>
-      <c r="L105" s="138"/>
-      <c r="M105" s="138"/>
-      <c r="N105" s="138"/>
-      <c r="O105" s="138"/>
-      <c r="P105" s="138"/>
-      <c r="Q105" s="138"/>
+      <c r="K105" s="100"/>
+      <c r="L105" s="100"/>
+      <c r="M105" s="100"/>
+      <c r="N105" s="100"/>
+      <c r="O105" s="100"/>
+      <c r="P105" s="100"/>
+      <c r="Q105" s="100"/>
       <c r="R105" s="4"/>
-      <c r="S105" s="153" t="s">
+      <c r="S105" s="76" t="s">
         <v>124</v>
       </c>
-      <c r="T105" s="154"/>
-      <c r="U105" s="154"/>
-      <c r="V105" s="154"/>
-      <c r="W105" s="154"/>
-      <c r="X105" s="154"/>
-      <c r="Y105" s="154"/>
-      <c r="Z105" s="154"/>
+      <c r="T105" s="138"/>
+      <c r="U105" s="138"/>
+      <c r="V105" s="138"/>
+      <c r="W105" s="138"/>
+      <c r="X105" s="138"/>
+      <c r="Y105" s="138"/>
+      <c r="Z105" s="138"/>
       <c r="AA105" s="4"/>
       <c r="AB105" s="47"/>
       <c r="AC105" s="47"/>
@@ -8013,45 +8146,45 @@
       <c r="BH105" s="43"/>
     </row>
     <row r="106" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="106"/>
-      <c r="B106" s="155"/>
-      <c r="C106" s="112" t="s">
+      <c r="A106" s="168"/>
+      <c r="B106" s="169"/>
+      <c r="C106" s="107" t="s">
         <v>183</v>
       </c>
-      <c r="D106" s="113"/>
-      <c r="E106" s="113"/>
-      <c r="F106" s="113"/>
-      <c r="G106" s="113"/>
-      <c r="H106" s="113"/>
-      <c r="I106" s="113"/>
-      <c r="J106" s="113"/>
-      <c r="K106" s="113"/>
-      <c r="L106" s="113"/>
-      <c r="M106" s="113"/>
+      <c r="D106" s="108"/>
+      <c r="E106" s="108"/>
+      <c r="F106" s="108"/>
+      <c r="G106" s="108"/>
+      <c r="H106" s="108"/>
+      <c r="I106" s="108"/>
+      <c r="J106" s="108"/>
+      <c r="K106" s="108"/>
+      <c r="L106" s="108"/>
+      <c r="M106" s="108"/>
       <c r="N106" s="50"/>
-      <c r="O106" s="114" t="s">
+      <c r="O106" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="P106" s="115"/>
-      <c r="Q106" s="116"/>
+      <c r="P106" s="105"/>
+      <c r="Q106" s="106"/>
       <c r="R106" s="56"/>
-      <c r="S106" s="117"/>
-      <c r="T106" s="117"/>
-      <c r="U106" s="117"/>
-      <c r="V106" s="117"/>
-      <c r="W106" s="117"/>
-      <c r="X106" s="117"/>
-      <c r="Y106" s="117"/>
-      <c r="Z106" s="117"/>
+      <c r="S106" s="74"/>
+      <c r="T106" s="74"/>
+      <c r="U106" s="74"/>
+      <c r="V106" s="74"/>
+      <c r="W106" s="74"/>
+      <c r="X106" s="74"/>
+      <c r="Y106" s="74"/>
+      <c r="Z106" s="74"/>
       <c r="AA106" s="4"/>
-      <c r="AB106" s="139"/>
-      <c r="AC106" s="139"/>
-      <c r="AD106" s="139"/>
-      <c r="AE106" s="139"/>
-      <c r="AF106" s="139"/>
-      <c r="AG106" s="139"/>
-      <c r="AH106" s="139"/>
-      <c r="AI106" s="139"/>
+      <c r="AB106" s="86"/>
+      <c r="AC106" s="86"/>
+      <c r="AD106" s="86"/>
+      <c r="AE106" s="86"/>
+      <c r="AF106" s="86"/>
+      <c r="AG106" s="86"/>
+      <c r="AH106" s="86"/>
+      <c r="AI106" s="86"/>
       <c r="AJ106" s="31"/>
       <c r="AO106" s="30">
         <v>19</v>
@@ -8082,32 +8215,32 @@
     <row r="107" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="39"/>
       <c r="B107" s="39"/>
-      <c r="C107" s="113"/>
-      <c r="D107" s="113"/>
-      <c r="E107" s="113"/>
-      <c r="F107" s="113"/>
-      <c r="G107" s="113"/>
-      <c r="H107" s="113"/>
-      <c r="I107" s="113"/>
-      <c r="J107" s="113"/>
-      <c r="K107" s="113"/>
-      <c r="L107" s="113"/>
-      <c r="M107" s="113"/>
+      <c r="C107" s="108"/>
+      <c r="D107" s="108"/>
+      <c r="E107" s="108"/>
+      <c r="F107" s="108"/>
+      <c r="G107" s="108"/>
+      <c r="H107" s="108"/>
+      <c r="I107" s="108"/>
+      <c r="J107" s="108"/>
+      <c r="K107" s="108"/>
+      <c r="L107" s="108"/>
+      <c r="M107" s="108"/>
       <c r="N107" s="50"/>
       <c r="O107" s="50"/>
       <c r="P107" s="50"/>
       <c r="Q107" s="50"/>
       <c r="R107" s="51"/>
-      <c r="S107" s="118" t="s">
+      <c r="S107" s="102" t="s">
         <v>182</v>
       </c>
-      <c r="T107" s="119"/>
-      <c r="U107" s="119"/>
-      <c r="V107" s="119"/>
-      <c r="W107" s="119"/>
-      <c r="X107" s="119"/>
-      <c r="Y107" s="119"/>
-      <c r="Z107" s="119"/>
+      <c r="T107" s="181"/>
+      <c r="U107" s="181"/>
+      <c r="V107" s="181"/>
+      <c r="W107" s="181"/>
+      <c r="X107" s="181"/>
+      <c r="Y107" s="181"/>
+      <c r="Z107" s="181"/>
       <c r="AA107" s="4"/>
       <c r="AB107" s="40"/>
       <c r="AC107" s="40"/>
@@ -8143,43 +8276,43 @@
       <c r="BH107" s="43"/>
     </row>
     <row r="108" spans="1:60" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="130"/>
-      <c r="B108" s="130"/>
-      <c r="C108" s="76" t="s">
+      <c r="A108" s="75"/>
+      <c r="B108" s="75"/>
+      <c r="C108" s="109" t="s">
         <v>127</v>
       </c>
-      <c r="D108" s="77"/>
-      <c r="E108" s="77"/>
-      <c r="F108" s="77"/>
-      <c r="G108" s="77"/>
-      <c r="H108" s="77"/>
-      <c r="I108" s="77"/>
-      <c r="J108" s="77"/>
-      <c r="K108" s="77"/>
-      <c r="L108" s="77"/>
-      <c r="M108" s="77"/>
+      <c r="D108" s="110"/>
+      <c r="E108" s="110"/>
+      <c r="F108" s="110"/>
+      <c r="G108" s="110"/>
+      <c r="H108" s="110"/>
+      <c r="I108" s="110"/>
+      <c r="J108" s="110"/>
+      <c r="K108" s="110"/>
+      <c r="L108" s="110"/>
+      <c r="M108" s="110"/>
       <c r="N108" s="42"/>
-      <c r="O108" s="114" t="s">
+      <c r="O108" s="104" t="s">
         <v>38</v>
       </c>
-      <c r="P108" s="115"/>
-      <c r="Q108" s="116"/>
-      <c r="S108" s="117"/>
-      <c r="T108" s="117"/>
-      <c r="U108" s="117"/>
-      <c r="V108" s="117"/>
-      <c r="W108" s="117"/>
-      <c r="X108" s="117"/>
-      <c r="Y108" s="117"/>
-      <c r="Z108" s="117"/>
-      <c r="AB108" s="153"/>
-      <c r="AC108" s="153"/>
-      <c r="AD108" s="153"/>
-      <c r="AE108" s="153"/>
-      <c r="AF108" s="153"/>
-      <c r="AG108" s="153"/>
-      <c r="AH108" s="153"/>
-      <c r="AI108" s="153"/>
+      <c r="P108" s="105"/>
+      <c r="Q108" s="106"/>
+      <c r="S108" s="74"/>
+      <c r="T108" s="74"/>
+      <c r="U108" s="74"/>
+      <c r="V108" s="74"/>
+      <c r="W108" s="74"/>
+      <c r="X108" s="74"/>
+      <c r="Y108" s="74"/>
+      <c r="Z108" s="74"/>
+      <c r="AB108" s="76"/>
+      <c r="AC108" s="76"/>
+      <c r="AD108" s="76"/>
+      <c r="AE108" s="76"/>
+      <c r="AF108" s="76"/>
+      <c r="AG108" s="76"/>
+      <c r="AH108" s="76"/>
+      <c r="AI108" s="76"/>
       <c r="AJ108" s="57"/>
       <c r="AK108" s="58"/>
       <c r="AL108" s="58"/>
@@ -8208,39 +8341,39 @@
     <row r="109" spans="1:60" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
-      <c r="C109" s="146"/>
-      <c r="D109" s="146"/>
-      <c r="E109" s="146"/>
-      <c r="F109" s="146"/>
-      <c r="G109" s="146"/>
-      <c r="H109" s="146"/>
-      <c r="I109" s="146"/>
+      <c r="C109" s="219"/>
+      <c r="D109" s="219"/>
+      <c r="E109" s="219"/>
+      <c r="F109" s="219"/>
+      <c r="G109" s="219"/>
+      <c r="H109" s="219"/>
+      <c r="I109" s="219"/>
       <c r="J109" s="53"/>
-      <c r="K109" s="138"/>
-      <c r="L109" s="138"/>
-      <c r="M109" s="138"/>
-      <c r="N109" s="138"/>
-      <c r="O109" s="138"/>
-      <c r="P109" s="138"/>
-      <c r="Q109" s="138"/>
+      <c r="K109" s="100"/>
+      <c r="L109" s="100"/>
+      <c r="M109" s="100"/>
+      <c r="N109" s="100"/>
+      <c r="O109" s="100"/>
+      <c r="P109" s="100"/>
+      <c r="Q109" s="100"/>
       <c r="R109" s="4"/>
-      <c r="S109" s="147"/>
-      <c r="T109" s="147"/>
-      <c r="U109" s="148"/>
-      <c r="V109" s="148"/>
-      <c r="W109" s="231"/>
-      <c r="X109" s="231"/>
-      <c r="Y109" s="148"/>
-      <c r="Z109" s="148"/>
+      <c r="S109" s="220"/>
+      <c r="T109" s="220"/>
+      <c r="U109" s="82"/>
+      <c r="V109" s="82"/>
+      <c r="W109" s="81"/>
+      <c r="X109" s="81"/>
+      <c r="Y109" s="82"/>
+      <c r="Z109" s="82"/>
       <c r="AA109" s="4"/>
-      <c r="AB109" s="153"/>
-      <c r="AC109" s="153"/>
-      <c r="AD109" s="153"/>
-      <c r="AE109" s="153"/>
-      <c r="AF109" s="153"/>
-      <c r="AG109" s="153"/>
-      <c r="AH109" s="153"/>
-      <c r="AI109" s="153"/>
+      <c r="AB109" s="76"/>
+      <c r="AC109" s="76"/>
+      <c r="AD109" s="76"/>
+      <c r="AE109" s="76"/>
+      <c r="AF109" s="76"/>
+      <c r="AG109" s="76"/>
+      <c r="AH109" s="76"/>
+      <c r="AI109" s="76"/>
       <c r="AJ109" s="31" t="s">
         <v>123</v>
       </c>
@@ -8271,43 +8404,43 @@
       <c r="BH109" s="43"/>
     </row>
     <row r="110" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="A110" s="149" t="s">
+      <c r="A110" s="72" t="s">
         <v>141</v>
       </c>
-      <c r="B110" s="229"/>
-      <c r="C110" s="82"/>
-      <c r="D110" s="83"/>
-      <c r="E110" s="83"/>
-      <c r="F110" s="83"/>
-      <c r="G110" s="83"/>
-      <c r="H110" s="83"/>
-      <c r="I110" s="84"/>
+      <c r="B110" s="73"/>
+      <c r="C110" s="78"/>
+      <c r="D110" s="79"/>
+      <c r="E110" s="79"/>
+      <c r="F110" s="79"/>
+      <c r="G110" s="79"/>
+      <c r="H110" s="79"/>
+      <c r="I110" s="80"/>
       <c r="J110" s="3"/>
-      <c r="K110" s="79"/>
-      <c r="L110" s="80"/>
-      <c r="M110" s="80"/>
-      <c r="N110" s="80"/>
-      <c r="O110" s="80"/>
-      <c r="P110" s="80"/>
-      <c r="Q110" s="81"/>
+      <c r="K110" s="87"/>
+      <c r="L110" s="88"/>
+      <c r="M110" s="88"/>
+      <c r="N110" s="88"/>
+      <c r="O110" s="88"/>
+      <c r="P110" s="88"/>
+      <c r="Q110" s="89"/>
       <c r="R110" s="4"/>
-      <c r="S110" s="120"/>
-      <c r="T110" s="140"/>
-      <c r="U110" s="140"/>
-      <c r="V110" s="140"/>
-      <c r="W110" s="140"/>
-      <c r="X110" s="140"/>
-      <c r="Y110" s="140"/>
-      <c r="Z110" s="141"/>
+      <c r="S110" s="90"/>
+      <c r="T110" s="221"/>
+      <c r="U110" s="221"/>
+      <c r="V110" s="221"/>
+      <c r="W110" s="221"/>
+      <c r="X110" s="221"/>
+      <c r="Y110" s="221"/>
+      <c r="Z110" s="222"/>
       <c r="AA110" s="4"/>
-      <c r="AB110" s="131"/>
-      <c r="AC110" s="132"/>
-      <c r="AD110" s="132"/>
-      <c r="AE110" s="132"/>
-      <c r="AF110" s="132"/>
-      <c r="AG110" s="132"/>
-      <c r="AH110" s="132"/>
-      <c r="AI110" s="133"/>
+      <c r="AB110" s="93"/>
+      <c r="AC110" s="94"/>
+      <c r="AD110" s="94"/>
+      <c r="AE110" s="94"/>
+      <c r="AF110" s="94"/>
+      <c r="AG110" s="94"/>
+      <c r="AH110" s="94"/>
+      <c r="AI110" s="95"/>
       <c r="AJ110" s="31"/>
       <c r="AO110" s="30">
         <v>16</v>
@@ -8338,47 +8471,47 @@
     <row r="111" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
-      <c r="C111" s="136" t="s">
+      <c r="C111" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="D111" s="136"/>
-      <c r="E111" s="136"/>
-      <c r="F111" s="136"/>
-      <c r="G111" s="136"/>
-      <c r="H111" s="136"/>
-      <c r="I111" s="136"/>
+      <c r="D111" s="85"/>
+      <c r="E111" s="85"/>
+      <c r="F111" s="85"/>
+      <c r="G111" s="85"/>
+      <c r="H111" s="85"/>
+      <c r="I111" s="85"/>
       <c r="J111" s="53"/>
-      <c r="K111" s="137" t="s">
+      <c r="K111" s="99" t="s">
         <v>50</v>
       </c>
-      <c r="L111" s="137"/>
-      <c r="M111" s="137"/>
-      <c r="N111" s="137"/>
-      <c r="O111" s="137"/>
-      <c r="P111" s="137"/>
-      <c r="Q111" s="137"/>
+      <c r="L111" s="99"/>
+      <c r="M111" s="99"/>
+      <c r="N111" s="99"/>
+      <c r="O111" s="99"/>
+      <c r="P111" s="99"/>
+      <c r="Q111" s="99"/>
       <c r="R111" s="4"/>
-      <c r="S111" s="142" t="s">
+      <c r="S111" s="223" t="s">
         <v>47</v>
       </c>
-      <c r="T111" s="143"/>
-      <c r="U111" s="101"/>
-      <c r="V111" s="102"/>
-      <c r="W111" s="103" t="s">
+      <c r="T111" s="224"/>
+      <c r="U111" s="229"/>
+      <c r="V111" s="230"/>
+      <c r="W111" s="231" t="s">
         <v>48</v>
       </c>
-      <c r="X111" s="104"/>
-      <c r="Y111" s="101"/>
-      <c r="Z111" s="102"/>
+      <c r="X111" s="232"/>
+      <c r="Y111" s="229"/>
+      <c r="Z111" s="230"/>
       <c r="AA111" s="4"/>
-      <c r="AB111" s="134"/>
-      <c r="AC111" s="105"/>
-      <c r="AD111" s="105"/>
-      <c r="AE111" s="105"/>
-      <c r="AF111" s="105"/>
-      <c r="AG111" s="105"/>
-      <c r="AH111" s="105"/>
-      <c r="AI111" s="135"/>
+      <c r="AB111" s="96"/>
+      <c r="AC111" s="97"/>
+      <c r="AD111" s="97"/>
+      <c r="AE111" s="97"/>
+      <c r="AF111" s="97"/>
+      <c r="AG111" s="97"/>
+      <c r="AH111" s="97"/>
+      <c r="AI111" s="98"/>
       <c r="AJ111" s="31" t="s">
         <v>123</v>
       </c>
@@ -8418,24 +8551,24 @@
       <c r="H112" s="46"/>
       <c r="I112" s="46"/>
       <c r="J112" s="46"/>
-      <c r="K112" s="138"/>
-      <c r="L112" s="138"/>
-      <c r="M112" s="138"/>
-      <c r="N112" s="138"/>
-      <c r="O112" s="138"/>
-      <c r="P112" s="138"/>
-      <c r="Q112" s="138"/>
+      <c r="K112" s="100"/>
+      <c r="L112" s="100"/>
+      <c r="M112" s="100"/>
+      <c r="N112" s="100"/>
+      <c r="O112" s="100"/>
+      <c r="P112" s="100"/>
+      <c r="Q112" s="100"/>
       <c r="R112" s="4"/>
-      <c r="S112" s="105" t="s">
+      <c r="S112" s="97" t="s">
         <v>124</v>
       </c>
-      <c r="T112" s="105"/>
-      <c r="U112" s="105"/>
-      <c r="V112" s="105"/>
-      <c r="W112" s="105"/>
-      <c r="X112" s="105"/>
-      <c r="Y112" s="105"/>
-      <c r="Z112" s="105"/>
+      <c r="T112" s="97"/>
+      <c r="U112" s="97"/>
+      <c r="V112" s="97"/>
+      <c r="W112" s="97"/>
+      <c r="X112" s="97"/>
+      <c r="Y112" s="97"/>
+      <c r="Z112" s="97"/>
       <c r="AA112" s="4"/>
       <c r="AB112" s="47"/>
       <c r="AC112" s="47"/>
@@ -8467,45 +8600,45 @@
       <c r="BH112" s="43"/>
     </row>
     <row r="113" spans="1:60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="106"/>
-      <c r="B113" s="106"/>
-      <c r="C113" s="112" t="s">
+      <c r="A113" s="168"/>
+      <c r="B113" s="168"/>
+      <c r="C113" s="107" t="s">
         <v>183</v>
       </c>
-      <c r="D113" s="113"/>
-      <c r="E113" s="113"/>
-      <c r="F113" s="113"/>
-      <c r="G113" s="113"/>
-      <c r="H113" s="113"/>
-      <c r="I113" s="113"/>
-      <c r="J113" s="113"/>
-      <c r="K113" s="113"/>
-      <c r="L113" s="113"/>
-      <c r="M113" s="113"/>
+      <c r="D113" s="108"/>
+      <c r="E113" s="108"/>
+      <c r="F113" s="108"/>
+      <c r="G113" s="108"/>
+      <c r="H113" s="108"/>
+      <c r="I113" s="108"/>
+      <c r="J113" s="108"/>
+      <c r="K113" s="108"/>
+      <c r="L113" s="108"/>
+      <c r="M113" s="108"/>
       <c r="N113" s="50"/>
-      <c r="O113" s="107" t="s">
+      <c r="O113" s="155" t="s">
         <v>38</v>
       </c>
-      <c r="P113" s="108"/>
-      <c r="Q113" s="109"/>
+      <c r="P113" s="156"/>
+      <c r="Q113" s="157"/>
       <c r="R113" s="56"/>
-      <c r="S113" s="110"/>
-      <c r="T113" s="111"/>
-      <c r="U113" s="110"/>
-      <c r="V113" s="111"/>
-      <c r="W113" s="110"/>
-      <c r="X113" s="111"/>
-      <c r="Y113" s="110"/>
-      <c r="Z113" s="111"/>
+      <c r="S113" s="139"/>
+      <c r="T113" s="117"/>
+      <c r="U113" s="139"/>
+      <c r="V113" s="117"/>
+      <c r="W113" s="139"/>
+      <c r="X113" s="117"/>
+      <c r="Y113" s="139"/>
+      <c r="Z113" s="117"/>
       <c r="AA113" s="4"/>
-      <c r="AB113" s="139"/>
-      <c r="AC113" s="139"/>
-      <c r="AD113" s="139"/>
-      <c r="AE113" s="139"/>
-      <c r="AF113" s="139"/>
-      <c r="AG113" s="139"/>
-      <c r="AH113" s="139"/>
-      <c r="AI113" s="139"/>
+      <c r="AB113" s="86"/>
+      <c r="AC113" s="86"/>
+      <c r="AD113" s="86"/>
+      <c r="AE113" s="86"/>
+      <c r="AF113" s="86"/>
+      <c r="AG113" s="86"/>
+      <c r="AH113" s="86"/>
+      <c r="AI113" s="86"/>
       <c r="AJ113" s="31"/>
       <c r="AO113" s="30">
         <v>19</v>
@@ -8536,32 +8669,32 @@
     <row r="114" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="39"/>
       <c r="B114" s="39"/>
-      <c r="C114" s="113"/>
-      <c r="D114" s="113"/>
-      <c r="E114" s="113"/>
-      <c r="F114" s="113"/>
-      <c r="G114" s="113"/>
-      <c r="H114" s="113"/>
-      <c r="I114" s="113"/>
-      <c r="J114" s="113"/>
-      <c r="K114" s="113"/>
-      <c r="L114" s="113"/>
-      <c r="M114" s="113"/>
+      <c r="C114" s="108"/>
+      <c r="D114" s="108"/>
+      <c r="E114" s="108"/>
+      <c r="F114" s="108"/>
+      <c r="G114" s="108"/>
+      <c r="H114" s="108"/>
+      <c r="I114" s="108"/>
+      <c r="J114" s="108"/>
+      <c r="K114" s="108"/>
+      <c r="L114" s="108"/>
+      <c r="M114" s="108"/>
       <c r="N114" s="50"/>
       <c r="O114" s="50"/>
       <c r="P114" s="50"/>
       <c r="Q114" s="50"/>
       <c r="R114" s="51"/>
-      <c r="S114" s="118" t="s">
+      <c r="S114" s="102" t="s">
         <v>182</v>
       </c>
-      <c r="T114" s="118"/>
-      <c r="U114" s="118"/>
-      <c r="V114" s="118"/>
-      <c r="W114" s="118"/>
-      <c r="X114" s="118"/>
-      <c r="Y114" s="118"/>
-      <c r="Z114" s="118"/>
+      <c r="T114" s="102"/>
+      <c r="U114" s="102"/>
+      <c r="V114" s="102"/>
+      <c r="W114" s="102"/>
+      <c r="X114" s="102"/>
+      <c r="Y114" s="102"/>
+      <c r="Z114" s="102"/>
       <c r="AA114" s="4"/>
       <c r="AB114" s="40"/>
       <c r="AC114" s="40"/>
@@ -8597,35 +8730,35 @@
       <c r="BH114" s="43"/>
     </row>
     <row r="115" spans="1:60" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="130"/>
-      <c r="B115" s="130"/>
-      <c r="C115" s="76" t="s">
+      <c r="A115" s="75"/>
+      <c r="B115" s="75"/>
+      <c r="C115" s="109" t="s">
         <v>127</v>
       </c>
-      <c r="D115" s="77"/>
-      <c r="E115" s="77"/>
-      <c r="F115" s="77"/>
-      <c r="G115" s="77"/>
-      <c r="H115" s="77"/>
-      <c r="I115" s="77"/>
-      <c r="J115" s="77"/>
-      <c r="K115" s="77"/>
-      <c r="L115" s="77"/>
-      <c r="M115" s="77"/>
+      <c r="D115" s="110"/>
+      <c r="E115" s="110"/>
+      <c r="F115" s="110"/>
+      <c r="G115" s="110"/>
+      <c r="H115" s="110"/>
+      <c r="I115" s="110"/>
+      <c r="J115" s="110"/>
+      <c r="K115" s="110"/>
+      <c r="L115" s="110"/>
+      <c r="M115" s="110"/>
       <c r="N115" s="42"/>
-      <c r="O115" s="107" t="s">
+      <c r="O115" s="155" t="s">
         <v>38</v>
       </c>
-      <c r="P115" s="108"/>
-      <c r="Q115" s="109"/>
-      <c r="S115" s="110"/>
-      <c r="T115" s="111"/>
-      <c r="U115" s="110"/>
-      <c r="V115" s="111"/>
-      <c r="W115" s="110"/>
-      <c r="X115" s="111"/>
-      <c r="Y115" s="110"/>
-      <c r="Z115" s="111"/>
+      <c r="P115" s="156"/>
+      <c r="Q115" s="157"/>
+      <c r="S115" s="139"/>
+      <c r="T115" s="117"/>
+      <c r="U115" s="139"/>
+      <c r="V115" s="117"/>
+      <c r="W115" s="139"/>
+      <c r="X115" s="117"/>
+      <c r="Y115" s="139"/>
+      <c r="Z115" s="117"/>
       <c r="AB115" s="37"/>
       <c r="AC115" s="37"/>
       <c r="AD115" s="37"/>
@@ -8663,23 +8796,23 @@
       <c r="AI116" s="37"/>
     </row>
     <row r="117" spans="1:60" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="85" t="s">
+      <c r="B117" s="115" t="s">
         <v>26</v>
       </c>
-      <c r="C117" s="85"/>
-      <c r="D117" s="85"/>
-      <c r="E117" s="85"/>
-      <c r="F117" s="85"/>
-      <c r="G117" s="85"/>
-      <c r="H117" s="85"/>
-      <c r="I117" s="85"/>
-      <c r="J117" s="85"/>
-      <c r="K117" s="85"/>
-      <c r="L117" s="85"/>
-      <c r="M117" s="85"/>
-      <c r="N117" s="85"/>
-      <c r="O117" s="85"/>
-      <c r="P117" s="85"/>
+      <c r="C117" s="115"/>
+      <c r="D117" s="115"/>
+      <c r="E117" s="115"/>
+      <c r="F117" s="115"/>
+      <c r="G117" s="115"/>
+      <c r="H117" s="115"/>
+      <c r="I117" s="115"/>
+      <c r="J117" s="115"/>
+      <c r="K117" s="115"/>
+      <c r="L117" s="115"/>
+      <c r="M117" s="115"/>
+      <c r="N117" s="115"/>
+      <c r="O117" s="115"/>
+      <c r="P117" s="115"/>
       <c r="AI117" s="37"/>
       <c r="AJ117" s="31"/>
       <c r="AO117" s="30">
@@ -8706,38 +8839,38 @@
       <c r="BH117" s="43"/>
     </row>
     <row r="118" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="B118" s="86"/>
-      <c r="C118" s="87"/>
-      <c r="D118" s="87"/>
-      <c r="E118" s="87"/>
-      <c r="F118" s="87"/>
-      <c r="G118" s="87"/>
-      <c r="H118" s="87"/>
-      <c r="I118" s="87"/>
-      <c r="J118" s="87"/>
-      <c r="K118" s="87"/>
-      <c r="L118" s="87"/>
-      <c r="M118" s="87"/>
-      <c r="N118" s="87"/>
-      <c r="O118" s="88"/>
-      <c r="Q118" s="92"/>
-      <c r="R118" s="93"/>
-      <c r="S118" s="93"/>
-      <c r="T118" s="93"/>
-      <c r="U118" s="93"/>
-      <c r="V118" s="93"/>
-      <c r="W118" s="93"/>
-      <c r="X118" s="94"/>
-      <c r="Z118" s="123"/>
-      <c r="AA118" s="124"/>
-      <c r="AB118" s="124"/>
-      <c r="AC118" s="124"/>
-      <c r="AD118" s="124"/>
-      <c r="AE118" s="124"/>
-      <c r="AF118" s="124"/>
-      <c r="AG118" s="124"/>
-      <c r="AH118" s="124"/>
-      <c r="AI118" s="125"/>
+      <c r="B118" s="186"/>
+      <c r="C118" s="187"/>
+      <c r="D118" s="187"/>
+      <c r="E118" s="187"/>
+      <c r="F118" s="187"/>
+      <c r="G118" s="187"/>
+      <c r="H118" s="187"/>
+      <c r="I118" s="187"/>
+      <c r="J118" s="187"/>
+      <c r="K118" s="187"/>
+      <c r="L118" s="187"/>
+      <c r="M118" s="187"/>
+      <c r="N118" s="187"/>
+      <c r="O118" s="188"/>
+      <c r="Q118" s="194"/>
+      <c r="R118" s="195"/>
+      <c r="S118" s="195"/>
+      <c r="T118" s="195"/>
+      <c r="U118" s="195"/>
+      <c r="V118" s="195"/>
+      <c r="W118" s="195"/>
+      <c r="X118" s="196"/>
+      <c r="Z118" s="121"/>
+      <c r="AA118" s="122"/>
+      <c r="AB118" s="122"/>
+      <c r="AC118" s="122"/>
+      <c r="AD118" s="122"/>
+      <c r="AE118" s="122"/>
+      <c r="AF118" s="122"/>
+      <c r="AG118" s="122"/>
+      <c r="AH118" s="122"/>
+      <c r="AI118" s="123"/>
       <c r="AJ118" s="31"/>
       <c r="AO118" s="30">
         <v>26</v>
@@ -8750,38 +8883,38 @@
       <c r="AS118" s="30"/>
     </row>
     <row r="119" spans="1:60" x14ac:dyDescent="0.25">
-      <c r="B119" s="89"/>
-      <c r="C119" s="90"/>
-      <c r="D119" s="90"/>
-      <c r="E119" s="90"/>
-      <c r="F119" s="90"/>
-      <c r="G119" s="90"/>
-      <c r="H119" s="90"/>
-      <c r="I119" s="90"/>
-      <c r="J119" s="90"/>
-      <c r="K119" s="90"/>
-      <c r="L119" s="90"/>
-      <c r="M119" s="90"/>
-      <c r="N119" s="90"/>
-      <c r="O119" s="91"/>
-      <c r="Q119" s="95"/>
-      <c r="R119" s="96"/>
-      <c r="S119" s="96"/>
-      <c r="T119" s="96"/>
-      <c r="U119" s="96"/>
-      <c r="V119" s="96"/>
-      <c r="W119" s="96"/>
-      <c r="X119" s="97"/>
-      <c r="Z119" s="126"/>
-      <c r="AA119" s="127"/>
-      <c r="AB119" s="127"/>
-      <c r="AC119" s="127"/>
-      <c r="AD119" s="127"/>
-      <c r="AE119" s="127"/>
-      <c r="AF119" s="127"/>
-      <c r="AG119" s="127"/>
-      <c r="AH119" s="127"/>
-      <c r="AI119" s="128"/>
+      <c r="B119" s="189"/>
+      <c r="C119" s="190"/>
+      <c r="D119" s="190"/>
+      <c r="E119" s="190"/>
+      <c r="F119" s="190"/>
+      <c r="G119" s="190"/>
+      <c r="H119" s="190"/>
+      <c r="I119" s="190"/>
+      <c r="J119" s="190"/>
+      <c r="K119" s="190"/>
+      <c r="L119" s="190"/>
+      <c r="M119" s="190"/>
+      <c r="N119" s="190"/>
+      <c r="O119" s="191"/>
+      <c r="Q119" s="197"/>
+      <c r="R119" s="198"/>
+      <c r="S119" s="198"/>
+      <c r="T119" s="198"/>
+      <c r="U119" s="198"/>
+      <c r="V119" s="198"/>
+      <c r="W119" s="198"/>
+      <c r="X119" s="199"/>
+      <c r="Z119" s="124"/>
+      <c r="AA119" s="125"/>
+      <c r="AB119" s="125"/>
+      <c r="AC119" s="125"/>
+      <c r="AD119" s="125"/>
+      <c r="AE119" s="125"/>
+      <c r="AF119" s="125"/>
+      <c r="AG119" s="125"/>
+      <c r="AH119" s="125"/>
+      <c r="AI119" s="126"/>
       <c r="AJ119" s="31"/>
       <c r="AO119" s="30">
         <v>27</v>
@@ -8793,42 +8926,42 @@
       <c r="AS119" s="30"/>
     </row>
     <row r="120" spans="1:60" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="129" t="s">
+      <c r="B120" s="154" t="s">
         <v>27</v>
       </c>
-      <c r="C120" s="129"/>
-      <c r="D120" s="129"/>
-      <c r="E120" s="129"/>
-      <c r="F120" s="129"/>
-      <c r="G120" s="129"/>
-      <c r="H120" s="129"/>
-      <c r="I120" s="129"/>
-      <c r="J120" s="129"/>
-      <c r="K120" s="129"/>
-      <c r="L120" s="129"/>
-      <c r="M120" s="129"/>
-      <c r="N120" s="129"/>
-      <c r="O120" s="129"/>
-      <c r="Q120" s="98"/>
-      <c r="R120" s="99"/>
-      <c r="S120" s="99"/>
-      <c r="T120" s="99"/>
-      <c r="U120" s="99"/>
-      <c r="V120" s="99"/>
-      <c r="W120" s="99"/>
-      <c r="X120" s="100"/>
-      <c r="Z120" s="129" t="s">
+      <c r="C120" s="154"/>
+      <c r="D120" s="154"/>
+      <c r="E120" s="154"/>
+      <c r="F120" s="154"/>
+      <c r="G120" s="154"/>
+      <c r="H120" s="154"/>
+      <c r="I120" s="154"/>
+      <c r="J120" s="154"/>
+      <c r="K120" s="154"/>
+      <c r="L120" s="154"/>
+      <c r="M120" s="154"/>
+      <c r="N120" s="154"/>
+      <c r="O120" s="154"/>
+      <c r="Q120" s="200"/>
+      <c r="R120" s="201"/>
+      <c r="S120" s="201"/>
+      <c r="T120" s="201"/>
+      <c r="U120" s="201"/>
+      <c r="V120" s="201"/>
+      <c r="W120" s="201"/>
+      <c r="X120" s="202"/>
+      <c r="Z120" s="154" t="s">
         <v>28</v>
       </c>
-      <c r="AA120" s="129"/>
-      <c r="AB120" s="129"/>
-      <c r="AC120" s="129"/>
-      <c r="AD120" s="129"/>
-      <c r="AE120" s="129"/>
-      <c r="AF120" s="129"/>
-      <c r="AG120" s="129"/>
-      <c r="AH120" s="129"/>
-      <c r="AI120" s="129"/>
+      <c r="AA120" s="154"/>
+      <c r="AB120" s="154"/>
+      <c r="AC120" s="154"/>
+      <c r="AD120" s="154"/>
+      <c r="AE120" s="154"/>
+      <c r="AF120" s="154"/>
+      <c r="AG120" s="154"/>
+      <c r="AH120" s="154"/>
+      <c r="AI120" s="154"/>
       <c r="AJ120" s="31"/>
       <c r="AO120" s="30">
         <v>28</v>
@@ -8844,16 +8977,16 @@
       <c r="O121" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="Q121" s="78" t="s">
+      <c r="Q121" s="228" t="s">
         <v>29</v>
       </c>
-      <c r="R121" s="78"/>
-      <c r="S121" s="78"/>
-      <c r="T121" s="78"/>
-      <c r="U121" s="78"/>
-      <c r="V121" s="78"/>
-      <c r="W121" s="78"/>
-      <c r="X121" s="78"/>
+      <c r="R121" s="228"/>
+      <c r="S121" s="228"/>
+      <c r="T121" s="228"/>
+      <c r="U121" s="228"/>
+      <c r="V121" s="228"/>
+      <c r="W121" s="228"/>
+      <c r="X121" s="228"/>
       <c r="AJ121" s="31"/>
       <c r="AO121" s="30">
         <v>29</v>
@@ -8866,24 +8999,389 @@
       <c r="AS121" s="30"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="kGSDZG0RfSUubZd5n1QekmZFN7Tvjv9HbUjDdUNTIeQRYwU/flFL/ATqkhfNb7nxXRzGpCxmbpBdR7e88LRR9Q==" saltValue="JR4kVKuLZHrTJN9CB5P0qg==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
-  <protectedRanges>
-    <protectedRange sqref="A61 A64:B73 A63 A62:B62 C61:AI65 C67:AI67 C66:W66 C69:AI73 C68:W68" name="Диапазон8"/>
-    <protectedRange sqref="A2 A5 A7:N7 A8:AI8 A9:I10 J10 A11:E12 F12 AI11 A13:H15 I15 B72:E73" name="Диапазон1"/>
-    <protectedRange sqref="A2 A16:Q17 R17:U17 U16:AI17 Q19:AI19 AD18 W18 A18:P19 A20:AI20 C47 S48:V48 D49:R49 Y49:Z49 X48:AC48 AE48:AI49 E47:R47" name="Диапазон2"/>
-    <protectedRange sqref="A22:B30 C29:Q30 A32:AI34 N23:O23 C25:L25 N25:O25 N27:O27 C27:L27 N21:O21 A21:H21 C23:I23 L23 J21:K21 I22:I28 A31:Q31 A74:AI74 A35:B35 A75:B75 A82:B82 A89:B89 A96:B96 A103:B103 A110:B110" name="Диапазон3"/>
-    <protectedRange sqref="Z45 B45 B49 B47 Y43:Y46 S47:W47 A43:A49 P43:X45 Z120 B120 Y118:Y121 A118:A121 P118:X120" name="Диапазон5"/>
-    <protectedRange sqref="Q46:X46 A52:E55 F52:G52 H55 K52 K54 K55:L55 F54:G54 G53:T53 A50:P51 Y50:AI51 O46 Q51:V51 Q121:X121 O121" name="Диапазон6"/>
-    <protectedRange sqref="G55:T55 A56:AI59 A55:E55 X52:AI55 U52:U55 V53:W55" name="Диапазон7"/>
-    <protectedRange sqref="R29:R30 S22:T30 U29:AI31 AF23:AG23 U25:AD25 AF25:AG25 AF27:AG27 U27:AD27 AF21:AG21 U23:AA23 AD23 AB21:AC21 AA22:AA28 R21:Z21" name="Диапазон3_1"/>
-    <protectedRange sqref="A37 A39:B40 AB102:AI102 A100:B102 AB107:AD107 AB39:AD39 A77 AB79:AD79 A79:B80 A84 AB86:AD86 A86:B87 A91 AB93:AD93 A93:B94 A98 AB100:AD100 A107:B108 A105 AB114:AD114 A112 A114:B115" name="Диапазон3_2"/>
-    <protectedRange sqref="AL39 C39:S39 C41:S41 J35:J37 R35:R37 W39 A36:J36 R36:S36 K36:Q37 S81 W81 A81:Q81 A88:Q88 W102 R97:S97 S102 C102:Q102 AL79 J75:J77 R75:R77 W79 A76:J76 R76:S76 K76:Q77 S88 W88 K97:Q98 AL86 J81:J84 R81:R84 W86 A83:J83 R83:S83 K83:Q84 A95:R95 AL93 J88:J91 R88:R91 W93 A90:J90 R90:S90 K90:Q91 AL100 J96:J98 R96:R98 W100 A97:J97 R104:S104 K104:Q105 AL107 J102:J105 R102:R105 W107 A104:J104 A109:S109 R111:S111 K111:Q112 AL114 J110:J112 R110:R112 W114 A111:J111 C79:S79 C86:S86 C93:S93 C100:S100 C107:S107 C114:S114" name="Диапазон4_1"/>
-    <protectedRange sqref="A42:AI42 A117:AH117" name="Диапазон5_1"/>
-    <protectedRange sqref="AB38:AI38 B38 AB78:AI78 B78 AB85:AI85 B85 AB92:AI92 B92 AB99:AI99 B99 AB106:AI106 B106 AB113:AI113 B113" name="Диапазон3_3"/>
-    <protectedRange sqref="A38 R38:S38 W38 D38:N38 S40 W40 A78 R78:S78 W78 S80 W80 A85 R85:S85 W85 S87 W87 A92 R92:S92 W92 S101 W101 S94 W94 A99 R99:S99 W99 A106 R106:S106 W106 S108 W108 A113 R113:S113 W113 W115 S115 D78:N78 D85:N85 D92:N92 D99:N99 D106:N106 D113:N113" name="Диапазон4"/>
-  </protectedRanges>
+  <sheetProtection algorithmName="SHA-512" hashValue="eDQfzOwUBo/QzkWtYxauSJqwQ5R0RKynrVOmlI7i/5V40NrKgoGa6RUzIGe+peRs5wx9srKZK31II8B0m5gC5w==" saltValue="1NbAgFM6UDNwytNs+/MyZw==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatCells="0"/>
   <dataConsolidate/>
   <mergeCells count="404">
+    <mergeCell ref="K9:W9"/>
+    <mergeCell ref="X7:Y7"/>
+    <mergeCell ref="O7:W7"/>
+    <mergeCell ref="C115:M115"/>
+    <mergeCell ref="Q121:X121"/>
+    <mergeCell ref="K110:Q110"/>
+    <mergeCell ref="C110:I110"/>
+    <mergeCell ref="B117:P117"/>
+    <mergeCell ref="B118:O119"/>
+    <mergeCell ref="Q118:X120"/>
+    <mergeCell ref="U111:V111"/>
+    <mergeCell ref="W111:X111"/>
+    <mergeCell ref="Y111:Z111"/>
+    <mergeCell ref="S112:Z112"/>
+    <mergeCell ref="A113:B113"/>
+    <mergeCell ref="O113:Q113"/>
+    <mergeCell ref="S113:T113"/>
+    <mergeCell ref="U113:V113"/>
+    <mergeCell ref="W113:X113"/>
+    <mergeCell ref="C99:M100"/>
+    <mergeCell ref="O99:Q99"/>
+    <mergeCell ref="S99:T99"/>
+    <mergeCell ref="U99:V99"/>
+    <mergeCell ref="U106:V106"/>
+    <mergeCell ref="W106:X106"/>
+    <mergeCell ref="Y106:Z106"/>
+    <mergeCell ref="C106:M107"/>
+    <mergeCell ref="O106:Q106"/>
+    <mergeCell ref="S107:Z107"/>
+    <mergeCell ref="S103:Z103"/>
+    <mergeCell ref="Z118:AI119"/>
+    <mergeCell ref="B120:O120"/>
+    <mergeCell ref="Z120:AI120"/>
+    <mergeCell ref="A115:B115"/>
+    <mergeCell ref="O115:Q115"/>
+    <mergeCell ref="S115:T115"/>
+    <mergeCell ref="U115:V115"/>
+    <mergeCell ref="W115:X115"/>
+    <mergeCell ref="Y115:Z115"/>
+    <mergeCell ref="Y113:Z113"/>
+    <mergeCell ref="AB110:AI111"/>
+    <mergeCell ref="C111:I111"/>
+    <mergeCell ref="K111:Q112"/>
+    <mergeCell ref="C113:M114"/>
+    <mergeCell ref="AB113:AI113"/>
+    <mergeCell ref="S114:Z114"/>
+    <mergeCell ref="S110:Z110"/>
+    <mergeCell ref="S111:T111"/>
+    <mergeCell ref="Y104:Z104"/>
+    <mergeCell ref="C109:I109"/>
+    <mergeCell ref="S109:T109"/>
+    <mergeCell ref="U109:V109"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="O108:Q108"/>
+    <mergeCell ref="S108:T108"/>
+    <mergeCell ref="U108:V108"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="K96:Q96"/>
+    <mergeCell ref="S96:Z96"/>
+    <mergeCell ref="K97:Q98"/>
+    <mergeCell ref="S97:T97"/>
+    <mergeCell ref="U97:V97"/>
+    <mergeCell ref="W97:X97"/>
+    <mergeCell ref="Y97:Z97"/>
+    <mergeCell ref="S98:Z98"/>
+    <mergeCell ref="A101:B101"/>
+    <mergeCell ref="A106:B106"/>
+    <mergeCell ref="S106:T106"/>
+    <mergeCell ref="W99:X99"/>
+    <mergeCell ref="Y99:Z99"/>
+    <mergeCell ref="K109:Q109"/>
+    <mergeCell ref="C108:M108"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="AB92:AI92"/>
+    <mergeCell ref="S93:Z93"/>
+    <mergeCell ref="AB96:AI97"/>
+    <mergeCell ref="S100:Z100"/>
+    <mergeCell ref="S101:T101"/>
+    <mergeCell ref="U101:V101"/>
+    <mergeCell ref="W101:X101"/>
+    <mergeCell ref="Y101:Z101"/>
+    <mergeCell ref="C101:M101"/>
+    <mergeCell ref="O101:Q101"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="C94:L94"/>
+    <mergeCell ref="O94:Q94"/>
+    <mergeCell ref="S94:T94"/>
+    <mergeCell ref="U94:V94"/>
+    <mergeCell ref="W94:X94"/>
+    <mergeCell ref="Y94:Z94"/>
+    <mergeCell ref="AB99:AI99"/>
+    <mergeCell ref="U90:V90"/>
+    <mergeCell ref="W90:X90"/>
+    <mergeCell ref="Y90:Z90"/>
+    <mergeCell ref="S91:Z91"/>
+    <mergeCell ref="A92:B92"/>
+    <mergeCell ref="C92:M93"/>
+    <mergeCell ref="O92:Q92"/>
+    <mergeCell ref="S92:T92"/>
+    <mergeCell ref="U92:V92"/>
+    <mergeCell ref="W92:X92"/>
+    <mergeCell ref="Y92:Z92"/>
+    <mergeCell ref="K82:Q82"/>
+    <mergeCell ref="AB82:AI83"/>
+    <mergeCell ref="C83:I83"/>
+    <mergeCell ref="K83:Q84"/>
+    <mergeCell ref="S82:Z82"/>
+    <mergeCell ref="S83:T83"/>
+    <mergeCell ref="U83:V83"/>
+    <mergeCell ref="W83:X83"/>
+    <mergeCell ref="Y83:Z83"/>
+    <mergeCell ref="S84:Z84"/>
+    <mergeCell ref="AA28:AB28"/>
+    <mergeCell ref="AC28:AD28"/>
+    <mergeCell ref="AG28:AH28"/>
+    <mergeCell ref="B31:P31"/>
+    <mergeCell ref="S34:Z34"/>
+    <mergeCell ref="S28:T28"/>
+    <mergeCell ref="U28:V28"/>
+    <mergeCell ref="AE28:AF28"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="B32:P32"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="W28:X28"/>
+    <mergeCell ref="Y28:Z28"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="U29:V29"/>
+    <mergeCell ref="W29:X29"/>
+    <mergeCell ref="R31:T31"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="C97:I97"/>
+    <mergeCell ref="C103:I103"/>
+    <mergeCell ref="K103:Q103"/>
+    <mergeCell ref="AB103:AI104"/>
+    <mergeCell ref="C104:I104"/>
+    <mergeCell ref="K104:Q105"/>
+    <mergeCell ref="S105:Z105"/>
+    <mergeCell ref="S104:T104"/>
+    <mergeCell ref="U104:V104"/>
+    <mergeCell ref="W104:X104"/>
+    <mergeCell ref="C80:L80"/>
+    <mergeCell ref="O80:Q80"/>
+    <mergeCell ref="C85:M86"/>
+    <mergeCell ref="O85:Q85"/>
+    <mergeCell ref="S86:Z86"/>
+    <mergeCell ref="C87:L87"/>
+    <mergeCell ref="O87:Q87"/>
+    <mergeCell ref="S87:T87"/>
+    <mergeCell ref="U87:V87"/>
+    <mergeCell ref="W87:X87"/>
+    <mergeCell ref="Y87:Z87"/>
+    <mergeCell ref="C82:I82"/>
+    <mergeCell ref="S85:T85"/>
+    <mergeCell ref="Z47:AA47"/>
+    <mergeCell ref="X47:Y47"/>
+    <mergeCell ref="X48:Y48"/>
+    <mergeCell ref="Z48:AA48"/>
+    <mergeCell ref="AB48:AC48"/>
+    <mergeCell ref="S47:V47"/>
+    <mergeCell ref="AB47:AC47"/>
+    <mergeCell ref="AE48:AI49"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A58:AI59"/>
+    <mergeCell ref="H55:J55"/>
+    <mergeCell ref="C74:J74"/>
+    <mergeCell ref="K74:R74"/>
+    <mergeCell ref="AB74:AI74"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="K75:Q75"/>
+    <mergeCell ref="S75:Z75"/>
+    <mergeCell ref="AB75:AI76"/>
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="O66:W66"/>
+    <mergeCell ref="K68:W68"/>
+    <mergeCell ref="X66:Y66"/>
+    <mergeCell ref="X68:Y68"/>
+    <mergeCell ref="W85:X85"/>
+    <mergeCell ref="Y85:Z85"/>
+    <mergeCell ref="AB85:AI85"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="B72:E72"/>
+    <mergeCell ref="F72:AH72"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="B43:O44"/>
+    <mergeCell ref="K76:Q77"/>
+    <mergeCell ref="S76:T76"/>
+    <mergeCell ref="U76:V76"/>
+    <mergeCell ref="W76:X76"/>
+    <mergeCell ref="Y76:Z76"/>
+    <mergeCell ref="S77:Z77"/>
+    <mergeCell ref="Z43:AI44"/>
+    <mergeCell ref="O67:AI67"/>
+    <mergeCell ref="J69:AI69"/>
+    <mergeCell ref="B70:P70"/>
+    <mergeCell ref="B66:N66"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="Q43:X45"/>
+    <mergeCell ref="A61:AI61"/>
+    <mergeCell ref="A63:AI64"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="B68:J68"/>
+    <mergeCell ref="S78:T78"/>
+    <mergeCell ref="AB70:AC70"/>
+    <mergeCell ref="AE70:AI70"/>
+    <mergeCell ref="Q70:V70"/>
+    <mergeCell ref="X70:Y70"/>
+    <mergeCell ref="Z70:AA70"/>
+    <mergeCell ref="C75:I75"/>
+    <mergeCell ref="S74:Z74"/>
+    <mergeCell ref="AB78:AI78"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="S79:Z79"/>
+    <mergeCell ref="S80:T80"/>
+    <mergeCell ref="U80:V80"/>
+    <mergeCell ref="W80:X80"/>
+    <mergeCell ref="Y80:Z80"/>
+    <mergeCell ref="U78:V78"/>
+    <mergeCell ref="W78:X78"/>
+    <mergeCell ref="Y78:Z78"/>
+    <mergeCell ref="C78:M79"/>
+    <mergeCell ref="O78:Q78"/>
+    <mergeCell ref="U85:V85"/>
+    <mergeCell ref="J10:AI10"/>
+    <mergeCell ref="F11:AH11"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="Z18:AA18"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B20:L20"/>
+    <mergeCell ref="AB19:AC19"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="A2:AI4"/>
+    <mergeCell ref="B7:N7"/>
+    <mergeCell ref="Q19:V19"/>
+    <mergeCell ref="A5:AI6"/>
+    <mergeCell ref="I15:AI15"/>
+    <mergeCell ref="B16:Q16"/>
+    <mergeCell ref="AB18:AC18"/>
+    <mergeCell ref="B9:J9"/>
+    <mergeCell ref="Q18:V18"/>
+    <mergeCell ref="I13:AI14"/>
+    <mergeCell ref="R16:T16"/>
+    <mergeCell ref="AE18:AI18"/>
+    <mergeCell ref="B18:P18"/>
+    <mergeCell ref="B19:P19"/>
+    <mergeCell ref="AE19:AI20"/>
+    <mergeCell ref="X9:Y9"/>
+    <mergeCell ref="AG26:AH26"/>
+    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="W26:X26"/>
+    <mergeCell ref="Y26:Z26"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="U24:V24"/>
+    <mergeCell ref="W24:X24"/>
+    <mergeCell ref="Y24:Z24"/>
+    <mergeCell ref="AA24:AB24"/>
+    <mergeCell ref="AC24:AD24"/>
+    <mergeCell ref="AE24:AF24"/>
+    <mergeCell ref="S24:T24"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="C21:H21"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="AB21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="S22:T22"/>
+    <mergeCell ref="U22:V22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="N21:Q21"/>
+    <mergeCell ref="O22:P22"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="U21:Z21"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="O8:AI8"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="Z19:AA19"/>
+    <mergeCell ref="F12:AI12"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="W22:X22"/>
+    <mergeCell ref="Y22:Z22"/>
+    <mergeCell ref="AA22:AB22"/>
+    <mergeCell ref="AC22:AD22"/>
+    <mergeCell ref="AE22:AF22"/>
+    <mergeCell ref="AG22:AH22"/>
+    <mergeCell ref="U23:V23"/>
+    <mergeCell ref="W23:X23"/>
+    <mergeCell ref="Y23:Z23"/>
+    <mergeCell ref="AG24:AH24"/>
+    <mergeCell ref="AA26:AB26"/>
+    <mergeCell ref="AE26:AF26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="AC26:AD26"/>
+    <mergeCell ref="S36:T36"/>
+    <mergeCell ref="U36:V36"/>
+    <mergeCell ref="W36:X36"/>
+    <mergeCell ref="Y36:Z36"/>
+    <mergeCell ref="S37:Z37"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="Y29:Z29"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="U25:V25"/>
+    <mergeCell ref="W25:X25"/>
+    <mergeCell ref="Y25:Z25"/>
+    <mergeCell ref="S26:T26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="U27:V27"/>
+    <mergeCell ref="W27:X27"/>
+    <mergeCell ref="Y27:Z27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="A1:AI1"/>
+    <mergeCell ref="A56:AI57"/>
+    <mergeCell ref="B42:P42"/>
+    <mergeCell ref="L55:T55"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="B45:O45"/>
+    <mergeCell ref="Z45:AI45"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="AB35:AI36"/>
+    <mergeCell ref="AB34:AI34"/>
+    <mergeCell ref="L53:T53"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="C35:I35"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="Q46:X46"/>
+    <mergeCell ref="B50:L50"/>
+    <mergeCell ref="X52:Y52"/>
+    <mergeCell ref="Z52:AI53"/>
+    <mergeCell ref="Z54:AI54"/>
+    <mergeCell ref="H53:J53"/>
+    <mergeCell ref="AE47:AI47"/>
+    <mergeCell ref="S48:V49"/>
+    <mergeCell ref="S38:T38"/>
+    <mergeCell ref="U38:V38"/>
+    <mergeCell ref="W38:X38"/>
+    <mergeCell ref="Y38:Z38"/>
+    <mergeCell ref="T32:AI32"/>
+    <mergeCell ref="AB38:AI38"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="S39:Z39"/>
+    <mergeCell ref="AB40:AI41"/>
+    <mergeCell ref="K34:R34"/>
+    <mergeCell ref="C34:J34"/>
+    <mergeCell ref="K35:Q35"/>
+    <mergeCell ref="C36:I36"/>
+    <mergeCell ref="O38:Q38"/>
+    <mergeCell ref="C38:M39"/>
+    <mergeCell ref="C40:M40"/>
+    <mergeCell ref="O40:Q40"/>
+    <mergeCell ref="S40:T40"/>
+    <mergeCell ref="U40:V40"/>
+    <mergeCell ref="W40:X40"/>
+    <mergeCell ref="Y40:Z40"/>
+    <mergeCell ref="K36:Q37"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="S35:Z35"/>
     <mergeCell ref="A110:B110"/>
     <mergeCell ref="W108:X108"/>
     <mergeCell ref="Y108:Z108"/>
@@ -8908,431 +9406,42 @@
     <mergeCell ref="AB89:AI90"/>
     <mergeCell ref="K90:Q91"/>
     <mergeCell ref="S90:T90"/>
-    <mergeCell ref="S38:T38"/>
-    <mergeCell ref="U38:V38"/>
-    <mergeCell ref="W38:X38"/>
-    <mergeCell ref="Y38:Z38"/>
-    <mergeCell ref="T32:AI32"/>
-    <mergeCell ref="AB38:AI38"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="S39:Z39"/>
-    <mergeCell ref="AB40:AI41"/>
-    <mergeCell ref="K34:R34"/>
-    <mergeCell ref="C34:J34"/>
-    <mergeCell ref="K35:Q35"/>
-    <mergeCell ref="C36:I36"/>
-    <mergeCell ref="O38:Q38"/>
-    <mergeCell ref="C38:M39"/>
-    <mergeCell ref="C40:M40"/>
-    <mergeCell ref="O40:Q40"/>
-    <mergeCell ref="S40:T40"/>
-    <mergeCell ref="U40:V40"/>
-    <mergeCell ref="W40:X40"/>
-    <mergeCell ref="Y40:Z40"/>
-    <mergeCell ref="K36:Q37"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="S35:Z35"/>
-    <mergeCell ref="A1:AI1"/>
-    <mergeCell ref="A56:AI57"/>
-    <mergeCell ref="B42:P42"/>
-    <mergeCell ref="L55:T55"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="B45:O45"/>
-    <mergeCell ref="Z45:AI45"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="AB35:AI36"/>
-    <mergeCell ref="AB34:AI34"/>
-    <mergeCell ref="L53:T53"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="C35:I35"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="Q46:X46"/>
-    <mergeCell ref="B50:L50"/>
-    <mergeCell ref="X52:Y52"/>
-    <mergeCell ref="Z52:AI53"/>
-    <mergeCell ref="Z54:AI54"/>
-    <mergeCell ref="H53:J53"/>
-    <mergeCell ref="AE47:AI47"/>
-    <mergeCell ref="S48:V49"/>
-    <mergeCell ref="S36:T36"/>
-    <mergeCell ref="U36:V36"/>
-    <mergeCell ref="W36:X36"/>
-    <mergeCell ref="Y36:Z36"/>
-    <mergeCell ref="S37:Z37"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="Y29:Z29"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="U25:V25"/>
-    <mergeCell ref="W25:X25"/>
-    <mergeCell ref="Y25:Z25"/>
-    <mergeCell ref="S26:T26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="U27:V27"/>
-    <mergeCell ref="W27:X27"/>
-    <mergeCell ref="Y27:Z27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="O8:AI8"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="Z19:AA19"/>
-    <mergeCell ref="F12:AI12"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="W22:X22"/>
-    <mergeCell ref="Y22:Z22"/>
-    <mergeCell ref="AA22:AB22"/>
-    <mergeCell ref="AC22:AD22"/>
-    <mergeCell ref="AE22:AF22"/>
-    <mergeCell ref="AG22:AH22"/>
-    <mergeCell ref="U23:V23"/>
-    <mergeCell ref="W23:X23"/>
-    <mergeCell ref="Y23:Z23"/>
-    <mergeCell ref="AG24:AH24"/>
-    <mergeCell ref="AA26:AB26"/>
-    <mergeCell ref="AE26:AF26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="AC26:AD26"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="C21:H21"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="AB21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="S22:T22"/>
-    <mergeCell ref="U22:V22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="N21:Q21"/>
-    <mergeCell ref="O22:P22"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="U21:Z21"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="AG26:AH26"/>
-    <mergeCell ref="U26:V26"/>
-    <mergeCell ref="W26:X26"/>
-    <mergeCell ref="Y26:Z26"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="U24:V24"/>
-    <mergeCell ref="W24:X24"/>
-    <mergeCell ref="Y24:Z24"/>
-    <mergeCell ref="AA24:AB24"/>
-    <mergeCell ref="AC24:AD24"/>
-    <mergeCell ref="AE24:AF24"/>
-    <mergeCell ref="S24:T24"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="J10:AI10"/>
-    <mergeCell ref="F11:AH11"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="Z18:AA18"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B20:L20"/>
-    <mergeCell ref="AB19:AC19"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="A2:AI4"/>
-    <mergeCell ref="B7:N7"/>
-    <mergeCell ref="Q19:V19"/>
-    <mergeCell ref="A5:AI6"/>
-    <mergeCell ref="I15:AI15"/>
-    <mergeCell ref="B16:Q16"/>
-    <mergeCell ref="AB18:AC18"/>
-    <mergeCell ref="B9:J9"/>
-    <mergeCell ref="Q18:V18"/>
-    <mergeCell ref="I13:AI14"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="AE18:AI18"/>
-    <mergeCell ref="B18:P18"/>
-    <mergeCell ref="B19:P19"/>
-    <mergeCell ref="AE19:AI20"/>
-    <mergeCell ref="X9:Y9"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="B68:J68"/>
-    <mergeCell ref="S78:T78"/>
-    <mergeCell ref="AB70:AC70"/>
-    <mergeCell ref="AE70:AI70"/>
-    <mergeCell ref="Q70:V70"/>
-    <mergeCell ref="X70:Y70"/>
-    <mergeCell ref="Z70:AA70"/>
-    <mergeCell ref="C75:I75"/>
-    <mergeCell ref="S74:Z74"/>
-    <mergeCell ref="AB78:AI78"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="S79:Z79"/>
-    <mergeCell ref="S80:T80"/>
-    <mergeCell ref="U80:V80"/>
-    <mergeCell ref="W80:X80"/>
-    <mergeCell ref="Y80:Z80"/>
-    <mergeCell ref="U78:V78"/>
-    <mergeCell ref="W78:X78"/>
-    <mergeCell ref="Y78:Z78"/>
-    <mergeCell ref="C78:M79"/>
-    <mergeCell ref="O78:Q78"/>
-    <mergeCell ref="U85:V85"/>
-    <mergeCell ref="W85:X85"/>
-    <mergeCell ref="Y85:Z85"/>
-    <mergeCell ref="AB85:AI85"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="B72:E72"/>
-    <mergeCell ref="F72:AH72"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="B43:O44"/>
-    <mergeCell ref="K76:Q77"/>
-    <mergeCell ref="S76:T76"/>
-    <mergeCell ref="U76:V76"/>
-    <mergeCell ref="W76:X76"/>
-    <mergeCell ref="Y76:Z76"/>
-    <mergeCell ref="S77:Z77"/>
-    <mergeCell ref="Z43:AI44"/>
-    <mergeCell ref="O67:AI67"/>
-    <mergeCell ref="J69:AI69"/>
-    <mergeCell ref="B70:P70"/>
-    <mergeCell ref="B66:N66"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="Q43:X45"/>
-    <mergeCell ref="A61:AI61"/>
-    <mergeCell ref="A63:AI64"/>
-    <mergeCell ref="A58:AI59"/>
-    <mergeCell ref="H55:J55"/>
-    <mergeCell ref="C74:J74"/>
-    <mergeCell ref="K74:R74"/>
-    <mergeCell ref="AB74:AI74"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="K75:Q75"/>
-    <mergeCell ref="S75:Z75"/>
-    <mergeCell ref="AB75:AI76"/>
-    <mergeCell ref="C76:I76"/>
-    <mergeCell ref="O66:W66"/>
-    <mergeCell ref="K68:W68"/>
-    <mergeCell ref="X66:Y66"/>
-    <mergeCell ref="X68:Y68"/>
-    <mergeCell ref="Z47:AA47"/>
-    <mergeCell ref="X47:Y47"/>
-    <mergeCell ref="X48:Y48"/>
-    <mergeCell ref="Z48:AA48"/>
-    <mergeCell ref="AB48:AC48"/>
-    <mergeCell ref="S47:V47"/>
-    <mergeCell ref="AB47:AC47"/>
-    <mergeCell ref="AE48:AI49"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C97:I97"/>
-    <mergeCell ref="C103:I103"/>
-    <mergeCell ref="K103:Q103"/>
-    <mergeCell ref="AB103:AI104"/>
-    <mergeCell ref="C104:I104"/>
-    <mergeCell ref="K104:Q105"/>
-    <mergeCell ref="S105:Z105"/>
-    <mergeCell ref="S104:T104"/>
-    <mergeCell ref="U104:V104"/>
-    <mergeCell ref="W104:X104"/>
-    <mergeCell ref="C80:L80"/>
-    <mergeCell ref="O80:Q80"/>
-    <mergeCell ref="C85:M86"/>
-    <mergeCell ref="O85:Q85"/>
-    <mergeCell ref="S86:Z86"/>
-    <mergeCell ref="C87:L87"/>
-    <mergeCell ref="O87:Q87"/>
-    <mergeCell ref="S87:T87"/>
-    <mergeCell ref="U87:V87"/>
-    <mergeCell ref="W87:X87"/>
-    <mergeCell ref="Y87:Z87"/>
-    <mergeCell ref="C82:I82"/>
-    <mergeCell ref="S85:T85"/>
-    <mergeCell ref="AA28:AB28"/>
-    <mergeCell ref="AC28:AD28"/>
-    <mergeCell ref="AG28:AH28"/>
-    <mergeCell ref="B31:P31"/>
-    <mergeCell ref="S34:Z34"/>
-    <mergeCell ref="S28:T28"/>
-    <mergeCell ref="U28:V28"/>
-    <mergeCell ref="AE28:AF28"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="B32:P32"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="W28:X28"/>
-    <mergeCell ref="Y28:Z28"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="U29:V29"/>
-    <mergeCell ref="W29:X29"/>
-    <mergeCell ref="R31:T31"/>
-    <mergeCell ref="K82:Q82"/>
-    <mergeCell ref="AB82:AI83"/>
-    <mergeCell ref="C83:I83"/>
-    <mergeCell ref="K83:Q84"/>
-    <mergeCell ref="S82:Z82"/>
-    <mergeCell ref="S83:T83"/>
-    <mergeCell ref="U83:V83"/>
-    <mergeCell ref="W83:X83"/>
-    <mergeCell ref="Y83:Z83"/>
-    <mergeCell ref="S84:Z84"/>
-    <mergeCell ref="U90:V90"/>
-    <mergeCell ref="W90:X90"/>
-    <mergeCell ref="Y90:Z90"/>
-    <mergeCell ref="S91:Z91"/>
-    <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:M93"/>
-    <mergeCell ref="O92:Q92"/>
-    <mergeCell ref="S92:T92"/>
-    <mergeCell ref="U92:V92"/>
-    <mergeCell ref="W92:X92"/>
-    <mergeCell ref="Y92:Z92"/>
-    <mergeCell ref="A99:B99"/>
-    <mergeCell ref="AB92:AI92"/>
-    <mergeCell ref="S93:Z93"/>
-    <mergeCell ref="AB96:AI97"/>
-    <mergeCell ref="S100:Z100"/>
-    <mergeCell ref="S101:T101"/>
-    <mergeCell ref="U101:V101"/>
-    <mergeCell ref="W101:X101"/>
-    <mergeCell ref="Y101:Z101"/>
-    <mergeCell ref="C101:M101"/>
-    <mergeCell ref="O101:Q101"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="C94:L94"/>
-    <mergeCell ref="O94:Q94"/>
-    <mergeCell ref="S94:T94"/>
-    <mergeCell ref="U94:V94"/>
-    <mergeCell ref="W94:X94"/>
-    <mergeCell ref="Y94:Z94"/>
-    <mergeCell ref="AB99:AI99"/>
-    <mergeCell ref="Y104:Z104"/>
-    <mergeCell ref="C109:I109"/>
-    <mergeCell ref="S109:T109"/>
-    <mergeCell ref="U109:V109"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="O108:Q108"/>
-    <mergeCell ref="S108:T108"/>
-    <mergeCell ref="U108:V108"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="K96:Q96"/>
-    <mergeCell ref="S96:Z96"/>
-    <mergeCell ref="K97:Q98"/>
-    <mergeCell ref="S97:T97"/>
-    <mergeCell ref="U97:V97"/>
-    <mergeCell ref="W97:X97"/>
-    <mergeCell ref="Y97:Z97"/>
-    <mergeCell ref="S98:Z98"/>
-    <mergeCell ref="A101:B101"/>
-    <mergeCell ref="A106:B106"/>
-    <mergeCell ref="S106:T106"/>
-    <mergeCell ref="W99:X99"/>
-    <mergeCell ref="Y99:Z99"/>
-    <mergeCell ref="K109:Q109"/>
-    <mergeCell ref="C108:M108"/>
-    <mergeCell ref="W106:X106"/>
-    <mergeCell ref="Y106:Z106"/>
-    <mergeCell ref="C106:M107"/>
-    <mergeCell ref="O106:Q106"/>
-    <mergeCell ref="S107:Z107"/>
-    <mergeCell ref="S103:Z103"/>
-    <mergeCell ref="Z118:AI119"/>
-    <mergeCell ref="B120:O120"/>
-    <mergeCell ref="Z120:AI120"/>
-    <mergeCell ref="A115:B115"/>
-    <mergeCell ref="O115:Q115"/>
-    <mergeCell ref="S115:T115"/>
-    <mergeCell ref="U115:V115"/>
-    <mergeCell ref="W115:X115"/>
-    <mergeCell ref="Y115:Z115"/>
-    <mergeCell ref="Y113:Z113"/>
-    <mergeCell ref="AB110:AI111"/>
-    <mergeCell ref="C111:I111"/>
-    <mergeCell ref="K111:Q112"/>
-    <mergeCell ref="C113:M114"/>
-    <mergeCell ref="AB113:AI113"/>
-    <mergeCell ref="S114:Z114"/>
-    <mergeCell ref="S110:Z110"/>
-    <mergeCell ref="S111:T111"/>
-    <mergeCell ref="K9:W9"/>
-    <mergeCell ref="X7:Y7"/>
-    <mergeCell ref="O7:W7"/>
-    <mergeCell ref="C115:M115"/>
-    <mergeCell ref="Q121:X121"/>
-    <mergeCell ref="K110:Q110"/>
-    <mergeCell ref="C110:I110"/>
-    <mergeCell ref="B117:P117"/>
-    <mergeCell ref="B118:O119"/>
-    <mergeCell ref="Q118:X120"/>
-    <mergeCell ref="U111:V111"/>
-    <mergeCell ref="W111:X111"/>
-    <mergeCell ref="Y111:Z111"/>
-    <mergeCell ref="S112:Z112"/>
-    <mergeCell ref="A113:B113"/>
-    <mergeCell ref="O113:Q113"/>
-    <mergeCell ref="S113:T113"/>
-    <mergeCell ref="U113:V113"/>
-    <mergeCell ref="W113:X113"/>
-    <mergeCell ref="C99:M100"/>
-    <mergeCell ref="O99:Q99"/>
-    <mergeCell ref="S99:T99"/>
-    <mergeCell ref="U99:V99"/>
-    <mergeCell ref="U106:V106"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
-  <dataValidations count="14">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F11:AH11">
+  <dataValidations count="11">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F11:AH11" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$AJ$20:$AJ$33</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R16:T16 R31:T31 O38:Q38 O40:Q40 O78:Q78 O80:Q80 O85:Q85 O87:Q87 O92:Q92 O94:Q94 O99:Q99 O101:Q101 O106:Q106 O108:Q108 O113:Q113 O115:Q115">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R16:T16 R31:T31 O38:Q38 O40:Q40 O78:Q78 O80:Q80 O85:Q85 O87:Q87 O92:Q92 O94:Q94 O99:Q99 O101:Q101 O106:Q106 O108:Q108 O113:Q113 O115:Q115" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$AK$22:$AK$23</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q18:V18">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q18:V18" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>$AL$23:$AL$25</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C96:I96 C75:I75 C82:I82 AE100 C35:I35 AE79 AE39 AE86 C89:I89 AE93 C103:I103 AE107 C110:I110 AE114">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C96:I96 C75:I75 C82:I82 AE100 C35:I35 AE79 AE39 AE86 C89:I89 AE93 C103:I103 AE107 C110:I110 AE114" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>$AM$20:$AM$24</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S47:V47">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S47:V47" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>$AS$19:$AS$21</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z47:AA47 E28:F28 E22:F22 W26:X26 Z18:AA18 W22:X22 W24:X24 W28:X28 E26:F26 E24:F24">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z47:AA47 E28:F28 E22:F22 W26:X26 Z18:AA18 W22:X22 W24:X24 W28:X28 E26:F26 E24:F24" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>$AP$19:$AP$30</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB47:AC47">
-      <formula1>$AQ$19:$AQ$53</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB47:AC47" xr:uid="{00000000-0002-0000-0000-000006000000}">
+      <formula1>$AQ$19:$AQ$55</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X18:Y18 U22:V22 U24:V24 U26:V26 U28:V28 C22:D22 C24:D24 C26:D26 C28:D28 X47:Y47">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X18:Y18 U22:V22 U24:V24 U26:V26 U28:V28 C22:D22 C24:D24 C26:D26 C28:D28 X47:Y47" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>$AT$39:$AT$69</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K22:L22 O22:P22 K24:L24 O24:P24 K26:L26 O26:P26 K28:L28 O28:P28 AC22:AD22 AG22:AH22 AC24:AD24 AG24:AH24 AC26:AD26 AG26:AH26 AC28:AD28 AG28:AH28">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K22:L22 O22:P22 K24:L24 O24:P24 K26:L26 O26:P26 K28:L28 O28:P28 AC22:AD22 AG22:AH22 AC24:AD24 AG24:AH24 AC26:AD26 AG26:AH26 AC28:AD28 AG28:AH28" xr:uid="{00000000-0002-0000-0000-000008000000}">
       <formula1>$AR$19:$AR$42</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB18:AC18 G22:H22 G24:H24 G26:H26 G28:H28 Y22:Z22">
-      <formula1>$AQ$19:$AQ$53</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y28:Z28">
-      <formula1>$AQ$19:$AQ$53</formula1>
-    </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z9:AI9 Z7:AI7 Z66:AI66 Z68:AI68">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z9:AI9 Z7:AI7 Z66:AI66 Z68:AI68" xr:uid="{00000000-0002-0000-0000-00000B000000}">
       <formula1>0</formula1>
       <formula2>9</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y26:Z26">
-      <formula1>$AQ$19:$AQ$53</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y24:Z24">
-      <formula1>$AQ$19:$AQ$53</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y22:Z22 Y24:Z24 AB18:AC18 Y26:Z26 Y28:Z28 G22:H22 G24:H24 G26:H26 G28:H28" xr:uid="{E1CCCCB1-B4D7-45DB-87CD-B69E8C5427DA}">
+      <formula1>$AQ$19:$AQ$55</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0" bottom="0" header="0.31496062992125984" footer="0"/>
